--- a/unified-summary.xlsx
+++ b/unified-summary.xlsx
@@ -23,13 +23,13 @@
     <t>Build Number:</t>
   </si>
   <si>
-    <t>#1</t>
+    <t>#2</t>
   </si>
   <si>
     <t>Execution Date:</t>
   </si>
   <si>
-    <t>2026-07-19 17:56:08 UTC</t>
+    <t>2026-07-19 18:21:02 UTC</t>
   </si>
   <si>
     <t>Branch:</t>
@@ -6075,7 +6075,7 @@
         <v>31</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
         <v>32</v>
@@ -6089,7 +6089,7 @@
         <v>31</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
         <v>32</v>
@@ -6103,7 +6103,7 @@
         <v>31</v>
       </c>
       <c r="C4">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
@@ -6117,7 +6117,7 @@
         <v>31</v>
       </c>
       <c r="C5">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
         <v>32</v>
@@ -6131,7 +6131,7 @@
         <v>31</v>
       </c>
       <c r="C6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
         <v>32</v>
@@ -6145,7 +6145,7 @@
         <v>31</v>
       </c>
       <c r="C7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
@@ -6159,7 +6159,7 @@
         <v>31</v>
       </c>
       <c r="C8">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
         <v>32</v>
@@ -6173,7 +6173,7 @@
         <v>31</v>
       </c>
       <c r="C9">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="D9" t="s">
         <v>32</v>
@@ -6187,7 +6187,7 @@
         <v>31</v>
       </c>
       <c r="C10">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D10" t="s">
         <v>32</v>
@@ -6201,7 +6201,7 @@
         <v>31</v>
       </c>
       <c r="C11">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
@@ -6215,7 +6215,7 @@
         <v>31</v>
       </c>
       <c r="C12">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
         <v>32</v>
@@ -6229,7 +6229,7 @@
         <v>31</v>
       </c>
       <c r="C13">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D13" t="s">
         <v>32</v>
@@ -6243,7 +6243,7 @@
         <v>31</v>
       </c>
       <c r="C14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
         <v>32</v>
@@ -6257,7 +6257,7 @@
         <v>31</v>
       </c>
       <c r="C15">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="D15" t="s">
         <v>32</v>
@@ -6271,7 +6271,7 @@
         <v>31</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s">
         <v>32</v>
@@ -6285,7 +6285,7 @@
         <v>31</v>
       </c>
       <c r="C17">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D17" t="s">
         <v>32</v>
@@ -6299,7 +6299,7 @@
         <v>31</v>
       </c>
       <c r="C18">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D18" t="s">
         <v>32</v>
@@ -6313,7 +6313,7 @@
         <v>31</v>
       </c>
       <c r="C19">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D19" t="s">
         <v>32</v>
@@ -6327,7 +6327,7 @@
         <v>31</v>
       </c>
       <c r="C20">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D20" t="s">
         <v>32</v>
@@ -6341,7 +6341,7 @@
         <v>31</v>
       </c>
       <c r="C21">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D21" t="s">
         <v>32</v>
@@ -6355,7 +6355,7 @@
         <v>31</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="D22" t="s">
         <v>32</v>
@@ -6369,7 +6369,7 @@
         <v>31</v>
       </c>
       <c r="C23">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D23" t="s">
         <v>32</v>
@@ -6383,7 +6383,7 @@
         <v>31</v>
       </c>
       <c r="C24">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D24" t="s">
         <v>32</v>
@@ -6397,7 +6397,7 @@
         <v>31</v>
       </c>
       <c r="C25">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D25" t="s">
         <v>32</v>
@@ -6411,7 +6411,7 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="D26" t="s">
         <v>32</v>
@@ -6425,7 +6425,7 @@
         <v>31</v>
       </c>
       <c r="C27">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D27" t="s">
         <v>32</v>
@@ -6439,7 +6439,7 @@
         <v>31</v>
       </c>
       <c r="C28">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D28" t="s">
         <v>32</v>
@@ -6453,7 +6453,7 @@
         <v>31</v>
       </c>
       <c r="C29">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="D29" t="s">
         <v>32</v>
@@ -6467,7 +6467,7 @@
         <v>31</v>
       </c>
       <c r="C30">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D30" t="s">
         <v>32</v>
@@ -6481,7 +6481,7 @@
         <v>31</v>
       </c>
       <c r="C31">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D31" t="s">
         <v>32</v>
@@ -6495,7 +6495,7 @@
         <v>31</v>
       </c>
       <c r="C32">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D32" t="s">
         <v>32</v>
@@ -6509,7 +6509,7 @@
         <v>31</v>
       </c>
       <c r="C33">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D33" t="s">
         <v>32</v>
@@ -6523,7 +6523,7 @@
         <v>31</v>
       </c>
       <c r="C34">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D34" t="s">
         <v>32</v>
@@ -6537,7 +6537,7 @@
         <v>31</v>
       </c>
       <c r="C35">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D35" t="s">
         <v>32</v>
@@ -6551,7 +6551,7 @@
         <v>31</v>
       </c>
       <c r="C36">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D36" t="s">
         <v>32</v>
@@ -6565,7 +6565,7 @@
         <v>31</v>
       </c>
       <c r="C37">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="D37" t="s">
         <v>32</v>
@@ -6579,7 +6579,7 @@
         <v>31</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D38" t="s">
         <v>32</v>
@@ -6593,7 +6593,7 @@
         <v>31</v>
       </c>
       <c r="C39">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="D39" t="s">
         <v>32</v>
@@ -6607,7 +6607,7 @@
         <v>31</v>
       </c>
       <c r="C40">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="D40" t="s">
         <v>32</v>
@@ -6621,7 +6621,7 @@
         <v>31</v>
       </c>
       <c r="C41">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D41" t="s">
         <v>32</v>
@@ -6635,7 +6635,7 @@
         <v>31</v>
       </c>
       <c r="C42">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D42" t="s">
         <v>32</v>
@@ -6649,7 +6649,7 @@
         <v>31</v>
       </c>
       <c r="C43">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D43" t="s">
         <v>32</v>
@@ -6663,7 +6663,7 @@
         <v>31</v>
       </c>
       <c r="C44">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="D44" t="s">
         <v>32</v>
@@ -6677,7 +6677,7 @@
         <v>31</v>
       </c>
       <c r="C45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D45" t="s">
         <v>32</v>
@@ -6691,7 +6691,7 @@
         <v>31</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D46" t="s">
         <v>32</v>
@@ -6705,7 +6705,7 @@
         <v>31</v>
       </c>
       <c r="C47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D47" t="s">
         <v>32</v>
@@ -6719,7 +6719,7 @@
         <v>31</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D48" t="s">
         <v>32</v>
@@ -6733,7 +6733,7 @@
         <v>31</v>
       </c>
       <c r="C49">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="D49" t="s">
         <v>32</v>
@@ -6747,7 +6747,7 @@
         <v>31</v>
       </c>
       <c r="C50">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D50" t="s">
         <v>32</v>
@@ -6761,7 +6761,7 @@
         <v>31</v>
       </c>
       <c r="C51">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D51" t="s">
         <v>32</v>
@@ -6775,7 +6775,7 @@
         <v>31</v>
       </c>
       <c r="C52">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D52" t="s">
         <v>32</v>
@@ -6789,7 +6789,7 @@
         <v>31</v>
       </c>
       <c r="C53">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D53" t="s">
         <v>32</v>
@@ -6803,7 +6803,7 @@
         <v>31</v>
       </c>
       <c r="C54">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="D54" t="s">
         <v>32</v>
@@ -6817,7 +6817,7 @@
         <v>31</v>
       </c>
       <c r="C55">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D55" t="s">
         <v>32</v>
@@ -6831,7 +6831,7 @@
         <v>31</v>
       </c>
       <c r="C56">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D56" t="s">
         <v>32</v>
@@ -6845,7 +6845,7 @@
         <v>31</v>
       </c>
       <c r="C57">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D57" t="s">
         <v>32</v>
@@ -6859,7 +6859,7 @@
         <v>31</v>
       </c>
       <c r="C58">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="D58" t="s">
         <v>32</v>
@@ -6873,7 +6873,7 @@
         <v>31</v>
       </c>
       <c r="C59">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="D59" t="s">
         <v>32</v>
@@ -6901,7 +6901,7 @@
         <v>31</v>
       </c>
       <c r="C61">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="D61" t="s">
         <v>32</v>
@@ -6915,7 +6915,7 @@
         <v>31</v>
       </c>
       <c r="C62">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D62" t="s">
         <v>32</v>
@@ -6929,7 +6929,7 @@
         <v>31</v>
       </c>
       <c r="C63">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="D63" t="s">
         <v>32</v>
@@ -6943,7 +6943,7 @@
         <v>31</v>
       </c>
       <c r="C64">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D64" t="s">
         <v>32</v>
@@ -6957,7 +6957,7 @@
         <v>31</v>
       </c>
       <c r="C65">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D65" t="s">
         <v>32</v>
@@ -6971,7 +6971,7 @@
         <v>31</v>
       </c>
       <c r="C66">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="D66" t="s">
         <v>32</v>
@@ -6985,7 +6985,7 @@
         <v>31</v>
       </c>
       <c r="C67">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D67" t="s">
         <v>32</v>
@@ -6999,7 +6999,7 @@
         <v>31</v>
       </c>
       <c r="C68">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D68" t="s">
         <v>32</v>
@@ -7013,7 +7013,7 @@
         <v>31</v>
       </c>
       <c r="C69">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D69" t="s">
         <v>32</v>
@@ -7027,7 +7027,7 @@
         <v>31</v>
       </c>
       <c r="C70">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D70" t="s">
         <v>32</v>
@@ -7041,7 +7041,7 @@
         <v>31</v>
       </c>
       <c r="C71">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="D71" t="s">
         <v>32</v>
@@ -7055,7 +7055,7 @@
         <v>31</v>
       </c>
       <c r="C72">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="D72" t="s">
         <v>32</v>
@@ -7069,7 +7069,7 @@
         <v>31</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D73" t="s">
         <v>32</v>
@@ -7083,7 +7083,7 @@
         <v>31</v>
       </c>
       <c r="C74">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D74" t="s">
         <v>32</v>
@@ -7097,7 +7097,7 @@
         <v>31</v>
       </c>
       <c r="C75">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="D75" t="s">
         <v>32</v>
@@ -7111,7 +7111,7 @@
         <v>31</v>
       </c>
       <c r="C76">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="D76" t="s">
         <v>32</v>
@@ -7125,7 +7125,7 @@
         <v>31</v>
       </c>
       <c r="C77">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="D77" t="s">
         <v>32</v>
@@ -7139,7 +7139,7 @@
         <v>31</v>
       </c>
       <c r="C78">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D78" t="s">
         <v>32</v>
@@ -7153,7 +7153,7 @@
         <v>31</v>
       </c>
       <c r="C79">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D79" t="s">
         <v>32</v>
@@ -7167,7 +7167,7 @@
         <v>31</v>
       </c>
       <c r="C80">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D80" t="s">
         <v>32</v>
@@ -7181,7 +7181,7 @@
         <v>31</v>
       </c>
       <c r="C81">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D81" t="s">
         <v>32</v>
@@ -7195,7 +7195,7 @@
         <v>31</v>
       </c>
       <c r="C82">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="D82" t="s">
         <v>32</v>
@@ -7209,7 +7209,7 @@
         <v>31</v>
       </c>
       <c r="C83">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="D83" t="s">
         <v>32</v>
@@ -7237,7 +7237,7 @@
         <v>31</v>
       </c>
       <c r="C85">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="D85" t="s">
         <v>32</v>
@@ -7251,7 +7251,7 @@
         <v>31</v>
       </c>
       <c r="C86">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D86" t="s">
         <v>32</v>
@@ -7265,7 +7265,7 @@
         <v>31</v>
       </c>
       <c r="C87">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="D87" t="s">
         <v>32</v>
@@ -7279,7 +7279,7 @@
         <v>31</v>
       </c>
       <c r="C88">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D88" t="s">
         <v>32</v>
@@ -7293,7 +7293,7 @@
         <v>31</v>
       </c>
       <c r="C89">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="D89" t="s">
         <v>32</v>
@@ -7307,7 +7307,7 @@
         <v>31</v>
       </c>
       <c r="C90">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="D90" t="s">
         <v>32</v>
@@ -7321,7 +7321,7 @@
         <v>31</v>
       </c>
       <c r="C91">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D91" t="s">
         <v>32</v>
@@ -7335,7 +7335,7 @@
         <v>31</v>
       </c>
       <c r="C92">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D92" t="s">
         <v>32</v>
@@ -7349,7 +7349,7 @@
         <v>31</v>
       </c>
       <c r="C93">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D93" t="s">
         <v>32</v>
@@ -7363,7 +7363,7 @@
         <v>31</v>
       </c>
       <c r="C94">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D94" t="s">
         <v>32</v>
@@ -7377,7 +7377,7 @@
         <v>31</v>
       </c>
       <c r="C95">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D95" t="s">
         <v>32</v>
@@ -7391,7 +7391,7 @@
         <v>31</v>
       </c>
       <c r="C96">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D96" t="s">
         <v>32</v>
@@ -7405,7 +7405,7 @@
         <v>31</v>
       </c>
       <c r="C97">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D97" t="s">
         <v>32</v>
@@ -7419,7 +7419,7 @@
         <v>31</v>
       </c>
       <c r="C98">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D98" t="s">
         <v>32</v>
@@ -7433,7 +7433,7 @@
         <v>31</v>
       </c>
       <c r="C99">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="D99" t="s">
         <v>32</v>
@@ -7447,7 +7447,7 @@
         <v>31</v>
       </c>
       <c r="C100">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D100" t="s">
         <v>32</v>
@@ -7461,7 +7461,7 @@
         <v>31</v>
       </c>
       <c r="C101">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D101" t="s">
         <v>32</v>
@@ -7475,7 +7475,7 @@
         <v>31</v>
       </c>
       <c r="C102">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D102" t="s">
         <v>32</v>
@@ -7489,7 +7489,7 @@
         <v>31</v>
       </c>
       <c r="C103">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D103" t="s">
         <v>32</v>
@@ -7503,7 +7503,7 @@
         <v>31</v>
       </c>
       <c r="C104">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D104" t="s">
         <v>32</v>
@@ -7517,7 +7517,7 @@
         <v>31</v>
       </c>
       <c r="C105">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="D105" t="s">
         <v>32</v>
@@ -7531,7 +7531,7 @@
         <v>31</v>
       </c>
       <c r="C106">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D106" t="s">
         <v>32</v>
@@ -7545,7 +7545,7 @@
         <v>31</v>
       </c>
       <c r="C107">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="D107" t="s">
         <v>32</v>
@@ -7559,7 +7559,7 @@
         <v>31</v>
       </c>
       <c r="C108">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D108" t="s">
         <v>32</v>
@@ -7573,7 +7573,7 @@
         <v>31</v>
       </c>
       <c r="C109">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D109" t="s">
         <v>32</v>
@@ -7587,7 +7587,7 @@
         <v>31</v>
       </c>
       <c r="C110">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="D110" t="s">
         <v>32</v>
@@ -7601,7 +7601,7 @@
         <v>31</v>
       </c>
       <c r="C111">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D111" t="s">
         <v>32</v>
@@ -7615,7 +7615,7 @@
         <v>31</v>
       </c>
       <c r="C112">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D112" t="s">
         <v>32</v>
@@ -7629,7 +7629,7 @@
         <v>31</v>
       </c>
       <c r="C113">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="D113" t="s">
         <v>32</v>
@@ -7643,7 +7643,7 @@
         <v>31</v>
       </c>
       <c r="C114">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D114" t="s">
         <v>32</v>
@@ -7657,7 +7657,7 @@
         <v>31</v>
       </c>
       <c r="C115">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="D115" t="s">
         <v>32</v>
@@ -7671,7 +7671,7 @@
         <v>31</v>
       </c>
       <c r="C116">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D116" t="s">
         <v>32</v>
@@ -7685,7 +7685,7 @@
         <v>31</v>
       </c>
       <c r="C117">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D117" t="s">
         <v>32</v>
@@ -7699,7 +7699,7 @@
         <v>31</v>
       </c>
       <c r="C118">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="D118" t="s">
         <v>32</v>
@@ -7713,7 +7713,7 @@
         <v>31</v>
       </c>
       <c r="C119">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D119" t="s">
         <v>32</v>
@@ -7727,7 +7727,7 @@
         <v>31</v>
       </c>
       <c r="C120">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D120" t="s">
         <v>32</v>
@@ -7741,7 +7741,7 @@
         <v>31</v>
       </c>
       <c r="C121">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D121" t="s">
         <v>32</v>
@@ -7755,7 +7755,7 @@
         <v>31</v>
       </c>
       <c r="C122">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="D122" t="s">
         <v>32</v>
@@ -7769,7 +7769,7 @@
         <v>31</v>
       </c>
       <c r="C123">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="D123" t="s">
         <v>32</v>
@@ -7783,7 +7783,7 @@
         <v>31</v>
       </c>
       <c r="C124">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D124" t="s">
         <v>32</v>
@@ -7797,7 +7797,7 @@
         <v>31</v>
       </c>
       <c r="C125">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="D125" t="s">
         <v>32</v>
@@ -7811,7 +7811,7 @@
         <v>31</v>
       </c>
       <c r="C126">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="D126" t="s">
         <v>32</v>
@@ -7825,7 +7825,7 @@
         <v>31</v>
       </c>
       <c r="C127">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D127" t="s">
         <v>32</v>
@@ -7839,7 +7839,7 @@
         <v>31</v>
       </c>
       <c r="C128">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="D128" t="s">
         <v>32</v>
@@ -7853,7 +7853,7 @@
         <v>31</v>
       </c>
       <c r="C129">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D129" t="s">
         <v>32</v>
@@ -7867,7 +7867,7 @@
         <v>31</v>
       </c>
       <c r="C130">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D130" t="s">
         <v>32</v>
@@ -7881,7 +7881,7 @@
         <v>31</v>
       </c>
       <c r="C131">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D131" t="s">
         <v>32</v>
@@ -7895,7 +7895,7 @@
         <v>31</v>
       </c>
       <c r="C132">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="D132" t="s">
         <v>32</v>
@@ -7909,7 +7909,7 @@
         <v>31</v>
       </c>
       <c r="C133">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D133" t="s">
         <v>32</v>
@@ -7923,7 +7923,7 @@
         <v>31</v>
       </c>
       <c r="C134">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="D134" t="s">
         <v>32</v>
@@ -7937,7 +7937,7 @@
         <v>31</v>
       </c>
       <c r="C135">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="D135" t="s">
         <v>32</v>
@@ -7951,7 +7951,7 @@
         <v>31</v>
       </c>
       <c r="C136">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="D136" t="s">
         <v>32</v>
@@ -7965,7 +7965,7 @@
         <v>31</v>
       </c>
       <c r="C137">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="D137" t="s">
         <v>32</v>
@@ -7979,7 +7979,7 @@
         <v>31</v>
       </c>
       <c r="C138">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D138" t="s">
         <v>32</v>
@@ -8007,7 +8007,7 @@
         <v>31</v>
       </c>
       <c r="C140">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D140" t="s">
         <v>32</v>
@@ -8021,7 +8021,7 @@
         <v>31</v>
       </c>
       <c r="C141">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="D141" t="s">
         <v>32</v>
@@ -8035,7 +8035,7 @@
         <v>31</v>
       </c>
       <c r="C142">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D142" t="s">
         <v>32</v>
@@ -8049,7 +8049,7 @@
         <v>31</v>
       </c>
       <c r="C143">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D143" t="s">
         <v>32</v>
@@ -8063,7 +8063,7 @@
         <v>31</v>
       </c>
       <c r="C144">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D144" t="s">
         <v>32</v>
@@ -8091,7 +8091,7 @@
         <v>31</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D146" t="s">
         <v>32</v>
@@ -8105,7 +8105,7 @@
         <v>31</v>
       </c>
       <c r="C147">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D147" t="s">
         <v>32</v>
@@ -8119,7 +8119,7 @@
         <v>31</v>
       </c>
       <c r="C148">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D148" t="s">
         <v>32</v>
@@ -8133,7 +8133,7 @@
         <v>31</v>
       </c>
       <c r="C149">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D149" t="s">
         <v>32</v>
@@ -8147,7 +8147,7 @@
         <v>31</v>
       </c>
       <c r="C150">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D150" t="s">
         <v>32</v>
@@ -8161,7 +8161,7 @@
         <v>31</v>
       </c>
       <c r="C151">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="D151" t="s">
         <v>32</v>
@@ -8175,7 +8175,7 @@
         <v>31</v>
       </c>
       <c r="C152">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D152" t="s">
         <v>32</v>
@@ -8189,7 +8189,7 @@
         <v>31</v>
       </c>
       <c r="C153">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="D153" t="s">
         <v>32</v>
@@ -8203,7 +8203,7 @@
         <v>31</v>
       </c>
       <c r="C154">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D154" t="s">
         <v>32</v>
@@ -8217,7 +8217,7 @@
         <v>31</v>
       </c>
       <c r="C155">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D155" t="s">
         <v>32</v>
@@ -8231,7 +8231,7 @@
         <v>31</v>
       </c>
       <c r="C156">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="D156" t="s">
         <v>32</v>
@@ -8245,7 +8245,7 @@
         <v>31</v>
       </c>
       <c r="C157">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="D157" t="s">
         <v>32</v>
@@ -8259,7 +8259,7 @@
         <v>31</v>
       </c>
       <c r="C158">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D158" t="s">
         <v>32</v>
@@ -8273,7 +8273,7 @@
         <v>31</v>
       </c>
       <c r="C159">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="D159" t="s">
         <v>32</v>
@@ -8287,7 +8287,7 @@
         <v>31</v>
       </c>
       <c r="C160">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="D160" t="s">
         <v>32</v>
@@ -8301,7 +8301,7 @@
         <v>31</v>
       </c>
       <c r="C161">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D161" t="s">
         <v>32</v>
@@ -8315,7 +8315,7 @@
         <v>31</v>
       </c>
       <c r="C162">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D162" t="s">
         <v>32</v>
@@ -8329,7 +8329,7 @@
         <v>31</v>
       </c>
       <c r="C163">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D163" t="s">
         <v>32</v>
@@ -8343,7 +8343,7 @@
         <v>31</v>
       </c>
       <c r="C164">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D164" t="s">
         <v>32</v>
@@ -8357,7 +8357,7 @@
         <v>31</v>
       </c>
       <c r="C165">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D165" t="s">
         <v>32</v>
@@ -8371,7 +8371,7 @@
         <v>31</v>
       </c>
       <c r="C166">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="D166" t="s">
         <v>32</v>
@@ -8385,7 +8385,7 @@
         <v>31</v>
       </c>
       <c r="C167">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D167" t="s">
         <v>32</v>
@@ -8399,7 +8399,7 @@
         <v>31</v>
       </c>
       <c r="C168">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D168" t="s">
         <v>32</v>
@@ -8413,7 +8413,7 @@
         <v>31</v>
       </c>
       <c r="C169">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D169" t="s">
         <v>32</v>
@@ -8427,7 +8427,7 @@
         <v>31</v>
       </c>
       <c r="C170">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D170" t="s">
         <v>32</v>
@@ -8441,7 +8441,7 @@
         <v>31</v>
       </c>
       <c r="C171">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D171" t="s">
         <v>32</v>
@@ -8455,7 +8455,7 @@
         <v>31</v>
       </c>
       <c r="C172">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D172" t="s">
         <v>32</v>
@@ -8469,7 +8469,7 @@
         <v>31</v>
       </c>
       <c r="C173">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D173" t="s">
         <v>32</v>
@@ -8483,7 +8483,7 @@
         <v>31</v>
       </c>
       <c r="C174">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D174" t="s">
         <v>32</v>
@@ -8497,7 +8497,7 @@
         <v>31</v>
       </c>
       <c r="C175">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D175" t="s">
         <v>32</v>
@@ -8511,7 +8511,7 @@
         <v>31</v>
       </c>
       <c r="C176">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D176" t="s">
         <v>32</v>
@@ -8525,7 +8525,7 @@
         <v>31</v>
       </c>
       <c r="C177">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="D177" t="s">
         <v>32</v>
@@ -8539,7 +8539,7 @@
         <v>31</v>
       </c>
       <c r="C178">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D178" t="s">
         <v>32</v>
@@ -8553,7 +8553,7 @@
         <v>31</v>
       </c>
       <c r="C179">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D179" t="s">
         <v>32</v>
@@ -8567,7 +8567,7 @@
         <v>31</v>
       </c>
       <c r="C180">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D180" t="s">
         <v>32</v>
@@ -8581,7 +8581,7 @@
         <v>31</v>
       </c>
       <c r="C181">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D181" t="s">
         <v>32</v>
@@ -8595,7 +8595,7 @@
         <v>31</v>
       </c>
       <c r="C182">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="D182" t="s">
         <v>32</v>
@@ -8623,7 +8623,7 @@
         <v>31</v>
       </c>
       <c r="C184">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D184" t="s">
         <v>32</v>
@@ -8637,7 +8637,7 @@
         <v>31</v>
       </c>
       <c r="C185">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D185" t="s">
         <v>32</v>
@@ -8651,7 +8651,7 @@
         <v>31</v>
       </c>
       <c r="C186">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="D186" t="s">
         <v>32</v>
@@ -8665,7 +8665,7 @@
         <v>31</v>
       </c>
       <c r="C187">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D187" t="s">
         <v>32</v>
@@ -8679,7 +8679,7 @@
         <v>31</v>
       </c>
       <c r="C188">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D188" t="s">
         <v>32</v>
@@ -8693,7 +8693,7 @@
         <v>31</v>
       </c>
       <c r="C189">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D189" t="s">
         <v>32</v>
@@ -8707,7 +8707,7 @@
         <v>31</v>
       </c>
       <c r="C190">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="D190" t="s">
         <v>32</v>
@@ -8721,7 +8721,7 @@
         <v>31</v>
       </c>
       <c r="C191">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D191" t="s">
         <v>32</v>
@@ -8735,7 +8735,7 @@
         <v>31</v>
       </c>
       <c r="C192">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="D192" t="s">
         <v>32</v>
@@ -8749,7 +8749,7 @@
         <v>31</v>
       </c>
       <c r="C193">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="D193" t="s">
         <v>32</v>
@@ -8763,7 +8763,7 @@
         <v>31</v>
       </c>
       <c r="C194">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D194" t="s">
         <v>32</v>
@@ -8777,7 +8777,7 @@
         <v>31</v>
       </c>
       <c r="C195">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="D195" t="s">
         <v>32</v>
@@ -8791,7 +8791,7 @@
         <v>31</v>
       </c>
       <c r="C196">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D196" t="s">
         <v>32</v>
@@ -8805,7 +8805,7 @@
         <v>31</v>
       </c>
       <c r="C197">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D197" t="s">
         <v>32</v>
@@ -8819,7 +8819,7 @@
         <v>31</v>
       </c>
       <c r="C198">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D198" t="s">
         <v>32</v>
@@ -8833,7 +8833,7 @@
         <v>31</v>
       </c>
       <c r="C199">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D199" t="s">
         <v>32</v>
@@ -8847,7 +8847,7 @@
         <v>31</v>
       </c>
       <c r="C200">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D200" t="s">
         <v>32</v>
@@ -8861,7 +8861,7 @@
         <v>31</v>
       </c>
       <c r="C201">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D201" t="s">
         <v>32</v>
@@ -8875,7 +8875,7 @@
         <v>31</v>
       </c>
       <c r="C202">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D202" t="s">
         <v>32</v>
@@ -8889,7 +8889,7 @@
         <v>31</v>
       </c>
       <c r="C203">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D203" t="s">
         <v>32</v>
@@ -8903,7 +8903,7 @@
         <v>31</v>
       </c>
       <c r="C204">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D204" t="s">
         <v>32</v>
@@ -8917,7 +8917,7 @@
         <v>31</v>
       </c>
       <c r="C205">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D205" t="s">
         <v>32</v>
@@ -8931,7 +8931,7 @@
         <v>31</v>
       </c>
       <c r="C206">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D206" t="s">
         <v>32</v>
@@ -8945,7 +8945,7 @@
         <v>31</v>
       </c>
       <c r="C207">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D207" t="s">
         <v>32</v>
@@ -8959,7 +8959,7 @@
         <v>31</v>
       </c>
       <c r="C208">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D208" t="s">
         <v>32</v>
@@ -8973,7 +8973,7 @@
         <v>31</v>
       </c>
       <c r="C209">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D209" t="s">
         <v>32</v>
@@ -8987,7 +8987,7 @@
         <v>31</v>
       </c>
       <c r="C210">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D210" t="s">
         <v>32</v>
@@ -9001,7 +9001,7 @@
         <v>31</v>
       </c>
       <c r="C211">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D211" t="s">
         <v>32</v>
@@ -9015,7 +9015,7 @@
         <v>31</v>
       </c>
       <c r="C212">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D212" t="s">
         <v>32</v>
@@ -9029,7 +9029,7 @@
         <v>31</v>
       </c>
       <c r="C213">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D213" t="s">
         <v>32</v>
@@ -9043,7 +9043,7 @@
         <v>31</v>
       </c>
       <c r="C214">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D214" t="s">
         <v>32</v>
@@ -9057,7 +9057,7 @@
         <v>31</v>
       </c>
       <c r="C215">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D215" t="s">
         <v>32</v>
@@ -9071,7 +9071,7 @@
         <v>31</v>
       </c>
       <c r="C216">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D216" t="s">
         <v>32</v>
@@ -9085,7 +9085,7 @@
         <v>31</v>
       </c>
       <c r="C217">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="D217" t="s">
         <v>32</v>
@@ -9099,7 +9099,7 @@
         <v>31</v>
       </c>
       <c r="C218">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D218" t="s">
         <v>32</v>
@@ -9113,7 +9113,7 @@
         <v>31</v>
       </c>
       <c r="C219">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D219" t="s">
         <v>32</v>
@@ -9127,7 +9127,7 @@
         <v>31</v>
       </c>
       <c r="C220">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="D220" t="s">
         <v>32</v>
@@ -9141,7 +9141,7 @@
         <v>31</v>
       </c>
       <c r="C221">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D221" t="s">
         <v>32</v>
@@ -9155,7 +9155,7 @@
         <v>31</v>
       </c>
       <c r="C222">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D222" t="s">
         <v>32</v>
@@ -9169,7 +9169,7 @@
         <v>31</v>
       </c>
       <c r="C223">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D223" t="s">
         <v>32</v>
@@ -9183,7 +9183,7 @@
         <v>31</v>
       </c>
       <c r="C224">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D224" t="s">
         <v>32</v>
@@ -9197,7 +9197,7 @@
         <v>31</v>
       </c>
       <c r="C225">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="D225" t="s">
         <v>32</v>
@@ -9211,7 +9211,7 @@
         <v>31</v>
       </c>
       <c r="C226">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D226" t="s">
         <v>32</v>
@@ -9225,7 +9225,7 @@
         <v>31</v>
       </c>
       <c r="C227">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="D227" t="s">
         <v>32</v>
@@ -9239,7 +9239,7 @@
         <v>31</v>
       </c>
       <c r="C228">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D228" t="s">
         <v>32</v>
@@ -9253,7 +9253,7 @@
         <v>31</v>
       </c>
       <c r="C229">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D229" t="s">
         <v>32</v>
@@ -9267,7 +9267,7 @@
         <v>31</v>
       </c>
       <c r="C230">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D230" t="s">
         <v>32</v>
@@ -9281,7 +9281,7 @@
         <v>31</v>
       </c>
       <c r="C231">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D231" t="s">
         <v>32</v>
@@ -9295,7 +9295,7 @@
         <v>31</v>
       </c>
       <c r="C232">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D232" t="s">
         <v>32</v>
@@ -9309,7 +9309,7 @@
         <v>31</v>
       </c>
       <c r="C233">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D233" t="s">
         <v>32</v>
@@ -9323,7 +9323,7 @@
         <v>31</v>
       </c>
       <c r="C234">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="D234" t="s">
         <v>32</v>
@@ -9337,7 +9337,7 @@
         <v>31</v>
       </c>
       <c r="C235">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="D235" t="s">
         <v>32</v>
@@ -9351,7 +9351,7 @@
         <v>31</v>
       </c>
       <c r="C236">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D236" t="s">
         <v>32</v>
@@ -9365,7 +9365,7 @@
         <v>31</v>
       </c>
       <c r="C237">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="D237" t="s">
         <v>32</v>
@@ -9379,7 +9379,7 @@
         <v>31</v>
       </c>
       <c r="C238">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D238" t="s">
         <v>32</v>
@@ -9393,7 +9393,7 @@
         <v>31</v>
       </c>
       <c r="C239">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D239" t="s">
         <v>32</v>
@@ -9407,7 +9407,7 @@
         <v>31</v>
       </c>
       <c r="C240">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="D240" t="s">
         <v>32</v>
@@ -9421,7 +9421,7 @@
         <v>31</v>
       </c>
       <c r="C241">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="D241" t="s">
         <v>32</v>
@@ -9435,7 +9435,7 @@
         <v>31</v>
       </c>
       <c r="C242">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D242" t="s">
         <v>32</v>
@@ -9449,7 +9449,7 @@
         <v>31</v>
       </c>
       <c r="C243">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="D243" t="s">
         <v>32</v>
@@ -9463,7 +9463,7 @@
         <v>31</v>
       </c>
       <c r="C244">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="D244" t="s">
         <v>32</v>
@@ -9477,7 +9477,7 @@
         <v>31</v>
       </c>
       <c r="C245">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D245" t="s">
         <v>32</v>
@@ -9491,7 +9491,7 @@
         <v>31</v>
       </c>
       <c r="C246">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D246" t="s">
         <v>32</v>
@@ -9505,7 +9505,7 @@
         <v>31</v>
       </c>
       <c r="C247">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D247" t="s">
         <v>32</v>
@@ -9519,7 +9519,7 @@
         <v>31</v>
       </c>
       <c r="C248">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D248" t="s">
         <v>32</v>
@@ -9533,7 +9533,7 @@
         <v>31</v>
       </c>
       <c r="C249">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="D249" t="s">
         <v>32</v>
@@ -9547,7 +9547,7 @@
         <v>31</v>
       </c>
       <c r="C250">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D250" t="s">
         <v>32</v>
@@ -9561,7 +9561,7 @@
         <v>31</v>
       </c>
       <c r="C251">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="D251" t="s">
         <v>32</v>
@@ -9575,7 +9575,7 @@
         <v>31</v>
       </c>
       <c r="C252">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D252" t="s">
         <v>32</v>
@@ -9589,7 +9589,7 @@
         <v>31</v>
       </c>
       <c r="C253">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D253" t="s">
         <v>32</v>
@@ -9603,7 +9603,7 @@
         <v>31</v>
       </c>
       <c r="C254">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="D254" t="s">
         <v>32</v>
@@ -9617,7 +9617,7 @@
         <v>31</v>
       </c>
       <c r="C255">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D255" t="s">
         <v>32</v>
@@ -9631,7 +9631,7 @@
         <v>31</v>
       </c>
       <c r="C256">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D256" t="s">
         <v>32</v>
@@ -9645,7 +9645,7 @@
         <v>31</v>
       </c>
       <c r="C257">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D257" t="s">
         <v>32</v>
@@ -9659,7 +9659,7 @@
         <v>31</v>
       </c>
       <c r="C258">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D258" t="s">
         <v>32</v>
@@ -9673,7 +9673,7 @@
         <v>31</v>
       </c>
       <c r="C259">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D259" t="s">
         <v>32</v>
@@ -9687,7 +9687,7 @@
         <v>31</v>
       </c>
       <c r="C260">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D260" t="s">
         <v>32</v>
@@ -9701,7 +9701,7 @@
         <v>31</v>
       </c>
       <c r="C261">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D261" t="s">
         <v>32</v>
@@ -9715,7 +9715,7 @@
         <v>31</v>
       </c>
       <c r="C262">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D262" t="s">
         <v>32</v>
@@ -9729,7 +9729,7 @@
         <v>31</v>
       </c>
       <c r="C263">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D263" t="s">
         <v>32</v>
@@ -9743,7 +9743,7 @@
         <v>31</v>
       </c>
       <c r="C264">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="D264" t="s">
         <v>32</v>
@@ -9757,7 +9757,7 @@
         <v>31</v>
       </c>
       <c r="C265">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D265" t="s">
         <v>32</v>
@@ -9771,7 +9771,7 @@
         <v>31</v>
       </c>
       <c r="C266">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="D266" t="s">
         <v>32</v>
@@ -9785,7 +9785,7 @@
         <v>31</v>
       </c>
       <c r="C267">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D267" t="s">
         <v>32</v>
@@ -9799,7 +9799,7 @@
         <v>31</v>
       </c>
       <c r="C268">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="D268" t="s">
         <v>32</v>
@@ -9813,7 +9813,7 @@
         <v>31</v>
       </c>
       <c r="C269">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D269" t="s">
         <v>32</v>
@@ -9827,7 +9827,7 @@
         <v>31</v>
       </c>
       <c r="C270">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D270" t="s">
         <v>32</v>
@@ -9841,7 +9841,7 @@
         <v>31</v>
       </c>
       <c r="C271">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D271" t="s">
         <v>32</v>
@@ -9855,7 +9855,7 @@
         <v>31</v>
       </c>
       <c r="C272">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D272" t="s">
         <v>32</v>
@@ -9869,7 +9869,7 @@
         <v>31</v>
       </c>
       <c r="C273">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D273" t="s">
         <v>32</v>
@@ -9883,7 +9883,7 @@
         <v>31</v>
       </c>
       <c r="C274">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D274" t="s">
         <v>32</v>
@@ -9897,7 +9897,7 @@
         <v>31</v>
       </c>
       <c r="C275">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="D275" t="s">
         <v>32</v>
@@ -9911,7 +9911,7 @@
         <v>31</v>
       </c>
       <c r="C276">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D276" t="s">
         <v>32</v>
@@ -9925,7 +9925,7 @@
         <v>31</v>
       </c>
       <c r="C277">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D277" t="s">
         <v>32</v>
@@ -9939,7 +9939,7 @@
         <v>31</v>
       </c>
       <c r="C278">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D278" t="s">
         <v>32</v>
@@ -9953,7 +9953,7 @@
         <v>31</v>
       </c>
       <c r="C279">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D279" t="s">
         <v>32</v>
@@ -9967,7 +9967,7 @@
         <v>31</v>
       </c>
       <c r="C280">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="D280" t="s">
         <v>32</v>
@@ -9981,7 +9981,7 @@
         <v>31</v>
       </c>
       <c r="C281">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D281" t="s">
         <v>32</v>
@@ -9995,7 +9995,7 @@
         <v>31</v>
       </c>
       <c r="C282">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D282" t="s">
         <v>32</v>
@@ -10009,7 +10009,7 @@
         <v>31</v>
       </c>
       <c r="C283">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D283" t="s">
         <v>32</v>
@@ -10023,7 +10023,7 @@
         <v>31</v>
       </c>
       <c r="C284">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D284" t="s">
         <v>32</v>
@@ -10037,7 +10037,7 @@
         <v>31</v>
       </c>
       <c r="C285">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D285" t="s">
         <v>32</v>
@@ -10051,7 +10051,7 @@
         <v>31</v>
       </c>
       <c r="C286">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D286" t="s">
         <v>32</v>
@@ -10065,7 +10065,7 @@
         <v>31</v>
       </c>
       <c r="C287">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="D287" t="s">
         <v>32</v>
@@ -10079,7 +10079,7 @@
         <v>31</v>
       </c>
       <c r="C288">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D288" t="s">
         <v>32</v>
@@ -10093,7 +10093,7 @@
         <v>31</v>
       </c>
       <c r="C289">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="D289" t="s">
         <v>32</v>
@@ -10107,7 +10107,7 @@
         <v>31</v>
       </c>
       <c r="C290">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D290" t="s">
         <v>32</v>
@@ -10121,7 +10121,7 @@
         <v>31</v>
       </c>
       <c r="C291">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D291" t="s">
         <v>32</v>
@@ -10135,7 +10135,7 @@
         <v>31</v>
       </c>
       <c r="C292">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D292" t="s">
         <v>32</v>
@@ -10149,7 +10149,7 @@
         <v>31</v>
       </c>
       <c r="C293">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D293" t="s">
         <v>32</v>
@@ -10163,7 +10163,7 @@
         <v>31</v>
       </c>
       <c r="C294">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D294" t="s">
         <v>32</v>
@@ -10177,7 +10177,7 @@
         <v>31</v>
       </c>
       <c r="C295">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="D295" t="s">
         <v>32</v>
@@ -10191,7 +10191,7 @@
         <v>31</v>
       </c>
       <c r="C296">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D296" t="s">
         <v>32</v>
@@ -10205,7 +10205,7 @@
         <v>31</v>
       </c>
       <c r="C297">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D297" t="s">
         <v>32</v>
@@ -10219,7 +10219,7 @@
         <v>31</v>
       </c>
       <c r="C298">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D298" t="s">
         <v>32</v>
@@ -10233,7 +10233,7 @@
         <v>31</v>
       </c>
       <c r="C299">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D299" t="s">
         <v>32</v>
@@ -10247,7 +10247,7 @@
         <v>31</v>
       </c>
       <c r="C300">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D300" t="s">
         <v>32</v>
@@ -10261,7 +10261,7 @@
         <v>31</v>
       </c>
       <c r="C301">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D301" t="s">
         <v>32</v>
@@ -10275,7 +10275,7 @@
         <v>31</v>
       </c>
       <c r="C302">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="D302" t="s">
         <v>32</v>
@@ -10289,7 +10289,7 @@
         <v>31</v>
       </c>
       <c r="C303">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D303" t="s">
         <v>32</v>
@@ -10303,7 +10303,7 @@
         <v>31</v>
       </c>
       <c r="C304">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D304" t="s">
         <v>32</v>
@@ -10317,7 +10317,7 @@
         <v>31</v>
       </c>
       <c r="C305">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="D305" t="s">
         <v>32</v>
@@ -10331,7 +10331,7 @@
         <v>31</v>
       </c>
       <c r="C306">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D306" t="s">
         <v>32</v>
@@ -10345,7 +10345,7 @@
         <v>31</v>
       </c>
       <c r="C307">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D307" t="s">
         <v>32</v>
@@ -10359,7 +10359,7 @@
         <v>31</v>
       </c>
       <c r="C308">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="D308" t="s">
         <v>32</v>
@@ -10373,7 +10373,7 @@
         <v>31</v>
       </c>
       <c r="C309">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="D309" t="s">
         <v>32</v>
@@ -10387,7 +10387,7 @@
         <v>31</v>
       </c>
       <c r="C310">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D310" t="s">
         <v>32</v>
@@ -10401,7 +10401,7 @@
         <v>31</v>
       </c>
       <c r="C311">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D311" t="s">
         <v>32</v>
@@ -10415,7 +10415,7 @@
         <v>31</v>
       </c>
       <c r="C312">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="D312" t="s">
         <v>32</v>
@@ -10429,7 +10429,7 @@
         <v>31</v>
       </c>
       <c r="C313">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="D313" t="s">
         <v>32</v>
@@ -10443,7 +10443,7 @@
         <v>31</v>
       </c>
       <c r="C314">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="D314" t="s">
         <v>32</v>
@@ -10457,7 +10457,7 @@
         <v>31</v>
       </c>
       <c r="C315">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D315" t="s">
         <v>32</v>
@@ -10471,7 +10471,7 @@
         <v>31</v>
       </c>
       <c r="C316">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D316" t="s">
         <v>32</v>
@@ -10485,7 +10485,7 @@
         <v>31</v>
       </c>
       <c r="C317">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D317" t="s">
         <v>32</v>
@@ -10499,7 +10499,7 @@
         <v>31</v>
       </c>
       <c r="C318">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D318" t="s">
         <v>32</v>
@@ -10513,7 +10513,7 @@
         <v>31</v>
       </c>
       <c r="C319">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D319" t="s">
         <v>32</v>
@@ -10527,7 +10527,7 @@
         <v>31</v>
       </c>
       <c r="C320">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D320" t="s">
         <v>32</v>
@@ -10541,7 +10541,7 @@
         <v>31</v>
       </c>
       <c r="C321">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D321" t="s">
         <v>32</v>
@@ -10555,7 +10555,7 @@
         <v>31</v>
       </c>
       <c r="C322">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="D322" t="s">
         <v>32</v>
@@ -10569,7 +10569,7 @@
         <v>31</v>
       </c>
       <c r="C323">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="D323" t="s">
         <v>32</v>
@@ -10583,7 +10583,7 @@
         <v>31</v>
       </c>
       <c r="C324">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D324" t="s">
         <v>32</v>
@@ -10597,7 +10597,7 @@
         <v>31</v>
       </c>
       <c r="C325">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="D325" t="s">
         <v>32</v>
@@ -10611,7 +10611,7 @@
         <v>31</v>
       </c>
       <c r="C326">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D326" t="s">
         <v>32</v>
@@ -10625,7 +10625,7 @@
         <v>31</v>
       </c>
       <c r="C327">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D327" t="s">
         <v>32</v>
@@ -10639,7 +10639,7 @@
         <v>31</v>
       </c>
       <c r="C328">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D328" t="s">
         <v>32</v>
@@ -10653,7 +10653,7 @@
         <v>31</v>
       </c>
       <c r="C329">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D329" t="s">
         <v>32</v>
@@ -10667,7 +10667,7 @@
         <v>31</v>
       </c>
       <c r="C330">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="D330" t="s">
         <v>32</v>
@@ -10681,7 +10681,7 @@
         <v>31</v>
       </c>
       <c r="C331">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D331" t="s">
         <v>32</v>
@@ -10695,7 +10695,7 @@
         <v>31</v>
       </c>
       <c r="C332">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="D332" t="s">
         <v>32</v>
@@ -10709,7 +10709,7 @@
         <v>31</v>
       </c>
       <c r="C333">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D333" t="s">
         <v>32</v>
@@ -10723,7 +10723,7 @@
         <v>31</v>
       </c>
       <c r="C334">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D334" t="s">
         <v>32</v>
@@ -10737,7 +10737,7 @@
         <v>31</v>
       </c>
       <c r="C335">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D335" t="s">
         <v>32</v>
@@ -10751,7 +10751,7 @@
         <v>31</v>
       </c>
       <c r="C336">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D336" t="s">
         <v>32</v>
@@ -10765,7 +10765,7 @@
         <v>31</v>
       </c>
       <c r="C337">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D337" t="s">
         <v>32</v>
@@ -10779,7 +10779,7 @@
         <v>31</v>
       </c>
       <c r="C338">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D338" t="s">
         <v>32</v>
@@ -10793,7 +10793,7 @@
         <v>31</v>
       </c>
       <c r="C339">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D339" t="s">
         <v>32</v>
@@ -10807,7 +10807,7 @@
         <v>31</v>
       </c>
       <c r="C340">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D340" t="s">
         <v>32</v>
@@ -10821,7 +10821,7 @@
         <v>31</v>
       </c>
       <c r="C341">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D341" t="s">
         <v>32</v>
@@ -10835,7 +10835,7 @@
         <v>31</v>
       </c>
       <c r="C342">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D342" t="s">
         <v>32</v>
@@ -10849,7 +10849,7 @@
         <v>31</v>
       </c>
       <c r="C343">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D343" t="s">
         <v>32</v>
@@ -10863,7 +10863,7 @@
         <v>31</v>
       </c>
       <c r="C344">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="D344" t="s">
         <v>32</v>
@@ -10877,7 +10877,7 @@
         <v>31</v>
       </c>
       <c r="C345">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="D345" t="s">
         <v>32</v>
@@ -10891,7 +10891,7 @@
         <v>31</v>
       </c>
       <c r="C346">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D346" t="s">
         <v>32</v>
@@ -10905,7 +10905,7 @@
         <v>31</v>
       </c>
       <c r="C347">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D347" t="s">
         <v>32</v>
@@ -10919,7 +10919,7 @@
         <v>31</v>
       </c>
       <c r="C348">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="D348" t="s">
         <v>32</v>
@@ -10933,7 +10933,7 @@
         <v>31</v>
       </c>
       <c r="C349">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="D349" t="s">
         <v>32</v>
@@ -10947,7 +10947,7 @@
         <v>31</v>
       </c>
       <c r="C350">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D350" t="s">
         <v>32</v>
@@ -10961,7 +10961,7 @@
         <v>31</v>
       </c>
       <c r="C351">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D351" t="s">
         <v>32</v>
@@ -10975,7 +10975,7 @@
         <v>31</v>
       </c>
       <c r="C352">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D352" t="s">
         <v>32</v>
@@ -10989,7 +10989,7 @@
         <v>31</v>
       </c>
       <c r="C353">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D353" t="s">
         <v>32</v>
@@ -11003,7 +11003,7 @@
         <v>31</v>
       </c>
       <c r="C354">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D354" t="s">
         <v>32</v>
@@ -11017,7 +11017,7 @@
         <v>31</v>
       </c>
       <c r="C355">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="D355" t="s">
         <v>32</v>
@@ -11031,7 +11031,7 @@
         <v>31</v>
       </c>
       <c r="C356">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="D356" t="s">
         <v>32</v>
@@ -11045,7 +11045,7 @@
         <v>31</v>
       </c>
       <c r="C357">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D357" t="s">
         <v>32</v>
@@ -11059,7 +11059,7 @@
         <v>31</v>
       </c>
       <c r="C358">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D358" t="s">
         <v>32</v>
@@ -11073,7 +11073,7 @@
         <v>31</v>
       </c>
       <c r="C359">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D359" t="s">
         <v>32</v>
@@ -11087,7 +11087,7 @@
         <v>31</v>
       </c>
       <c r="C360">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="D360" t="s">
         <v>32</v>
@@ -11101,7 +11101,7 @@
         <v>31</v>
       </c>
       <c r="C361">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D361" t="s">
         <v>32</v>
@@ -11115,7 +11115,7 @@
         <v>31</v>
       </c>
       <c r="C362">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D362" t="s">
         <v>32</v>
@@ -11129,7 +11129,7 @@
         <v>31</v>
       </c>
       <c r="C363">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D363" t="s">
         <v>32</v>
@@ -11143,7 +11143,7 @@
         <v>31</v>
       </c>
       <c r="C364">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D364" t="s">
         <v>32</v>
@@ -11157,7 +11157,7 @@
         <v>31</v>
       </c>
       <c r="C365">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="D365" t="s">
         <v>32</v>
@@ -11171,7 +11171,7 @@
         <v>31</v>
       </c>
       <c r="C366">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D366" t="s">
         <v>32</v>
@@ -11185,7 +11185,7 @@
         <v>31</v>
       </c>
       <c r="C367">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D367" t="s">
         <v>32</v>
@@ -11199,7 +11199,7 @@
         <v>31</v>
       </c>
       <c r="C368">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D368" t="s">
         <v>32</v>
@@ -11213,7 +11213,7 @@
         <v>31</v>
       </c>
       <c r="C369">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="D369" t="s">
         <v>32</v>
@@ -11227,7 +11227,7 @@
         <v>31</v>
       </c>
       <c r="C370">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="D370" t="s">
         <v>32</v>
@@ -11241,7 +11241,7 @@
         <v>31</v>
       </c>
       <c r="C371">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D371" t="s">
         <v>32</v>
@@ -11255,7 +11255,7 @@
         <v>31</v>
       </c>
       <c r="C372">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D372" t="s">
         <v>32</v>
@@ -11269,7 +11269,7 @@
         <v>31</v>
       </c>
       <c r="C373">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D373" t="s">
         <v>32</v>
@@ -11283,7 +11283,7 @@
         <v>31</v>
       </c>
       <c r="C374">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D374" t="s">
         <v>32</v>
@@ -11297,7 +11297,7 @@
         <v>31</v>
       </c>
       <c r="C375">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D375" t="s">
         <v>32</v>
@@ -11311,7 +11311,7 @@
         <v>31</v>
       </c>
       <c r="C376">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D376" t="s">
         <v>32</v>
@@ -11325,7 +11325,7 @@
         <v>31</v>
       </c>
       <c r="C377">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D377" t="s">
         <v>32</v>
@@ -11339,7 +11339,7 @@
         <v>31</v>
       </c>
       <c r="C378">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D378" t="s">
         <v>32</v>
@@ -11353,7 +11353,7 @@
         <v>31</v>
       </c>
       <c r="C379">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D379" t="s">
         <v>32</v>
@@ -11367,7 +11367,7 @@
         <v>31</v>
       </c>
       <c r="C380">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D380" t="s">
         <v>32</v>
@@ -11381,7 +11381,7 @@
         <v>31</v>
       </c>
       <c r="C381">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="D381" t="s">
         <v>32</v>
@@ -11395,7 +11395,7 @@
         <v>31</v>
       </c>
       <c r="C382">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="D382" t="s">
         <v>32</v>
@@ -11409,7 +11409,7 @@
         <v>31</v>
       </c>
       <c r="C383">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D383" t="s">
         <v>32</v>
@@ -11423,7 +11423,7 @@
         <v>31</v>
       </c>
       <c r="C384">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D384" t="s">
         <v>32</v>
@@ -11437,7 +11437,7 @@
         <v>31</v>
       </c>
       <c r="C385">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="D385" t="s">
         <v>32</v>
@@ -11451,7 +11451,7 @@
         <v>31</v>
       </c>
       <c r="C386">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D386" t="s">
         <v>32</v>
@@ -11465,7 +11465,7 @@
         <v>31</v>
       </c>
       <c r="C387">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D387" t="s">
         <v>32</v>
@@ -11479,7 +11479,7 @@
         <v>31</v>
       </c>
       <c r="C388">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="D388" t="s">
         <v>32</v>
@@ -11493,7 +11493,7 @@
         <v>31</v>
       </c>
       <c r="C389">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="D389" t="s">
         <v>32</v>
@@ -11507,7 +11507,7 @@
         <v>31</v>
       </c>
       <c r="C390">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="D390" t="s">
         <v>32</v>
@@ -11521,7 +11521,7 @@
         <v>31</v>
       </c>
       <c r="C391">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D391" t="s">
         <v>32</v>
@@ -11535,7 +11535,7 @@
         <v>31</v>
       </c>
       <c r="C392">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D392" t="s">
         <v>32</v>
@@ -11549,7 +11549,7 @@
         <v>31</v>
       </c>
       <c r="C393">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D393" t="s">
         <v>32</v>
@@ -11563,7 +11563,7 @@
         <v>31</v>
       </c>
       <c r="C394">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D394" t="s">
         <v>32</v>
@@ -11577,7 +11577,7 @@
         <v>31</v>
       </c>
       <c r="C395">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="D395" t="s">
         <v>32</v>
@@ -11591,7 +11591,7 @@
         <v>31</v>
       </c>
       <c r="C396">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D396" t="s">
         <v>32</v>
@@ -11605,7 +11605,7 @@
         <v>31</v>
       </c>
       <c r="C397">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D397" t="s">
         <v>32</v>
@@ -11619,7 +11619,7 @@
         <v>31</v>
       </c>
       <c r="C398">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D398" t="s">
         <v>32</v>
@@ -11633,7 +11633,7 @@
         <v>31</v>
       </c>
       <c r="C399">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="D399" t="s">
         <v>32</v>
@@ -11647,7 +11647,7 @@
         <v>31</v>
       </c>
       <c r="C400">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D400" t="s">
         <v>32</v>
@@ -11661,7 +11661,7 @@
         <v>31</v>
       </c>
       <c r="C401">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D401" t="s">
         <v>32</v>
@@ -22556,7 +22556,7 @@
         <v>31</v>
       </c>
       <c r="C2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
         <v>32</v>
@@ -22570,7 +22570,7 @@
         <v>31</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
         <v>32</v>
@@ -22584,7 +22584,7 @@
         <v>31</v>
       </c>
       <c r="C4">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
@@ -22598,7 +22598,7 @@
         <v>31</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
         <v>32</v>
@@ -22612,7 +22612,7 @@
         <v>31</v>
       </c>
       <c r="C6">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
         <v>32</v>
@@ -22626,7 +22626,7 @@
         <v>31</v>
       </c>
       <c r="C7">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
@@ -22640,7 +22640,7 @@
         <v>31</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
         <v>32</v>
@@ -22654,7 +22654,7 @@
         <v>31</v>
       </c>
       <c r="C9">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
         <v>32</v>
@@ -22668,7 +22668,7 @@
         <v>31</v>
       </c>
       <c r="C10">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
         <v>32</v>
@@ -22682,7 +22682,7 @@
         <v>31</v>
       </c>
       <c r="C11">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
@@ -22696,7 +22696,7 @@
         <v>31</v>
       </c>
       <c r="C12">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
         <v>32</v>
@@ -22710,7 +22710,7 @@
         <v>31</v>
       </c>
       <c r="C13">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
         <v>32</v>
@@ -22724,7 +22724,7 @@
         <v>31</v>
       </c>
       <c r="C14">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D14" t="s">
         <v>32</v>
@@ -22738,7 +22738,7 @@
         <v>31</v>
       </c>
       <c r="C15">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
         <v>32</v>
@@ -22752,7 +22752,7 @@
         <v>31</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" t="s">
         <v>32</v>
@@ -22766,7 +22766,7 @@
         <v>31</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
         <v>32</v>
@@ -22780,7 +22780,7 @@
         <v>31</v>
       </c>
       <c r="C18">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D18" t="s">
         <v>32</v>
@@ -22794,7 +22794,7 @@
         <v>31</v>
       </c>
       <c r="C19">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D19" t="s">
         <v>32</v>
@@ -22808,7 +22808,7 @@
         <v>31</v>
       </c>
       <c r="C20">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D20" t="s">
         <v>32</v>
@@ -22822,7 +22822,7 @@
         <v>31</v>
       </c>
       <c r="C21">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D21" t="s">
         <v>32</v>
@@ -22836,7 +22836,7 @@
         <v>31</v>
       </c>
       <c r="C22">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D22" t="s">
         <v>32</v>
@@ -22850,7 +22850,7 @@
         <v>31</v>
       </c>
       <c r="C23">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D23" t="s">
         <v>32</v>
@@ -22864,7 +22864,7 @@
         <v>31</v>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D24" t="s">
         <v>32</v>
@@ -22878,7 +22878,7 @@
         <v>31</v>
       </c>
       <c r="C25">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D25" t="s">
         <v>32</v>
@@ -22892,7 +22892,7 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="D26" t="s">
         <v>32</v>
@@ -22906,7 +22906,7 @@
         <v>31</v>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D27" t="s">
         <v>32</v>
@@ -22920,7 +22920,7 @@
         <v>31</v>
       </c>
       <c r="C28">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D28" t="s">
         <v>32</v>
@@ -22934,7 +22934,7 @@
         <v>31</v>
       </c>
       <c r="C29">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D29" t="s">
         <v>32</v>
@@ -22948,7 +22948,7 @@
         <v>31</v>
       </c>
       <c r="C30">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="D30" t="s">
         <v>32</v>
@@ -22962,7 +22962,7 @@
         <v>31</v>
       </c>
       <c r="C31">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D31" t="s">
         <v>32</v>
@@ -22976,7 +22976,7 @@
         <v>31</v>
       </c>
       <c r="C32">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D32" t="s">
         <v>32</v>
@@ -22990,7 +22990,7 @@
         <v>31</v>
       </c>
       <c r="C33">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D33" t="s">
         <v>32</v>
@@ -23004,7 +23004,7 @@
         <v>31</v>
       </c>
       <c r="C34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D34" t="s">
         <v>32</v>
@@ -23018,7 +23018,7 @@
         <v>31</v>
       </c>
       <c r="C35">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D35" t="s">
         <v>32</v>
@@ -23032,7 +23032,7 @@
         <v>31</v>
       </c>
       <c r="C36">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D36" t="s">
         <v>32</v>
@@ -23046,7 +23046,7 @@
         <v>31</v>
       </c>
       <c r="C37">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="D37" t="s">
         <v>32</v>
@@ -23060,7 +23060,7 @@
         <v>31</v>
       </c>
       <c r="C38">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D38" t="s">
         <v>32</v>
@@ -23074,7 +23074,7 @@
         <v>31</v>
       </c>
       <c r="C39">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D39" t="s">
         <v>32</v>
@@ -23088,7 +23088,7 @@
         <v>31</v>
       </c>
       <c r="C40">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D40" t="s">
         <v>32</v>
@@ -23102,7 +23102,7 @@
         <v>31</v>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D41" t="s">
         <v>32</v>
@@ -23116,7 +23116,7 @@
         <v>31</v>
       </c>
       <c r="C42">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D42" t="s">
         <v>32</v>
@@ -23130,7 +23130,7 @@
         <v>31</v>
       </c>
       <c r="C43">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D43" t="s">
         <v>32</v>
@@ -23144,7 +23144,7 @@
         <v>31</v>
       </c>
       <c r="C44">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D44" t="s">
         <v>32</v>
@@ -23158,7 +23158,7 @@
         <v>31</v>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D45" t="s">
         <v>32</v>
@@ -23186,7 +23186,7 @@
         <v>31</v>
       </c>
       <c r="C47">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D47" t="s">
         <v>32</v>
@@ -23200,7 +23200,7 @@
         <v>31</v>
       </c>
       <c r="C48">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D48" t="s">
         <v>32</v>
@@ -23214,7 +23214,7 @@
         <v>31</v>
       </c>
       <c r="C49">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D49" t="s">
         <v>32</v>
@@ -23228,7 +23228,7 @@
         <v>31</v>
       </c>
       <c r="C50">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D50" t="s">
         <v>32</v>
@@ -23242,7 +23242,7 @@
         <v>31</v>
       </c>
       <c r="C51">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D51" t="s">
         <v>32</v>
@@ -23256,7 +23256,7 @@
         <v>31</v>
       </c>
       <c r="C52">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D52" t="s">
         <v>32</v>
@@ -23270,7 +23270,7 @@
         <v>31</v>
       </c>
       <c r="C53">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D53" t="s">
         <v>32</v>
@@ -23284,7 +23284,7 @@
         <v>31</v>
       </c>
       <c r="C54">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D54" t="s">
         <v>32</v>
@@ -23298,7 +23298,7 @@
         <v>31</v>
       </c>
       <c r="C55">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D55" t="s">
         <v>32</v>
@@ -23312,7 +23312,7 @@
         <v>31</v>
       </c>
       <c r="C56">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D56" t="s">
         <v>32</v>
@@ -23326,7 +23326,7 @@
         <v>31</v>
       </c>
       <c r="C57">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D57" t="s">
         <v>32</v>
@@ -23340,7 +23340,7 @@
         <v>31</v>
       </c>
       <c r="C58">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="D58" t="s">
         <v>32</v>
@@ -23354,7 +23354,7 @@
         <v>31</v>
       </c>
       <c r="C59">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D59" t="s">
         <v>32</v>
@@ -23368,7 +23368,7 @@
         <v>31</v>
       </c>
       <c r="C60">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D60" t="s">
         <v>32</v>
@@ -23382,7 +23382,7 @@
         <v>31</v>
       </c>
       <c r="C61">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D61" t="s">
         <v>32</v>
@@ -23396,7 +23396,7 @@
         <v>31</v>
       </c>
       <c r="C62">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D62" t="s">
         <v>32</v>
@@ -23410,7 +23410,7 @@
         <v>31</v>
       </c>
       <c r="C63">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D63" t="s">
         <v>32</v>
@@ -23424,7 +23424,7 @@
         <v>31</v>
       </c>
       <c r="C64">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="D64" t="s">
         <v>32</v>
@@ -23438,7 +23438,7 @@
         <v>31</v>
       </c>
       <c r="C65">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D65" t="s">
         <v>32</v>
@@ -23452,7 +23452,7 @@
         <v>31</v>
       </c>
       <c r="C66">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D66" t="s">
         <v>32</v>
@@ -23466,7 +23466,7 @@
         <v>31</v>
       </c>
       <c r="C67">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D67" t="s">
         <v>32</v>
@@ -23480,7 +23480,7 @@
         <v>31</v>
       </c>
       <c r="C68">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D68" t="s">
         <v>32</v>
@@ -23494,7 +23494,7 @@
         <v>31</v>
       </c>
       <c r="C69">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D69" t="s">
         <v>32</v>
@@ -23508,7 +23508,7 @@
         <v>31</v>
       </c>
       <c r="C70">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D70" t="s">
         <v>32</v>
@@ -23522,7 +23522,7 @@
         <v>31</v>
       </c>
       <c r="C71">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D71" t="s">
         <v>32</v>
@@ -23536,7 +23536,7 @@
         <v>31</v>
       </c>
       <c r="C72">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D72" t="s">
         <v>32</v>
@@ -23550,7 +23550,7 @@
         <v>31</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="D73" t="s">
         <v>32</v>
@@ -23564,7 +23564,7 @@
         <v>31</v>
       </c>
       <c r="C74">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D74" t="s">
         <v>32</v>
@@ -23578,7 +23578,7 @@
         <v>31</v>
       </c>
       <c r="C75">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D75" t="s">
         <v>32</v>
@@ -23592,7 +23592,7 @@
         <v>31</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D76" t="s">
         <v>32</v>
@@ -23606,7 +23606,7 @@
         <v>31</v>
       </c>
       <c r="C77">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="D77" t="s">
         <v>32</v>
@@ -23620,7 +23620,7 @@
         <v>31</v>
       </c>
       <c r="C78">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D78" t="s">
         <v>32</v>
@@ -23634,7 +23634,7 @@
         <v>31</v>
       </c>
       <c r="C79">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D79" t="s">
         <v>32</v>
@@ -23648,7 +23648,7 @@
         <v>31</v>
       </c>
       <c r="C80">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D80" t="s">
         <v>32</v>
@@ -23662,7 +23662,7 @@
         <v>31</v>
       </c>
       <c r="C81">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D81" t="s">
         <v>32</v>
@@ -23676,7 +23676,7 @@
         <v>31</v>
       </c>
       <c r="C82">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="D82" t="s">
         <v>32</v>
@@ -23690,7 +23690,7 @@
         <v>31</v>
       </c>
       <c r="C83">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D83" t="s">
         <v>32</v>
@@ -23704,7 +23704,7 @@
         <v>31</v>
       </c>
       <c r="C84">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D84" t="s">
         <v>32</v>
@@ -23718,7 +23718,7 @@
         <v>31</v>
       </c>
       <c r="C85">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="D85" t="s">
         <v>32</v>
@@ -23732,7 +23732,7 @@
         <v>31</v>
       </c>
       <c r="C86">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D86" t="s">
         <v>32</v>
@@ -23746,7 +23746,7 @@
         <v>31</v>
       </c>
       <c r="C87">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D87" t="s">
         <v>32</v>
@@ -23774,7 +23774,7 @@
         <v>31</v>
       </c>
       <c r="C89">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D89" t="s">
         <v>32</v>
@@ -23788,7 +23788,7 @@
         <v>31</v>
       </c>
       <c r="C90">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D90" t="s">
         <v>32</v>
@@ -23802,7 +23802,7 @@
         <v>31</v>
       </c>
       <c r="C91">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D91" t="s">
         <v>32</v>
@@ -23816,7 +23816,7 @@
         <v>31</v>
       </c>
       <c r="C92">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D92" t="s">
         <v>32</v>
@@ -23830,7 +23830,7 @@
         <v>31</v>
       </c>
       <c r="C93">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D93" t="s">
         <v>32</v>
@@ -23844,7 +23844,7 @@
         <v>31</v>
       </c>
       <c r="C94">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D94" t="s">
         <v>32</v>
@@ -23858,7 +23858,7 @@
         <v>31</v>
       </c>
       <c r="C95">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D95" t="s">
         <v>32</v>
@@ -23872,7 +23872,7 @@
         <v>31</v>
       </c>
       <c r="C96">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D96" t="s">
         <v>32</v>
@@ -23886,7 +23886,7 @@
         <v>31</v>
       </c>
       <c r="C97">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D97" t="s">
         <v>32</v>
@@ -23900,7 +23900,7 @@
         <v>31</v>
       </c>
       <c r="C98">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D98" t="s">
         <v>32</v>
@@ -23914,7 +23914,7 @@
         <v>31</v>
       </c>
       <c r="C99">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D99" t="s">
         <v>32</v>
@@ -23928,7 +23928,7 @@
         <v>31</v>
       </c>
       <c r="C100">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="D100" t="s">
         <v>32</v>
@@ -23942,7 +23942,7 @@
         <v>31</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D101" t="s">
         <v>32</v>
@@ -23956,7 +23956,7 @@
         <v>31</v>
       </c>
       <c r="C102">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D102" t="s">
         <v>32</v>
@@ -23970,7 +23970,7 @@
         <v>31</v>
       </c>
       <c r="C103">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D103" t="s">
         <v>32</v>
@@ -23984,7 +23984,7 @@
         <v>31</v>
       </c>
       <c r="C104">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D104" t="s">
         <v>32</v>
@@ -23998,7 +23998,7 @@
         <v>31</v>
       </c>
       <c r="C105">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D105" t="s">
         <v>32</v>
@@ -24012,7 +24012,7 @@
         <v>31</v>
       </c>
       <c r="C106">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D106" t="s">
         <v>32</v>
@@ -24026,7 +24026,7 @@
         <v>31</v>
       </c>
       <c r="C107">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D107" t="s">
         <v>32</v>
@@ -24040,7 +24040,7 @@
         <v>31</v>
       </c>
       <c r="C108">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D108" t="s">
         <v>32</v>
@@ -24068,7 +24068,7 @@
         <v>31</v>
       </c>
       <c r="C110">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D110" t="s">
         <v>32</v>
@@ -24082,7 +24082,7 @@
         <v>31</v>
       </c>
       <c r="C111">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D111" t="s">
         <v>32</v>
@@ -24096,7 +24096,7 @@
         <v>31</v>
       </c>
       <c r="C112">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D112" t="s">
         <v>32</v>
@@ -24110,7 +24110,7 @@
         <v>31</v>
       </c>
       <c r="C113">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D113" t="s">
         <v>32</v>
@@ -24124,7 +24124,7 @@
         <v>31</v>
       </c>
       <c r="C114">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D114" t="s">
         <v>32</v>
@@ -24138,7 +24138,7 @@
         <v>31</v>
       </c>
       <c r="C115">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D115" t="s">
         <v>32</v>
@@ -24152,7 +24152,7 @@
         <v>31</v>
       </c>
       <c r="C116">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D116" t="s">
         <v>32</v>
@@ -24166,7 +24166,7 @@
         <v>31</v>
       </c>
       <c r="C117">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="D117" t="s">
         <v>32</v>
@@ -24180,7 +24180,7 @@
         <v>31</v>
       </c>
       <c r="C118">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D118" t="s">
         <v>32</v>
@@ -24194,7 +24194,7 @@
         <v>31</v>
       </c>
       <c r="C119">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D119" t="s">
         <v>32</v>
@@ -24208,7 +24208,7 @@
         <v>31</v>
       </c>
       <c r="C120">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D120" t="s">
         <v>32</v>
@@ -24222,7 +24222,7 @@
         <v>31</v>
       </c>
       <c r="C121">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D121" t="s">
         <v>32</v>
@@ -24236,7 +24236,7 @@
         <v>31</v>
       </c>
       <c r="C122">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="D122" t="s">
         <v>32</v>
@@ -24250,7 +24250,7 @@
         <v>31</v>
       </c>
       <c r="C123">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D123" t="s">
         <v>32</v>
@@ -24264,7 +24264,7 @@
         <v>31</v>
       </c>
       <c r="C124">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D124" t="s">
         <v>32</v>
@@ -24278,7 +24278,7 @@
         <v>31</v>
       </c>
       <c r="C125">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="D125" t="s">
         <v>32</v>
@@ -24292,7 +24292,7 @@
         <v>31</v>
       </c>
       <c r="C126">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D126" t="s">
         <v>32</v>
@@ -24306,7 +24306,7 @@
         <v>31</v>
       </c>
       <c r="C127">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D127" t="s">
         <v>32</v>
@@ -24320,7 +24320,7 @@
         <v>31</v>
       </c>
       <c r="C128">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D128" t="s">
         <v>32</v>
@@ -24334,7 +24334,7 @@
         <v>31</v>
       </c>
       <c r="C129">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D129" t="s">
         <v>32</v>
@@ -24348,7 +24348,7 @@
         <v>31</v>
       </c>
       <c r="C130">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D130" t="s">
         <v>32</v>
@@ -24362,7 +24362,7 @@
         <v>31</v>
       </c>
       <c r="C131">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D131" t="s">
         <v>32</v>
@@ -24376,7 +24376,7 @@
         <v>31</v>
       </c>
       <c r="C132">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D132" t="s">
         <v>32</v>
@@ -24390,7 +24390,7 @@
         <v>31</v>
       </c>
       <c r="C133">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="D133" t="s">
         <v>32</v>
@@ -24404,7 +24404,7 @@
         <v>31</v>
       </c>
       <c r="C134">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D134" t="s">
         <v>32</v>
@@ -24418,7 +24418,7 @@
         <v>31</v>
       </c>
       <c r="C135">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D135" t="s">
         <v>32</v>
@@ -24432,7 +24432,7 @@
         <v>31</v>
       </c>
       <c r="C136">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="D136" t="s">
         <v>32</v>
@@ -24446,7 +24446,7 @@
         <v>31</v>
       </c>
       <c r="C137">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D137" t="s">
         <v>32</v>
@@ -24460,7 +24460,7 @@
         <v>31</v>
       </c>
       <c r="C138">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D138" t="s">
         <v>32</v>
@@ -24474,7 +24474,7 @@
         <v>31</v>
       </c>
       <c r="C139">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D139" t="s">
         <v>32</v>
@@ -24488,7 +24488,7 @@
         <v>31</v>
       </c>
       <c r="C140">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D140" t="s">
         <v>32</v>
@@ -24502,7 +24502,7 @@
         <v>31</v>
       </c>
       <c r="C141">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D141" t="s">
         <v>32</v>
@@ -24516,7 +24516,7 @@
         <v>31</v>
       </c>
       <c r="C142">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D142" t="s">
         <v>32</v>
@@ -24544,7 +24544,7 @@
         <v>31</v>
       </c>
       <c r="C144">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D144" t="s">
         <v>32</v>
@@ -24558,7 +24558,7 @@
         <v>31</v>
       </c>
       <c r="C145">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D145" t="s">
         <v>32</v>
@@ -24572,7 +24572,7 @@
         <v>31</v>
       </c>
       <c r="C146">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D146" t="s">
         <v>32</v>
@@ -24586,7 +24586,7 @@
         <v>31</v>
       </c>
       <c r="C147">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D147" t="s">
         <v>32</v>
@@ -24600,7 +24600,7 @@
         <v>31</v>
       </c>
       <c r="C148">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D148" t="s">
         <v>32</v>
@@ -24614,7 +24614,7 @@
         <v>31</v>
       </c>
       <c r="C149">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="D149" t="s">
         <v>32</v>
@@ -24628,7 +24628,7 @@
         <v>31</v>
       </c>
       <c r="C150">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D150" t="s">
         <v>32</v>
@@ -24642,7 +24642,7 @@
         <v>31</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D151" t="s">
         <v>32</v>
@@ -24656,7 +24656,7 @@
         <v>31</v>
       </c>
       <c r="C152">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D152" t="s">
         <v>32</v>
@@ -24670,7 +24670,7 @@
         <v>31</v>
       </c>
       <c r="C153">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D153" t="s">
         <v>32</v>
@@ -24684,7 +24684,7 @@
         <v>31</v>
       </c>
       <c r="C154">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D154" t="s">
         <v>32</v>
@@ -24698,7 +24698,7 @@
         <v>31</v>
       </c>
       <c r="C155">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D155" t="s">
         <v>32</v>
@@ -24712,7 +24712,7 @@
         <v>31</v>
       </c>
       <c r="C156">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D156" t="s">
         <v>32</v>
@@ -24726,7 +24726,7 @@
         <v>31</v>
       </c>
       <c r="C157">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D157" t="s">
         <v>32</v>
@@ -24740,7 +24740,7 @@
         <v>31</v>
       </c>
       <c r="C158">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D158" t="s">
         <v>32</v>
@@ -24754,7 +24754,7 @@
         <v>31</v>
       </c>
       <c r="C159">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="D159" t="s">
         <v>32</v>
@@ -24768,7 +24768,7 @@
         <v>31</v>
       </c>
       <c r="C160">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="D160" t="s">
         <v>32</v>
@@ -24782,7 +24782,7 @@
         <v>31</v>
       </c>
       <c r="C161">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D161" t="s">
         <v>32</v>
@@ -24796,7 +24796,7 @@
         <v>31</v>
       </c>
       <c r="C162">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D162" t="s">
         <v>32</v>
@@ -24810,7 +24810,7 @@
         <v>31</v>
       </c>
       <c r="C163">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D163" t="s">
         <v>32</v>
@@ -24824,7 +24824,7 @@
         <v>31</v>
       </c>
       <c r="C164">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D164" t="s">
         <v>32</v>
@@ -24838,7 +24838,7 @@
         <v>31</v>
       </c>
       <c r="C165">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D165" t="s">
         <v>32</v>
@@ -24852,7 +24852,7 @@
         <v>31</v>
       </c>
       <c r="C166">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D166" t="s">
         <v>32</v>
@@ -24866,7 +24866,7 @@
         <v>31</v>
       </c>
       <c r="C167">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D167" t="s">
         <v>32</v>
@@ -24894,7 +24894,7 @@
         <v>31</v>
       </c>
       <c r="C169">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D169" t="s">
         <v>32</v>
@@ -24908,7 +24908,7 @@
         <v>31</v>
       </c>
       <c r="C170">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D170" t="s">
         <v>32</v>
@@ -24922,7 +24922,7 @@
         <v>31</v>
       </c>
       <c r="C171">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D171" t="s">
         <v>32</v>
@@ -24936,7 +24936,7 @@
         <v>31</v>
       </c>
       <c r="C172">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D172" t="s">
         <v>32</v>
@@ -24950,7 +24950,7 @@
         <v>31</v>
       </c>
       <c r="C173">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D173" t="s">
         <v>32</v>
@@ -24964,7 +24964,7 @@
         <v>31</v>
       </c>
       <c r="C174">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D174" t="s">
         <v>32</v>
@@ -24978,7 +24978,7 @@
         <v>31</v>
       </c>
       <c r="C175">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="D175" t="s">
         <v>32</v>
@@ -24992,7 +24992,7 @@
         <v>31</v>
       </c>
       <c r="C176">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D176" t="s">
         <v>32</v>
@@ -25006,7 +25006,7 @@
         <v>31</v>
       </c>
       <c r="C177">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D177" t="s">
         <v>32</v>
@@ -25020,7 +25020,7 @@
         <v>31</v>
       </c>
       <c r="C178">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D178" t="s">
         <v>32</v>
@@ -25034,7 +25034,7 @@
         <v>31</v>
       </c>
       <c r="C179">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D179" t="s">
         <v>32</v>
@@ -25048,7 +25048,7 @@
         <v>31</v>
       </c>
       <c r="C180">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D180" t="s">
         <v>32</v>
@@ -25062,7 +25062,7 @@
         <v>31</v>
       </c>
       <c r="C181">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D181" t="s">
         <v>32</v>
@@ -25076,7 +25076,7 @@
         <v>31</v>
       </c>
       <c r="C182">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D182" t="s">
         <v>32</v>
@@ -25090,7 +25090,7 @@
         <v>31</v>
       </c>
       <c r="C183">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D183" t="s">
         <v>32</v>
@@ -25104,7 +25104,7 @@
         <v>31</v>
       </c>
       <c r="C184">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D184" t="s">
         <v>32</v>
@@ -25118,7 +25118,7 @@
         <v>31</v>
       </c>
       <c r="C185">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="D185" t="s">
         <v>32</v>
@@ -25132,7 +25132,7 @@
         <v>31</v>
       </c>
       <c r="C186">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D186" t="s">
         <v>32</v>
@@ -25146,7 +25146,7 @@
         <v>31</v>
       </c>
       <c r="C187">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D187" t="s">
         <v>32</v>
@@ -25160,7 +25160,7 @@
         <v>31</v>
       </c>
       <c r="C188">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D188" t="s">
         <v>32</v>
@@ -25174,7 +25174,7 @@
         <v>31</v>
       </c>
       <c r="C189">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D189" t="s">
         <v>32</v>
@@ -25188,7 +25188,7 @@
         <v>31</v>
       </c>
       <c r="C190">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D190" t="s">
         <v>32</v>
@@ -25202,7 +25202,7 @@
         <v>31</v>
       </c>
       <c r="C191">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="D191" t="s">
         <v>32</v>
@@ -25216,7 +25216,7 @@
         <v>31</v>
       </c>
       <c r="C192">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D192" t="s">
         <v>32</v>
@@ -25230,7 +25230,7 @@
         <v>31</v>
       </c>
       <c r="C193">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D193" t="s">
         <v>32</v>
@@ -25244,7 +25244,7 @@
         <v>31</v>
       </c>
       <c r="C194">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D194" t="s">
         <v>32</v>
@@ -25258,7 +25258,7 @@
         <v>31</v>
       </c>
       <c r="C195">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D195" t="s">
         <v>32</v>
@@ -25272,7 +25272,7 @@
         <v>31</v>
       </c>
       <c r="C196">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D196" t="s">
         <v>32</v>
@@ -25286,7 +25286,7 @@
         <v>31</v>
       </c>
       <c r="C197">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D197" t="s">
         <v>32</v>
@@ -25300,7 +25300,7 @@
         <v>31</v>
       </c>
       <c r="C198">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="D198" t="s">
         <v>32</v>
@@ -25314,7 +25314,7 @@
         <v>31</v>
       </c>
       <c r="C199">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D199" t="s">
         <v>32</v>
@@ -25328,7 +25328,7 @@
         <v>31</v>
       </c>
       <c r="C200">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D200" t="s">
         <v>32</v>
@@ -25342,7 +25342,7 @@
         <v>31</v>
       </c>
       <c r="C201">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D201" t="s">
         <v>32</v>
@@ -25356,7 +25356,7 @@
         <v>31</v>
       </c>
       <c r="C202">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D202" t="s">
         <v>32</v>
@@ -25370,7 +25370,7 @@
         <v>31</v>
       </c>
       <c r="C203">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D203" t="s">
         <v>32</v>
@@ -25384,7 +25384,7 @@
         <v>31</v>
       </c>
       <c r="C204">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D204" t="s">
         <v>32</v>
@@ -25398,7 +25398,7 @@
         <v>31</v>
       </c>
       <c r="C205">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D205" t="s">
         <v>32</v>
@@ -25412,7 +25412,7 @@
         <v>31</v>
       </c>
       <c r="C206">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D206" t="s">
         <v>32</v>
@@ -25426,7 +25426,7 @@
         <v>31</v>
       </c>
       <c r="C207">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D207" t="s">
         <v>32</v>
@@ -25440,7 +25440,7 @@
         <v>31</v>
       </c>
       <c r="C208">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D208" t="s">
         <v>32</v>
@@ -25454,7 +25454,7 @@
         <v>31</v>
       </c>
       <c r="C209">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D209" t="s">
         <v>32</v>
@@ -25468,7 +25468,7 @@
         <v>31</v>
       </c>
       <c r="C210">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D210" t="s">
         <v>32</v>
@@ -25482,7 +25482,7 @@
         <v>31</v>
       </c>
       <c r="C211">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D211" t="s">
         <v>32</v>
@@ -25496,7 +25496,7 @@
         <v>31</v>
       </c>
       <c r="C212">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D212" t="s">
         <v>32</v>
@@ -25510,7 +25510,7 @@
         <v>31</v>
       </c>
       <c r="C213">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D213" t="s">
         <v>32</v>
@@ -25524,7 +25524,7 @@
         <v>31</v>
       </c>
       <c r="C214">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="D214" t="s">
         <v>32</v>
@@ -25538,7 +25538,7 @@
         <v>31</v>
       </c>
       <c r="C215">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D215" t="s">
         <v>32</v>
@@ -25552,7 +25552,7 @@
         <v>31</v>
       </c>
       <c r="C216">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D216" t="s">
         <v>32</v>
@@ -25566,7 +25566,7 @@
         <v>31</v>
       </c>
       <c r="C217">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D217" t="s">
         <v>32</v>
@@ -25580,7 +25580,7 @@
         <v>31</v>
       </c>
       <c r="C218">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="D218" t="s">
         <v>32</v>
@@ -25594,7 +25594,7 @@
         <v>31</v>
       </c>
       <c r="C219">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D219" t="s">
         <v>32</v>
@@ -25608,7 +25608,7 @@
         <v>31</v>
       </c>
       <c r="C220">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="D220" t="s">
         <v>32</v>
@@ -25622,7 +25622,7 @@
         <v>31</v>
       </c>
       <c r="C221">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D221" t="s">
         <v>32</v>
@@ -25636,7 +25636,7 @@
         <v>31</v>
       </c>
       <c r="C222">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D222" t="s">
         <v>32</v>
@@ -25650,7 +25650,7 @@
         <v>31</v>
       </c>
       <c r="C223">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D223" t="s">
         <v>32</v>
@@ -25664,7 +25664,7 @@
         <v>31</v>
       </c>
       <c r="C224">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D224" t="s">
         <v>32</v>
@@ -25678,7 +25678,7 @@
         <v>31</v>
       </c>
       <c r="C225">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D225" t="s">
         <v>32</v>
@@ -25692,7 +25692,7 @@
         <v>31</v>
       </c>
       <c r="C226">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D226" t="s">
         <v>32</v>
@@ -25706,7 +25706,7 @@
         <v>31</v>
       </c>
       <c r="C227">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D227" t="s">
         <v>32</v>
@@ -25720,7 +25720,7 @@
         <v>31</v>
       </c>
       <c r="C228">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D228" t="s">
         <v>32</v>
@@ -25734,7 +25734,7 @@
         <v>31</v>
       </c>
       <c r="C229">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D229" t="s">
         <v>32</v>
@@ -25748,7 +25748,7 @@
         <v>31</v>
       </c>
       <c r="C230">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="D230" t="s">
         <v>32</v>
@@ -25762,7 +25762,7 @@
         <v>31</v>
       </c>
       <c r="C231">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D231" t="s">
         <v>32</v>
@@ -25776,7 +25776,7 @@
         <v>31</v>
       </c>
       <c r="C232">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D232" t="s">
         <v>32</v>
@@ -25790,7 +25790,7 @@
         <v>31</v>
       </c>
       <c r="C233">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D233" t="s">
         <v>32</v>
@@ -25818,7 +25818,7 @@
         <v>31</v>
       </c>
       <c r="C235">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D235" t="s">
         <v>32</v>
@@ -25832,7 +25832,7 @@
         <v>31</v>
       </c>
       <c r="C236">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D236" t="s">
         <v>32</v>
@@ -25846,7 +25846,7 @@
         <v>31</v>
       </c>
       <c r="C237">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D237" t="s">
         <v>32</v>
@@ -25860,7 +25860,7 @@
         <v>31</v>
       </c>
       <c r="C238">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D238" t="s">
         <v>32</v>
@@ -25874,7 +25874,7 @@
         <v>31</v>
       </c>
       <c r="C239">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D239" t="s">
         <v>32</v>
@@ -25888,7 +25888,7 @@
         <v>31</v>
       </c>
       <c r="C240">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D240" t="s">
         <v>32</v>
@@ -25902,7 +25902,7 @@
         <v>31</v>
       </c>
       <c r="C241">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D241" t="s">
         <v>32</v>
@@ -25916,7 +25916,7 @@
         <v>31</v>
       </c>
       <c r="C242">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D242" t="s">
         <v>32</v>
@@ -25930,7 +25930,7 @@
         <v>31</v>
       </c>
       <c r="C243">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D243" t="s">
         <v>32</v>
@@ -25944,7 +25944,7 @@
         <v>31</v>
       </c>
       <c r="C244">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D244" t="s">
         <v>32</v>
@@ -25958,7 +25958,7 @@
         <v>31</v>
       </c>
       <c r="C245">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D245" t="s">
         <v>32</v>
@@ -25972,7 +25972,7 @@
         <v>31</v>
       </c>
       <c r="C246">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D246" t="s">
         <v>32</v>
@@ -25986,7 +25986,7 @@
         <v>31</v>
       </c>
       <c r="C247">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D247" t="s">
         <v>32</v>
@@ -26000,7 +26000,7 @@
         <v>31</v>
       </c>
       <c r="C248">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D248" t="s">
         <v>32</v>
@@ -26014,7 +26014,7 @@
         <v>31</v>
       </c>
       <c r="C249">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D249" t="s">
         <v>32</v>
@@ -26028,7 +26028,7 @@
         <v>31</v>
       </c>
       <c r="C250">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D250" t="s">
         <v>32</v>
@@ -26042,7 +26042,7 @@
         <v>31</v>
       </c>
       <c r="C251">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D251" t="s">
         <v>32</v>
@@ -26056,7 +26056,7 @@
         <v>31</v>
       </c>
       <c r="C252">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D252" t="s">
         <v>32</v>
@@ -26084,7 +26084,7 @@
         <v>31</v>
       </c>
       <c r="C254">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D254" t="s">
         <v>32</v>
@@ -26098,7 +26098,7 @@
         <v>31</v>
       </c>
       <c r="C255">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D255" t="s">
         <v>32</v>
@@ -26112,7 +26112,7 @@
         <v>31</v>
       </c>
       <c r="C256">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D256" t="s">
         <v>32</v>
@@ -26126,7 +26126,7 @@
         <v>31</v>
       </c>
       <c r="C257">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D257" t="s">
         <v>32</v>
@@ -26140,7 +26140,7 @@
         <v>31</v>
       </c>
       <c r="C258">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="D258" t="s">
         <v>32</v>
@@ -26154,7 +26154,7 @@
         <v>31</v>
       </c>
       <c r="C259">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D259" t="s">
         <v>32</v>
@@ -26168,7 +26168,7 @@
         <v>31</v>
       </c>
       <c r="C260">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D260" t="s">
         <v>32</v>
@@ -26182,7 +26182,7 @@
         <v>31</v>
       </c>
       <c r="C261">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D261" t="s">
         <v>32</v>
@@ -26196,7 +26196,7 @@
         <v>31</v>
       </c>
       <c r="C262">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D262" t="s">
         <v>32</v>
@@ -26210,7 +26210,7 @@
         <v>31</v>
       </c>
       <c r="C263">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D263" t="s">
         <v>32</v>
@@ -26224,7 +26224,7 @@
         <v>31</v>
       </c>
       <c r="C264">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D264" t="s">
         <v>32</v>
@@ -26238,7 +26238,7 @@
         <v>31</v>
       </c>
       <c r="C265">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D265" t="s">
         <v>32</v>
@@ -26252,7 +26252,7 @@
         <v>31</v>
       </c>
       <c r="C266">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D266" t="s">
         <v>32</v>
@@ -26266,7 +26266,7 @@
         <v>31</v>
       </c>
       <c r="C267">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D267" t="s">
         <v>32</v>
@@ -26280,7 +26280,7 @@
         <v>31</v>
       </c>
       <c r="C268">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D268" t="s">
         <v>32</v>
@@ -26294,7 +26294,7 @@
         <v>31</v>
       </c>
       <c r="C269">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D269" t="s">
         <v>32</v>
@@ -26308,7 +26308,7 @@
         <v>31</v>
       </c>
       <c r="C270">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="D270" t="s">
         <v>32</v>
@@ -26322,7 +26322,7 @@
         <v>31</v>
       </c>
       <c r="C271">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D271" t="s">
         <v>32</v>
@@ -26336,7 +26336,7 @@
         <v>31</v>
       </c>
       <c r="C272">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D272" t="s">
         <v>32</v>
@@ -26350,7 +26350,7 @@
         <v>31</v>
       </c>
       <c r="C273">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D273" t="s">
         <v>32</v>
@@ -26364,7 +26364,7 @@
         <v>31</v>
       </c>
       <c r="C274">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D274" t="s">
         <v>32</v>
@@ -26378,7 +26378,7 @@
         <v>31</v>
       </c>
       <c r="C275">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D275" t="s">
         <v>32</v>
@@ -26392,7 +26392,7 @@
         <v>31</v>
       </c>
       <c r="C276">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D276" t="s">
         <v>32</v>
@@ -26406,7 +26406,7 @@
         <v>31</v>
       </c>
       <c r="C277">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D277" t="s">
         <v>32</v>
@@ -26420,7 +26420,7 @@
         <v>31</v>
       </c>
       <c r="C278">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D278" t="s">
         <v>32</v>
@@ -26434,7 +26434,7 @@
         <v>31</v>
       </c>
       <c r="C279">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D279" t="s">
         <v>32</v>
@@ -26448,7 +26448,7 @@
         <v>31</v>
       </c>
       <c r="C280">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="D280" t="s">
         <v>32</v>
@@ -26462,7 +26462,7 @@
         <v>31</v>
       </c>
       <c r="C281">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D281" t="s">
         <v>32</v>
@@ -26490,7 +26490,7 @@
         <v>31</v>
       </c>
       <c r="C283">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D283" t="s">
         <v>32</v>
@@ -26504,7 +26504,7 @@
         <v>31</v>
       </c>
       <c r="C284">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D284" t="s">
         <v>32</v>
@@ -26518,7 +26518,7 @@
         <v>31</v>
       </c>
       <c r="C285">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="D285" t="s">
         <v>32</v>
@@ -26532,7 +26532,7 @@
         <v>31</v>
       </c>
       <c r="C286">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D286" t="s">
         <v>32</v>
@@ -26546,7 +26546,7 @@
         <v>31</v>
       </c>
       <c r="C287">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D287" t="s">
         <v>32</v>
@@ -26560,7 +26560,7 @@
         <v>31</v>
       </c>
       <c r="C288">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D288" t="s">
         <v>32</v>
@@ -26574,7 +26574,7 @@
         <v>31</v>
       </c>
       <c r="C289">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D289" t="s">
         <v>32</v>
@@ -26588,7 +26588,7 @@
         <v>31</v>
       </c>
       <c r="C290">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="D290" t="s">
         <v>32</v>
@@ -26602,7 +26602,7 @@
         <v>31</v>
       </c>
       <c r="C291">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D291" t="s">
         <v>32</v>
@@ -26616,7 +26616,7 @@
         <v>31</v>
       </c>
       <c r="C292">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D292" t="s">
         <v>32</v>
@@ -26644,7 +26644,7 @@
         <v>31</v>
       </c>
       <c r="C294">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D294" t="s">
         <v>32</v>
@@ -26658,7 +26658,7 @@
         <v>31</v>
       </c>
       <c r="C295">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="D295" t="s">
         <v>32</v>
@@ -26672,7 +26672,7 @@
         <v>31</v>
       </c>
       <c r="C296">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D296" t="s">
         <v>32</v>
@@ -26686,7 +26686,7 @@
         <v>31</v>
       </c>
       <c r="C297">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="D297" t="s">
         <v>32</v>
@@ -26700,7 +26700,7 @@
         <v>31</v>
       </c>
       <c r="C298">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D298" t="s">
         <v>32</v>
@@ -26714,7 +26714,7 @@
         <v>31</v>
       </c>
       <c r="C299">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="D299" t="s">
         <v>32</v>
@@ -26728,7 +26728,7 @@
         <v>31</v>
       </c>
       <c r="C300">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D300" t="s">
         <v>32</v>
@@ -26742,7 +26742,7 @@
         <v>31</v>
       </c>
       <c r="C301">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D301" t="s">
         <v>32</v>
@@ -26756,7 +26756,7 @@
         <v>31</v>
       </c>
       <c r="C302">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D302" t="s">
         <v>32</v>
@@ -26770,7 +26770,7 @@
         <v>31</v>
       </c>
       <c r="C303">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D303" t="s">
         <v>32</v>
@@ -26784,7 +26784,7 @@
         <v>31</v>
       </c>
       <c r="C304">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="D304" t="s">
         <v>32</v>
@@ -26798,7 +26798,7 @@
         <v>31</v>
       </c>
       <c r="C305">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D305" t="s">
         <v>32</v>
@@ -26812,7 +26812,7 @@
         <v>31</v>
       </c>
       <c r="C306">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="D306" t="s">
         <v>32</v>
@@ -26826,7 +26826,7 @@
         <v>31</v>
       </c>
       <c r="C307">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D307" t="s">
         <v>32</v>
@@ -26854,7 +26854,7 @@
         <v>31</v>
       </c>
       <c r="C309">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D309" t="s">
         <v>32</v>
@@ -26868,7 +26868,7 @@
         <v>31</v>
       </c>
       <c r="C310">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="D310" t="s">
         <v>32</v>
@@ -26882,7 +26882,7 @@
         <v>31</v>
       </c>
       <c r="C311">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="D311" t="s">
         <v>32</v>
@@ -26896,7 +26896,7 @@
         <v>31</v>
       </c>
       <c r="C312">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D312" t="s">
         <v>32</v>
@@ -26910,7 +26910,7 @@
         <v>31</v>
       </c>
       <c r="C313">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D313" t="s">
         <v>32</v>
@@ -26924,7 +26924,7 @@
         <v>31</v>
       </c>
       <c r="C314">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="D314" t="s">
         <v>32</v>
@@ -26938,7 +26938,7 @@
         <v>31</v>
       </c>
       <c r="C315">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D315" t="s">
         <v>32</v>
@@ -26952,7 +26952,7 @@
         <v>31</v>
       </c>
       <c r="C316">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D316" t="s">
         <v>32</v>
@@ -26966,7 +26966,7 @@
         <v>31</v>
       </c>
       <c r="C317">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D317" t="s">
         <v>32</v>
@@ -26980,7 +26980,7 @@
         <v>31</v>
       </c>
       <c r="C318">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="D318" t="s">
         <v>32</v>
@@ -26994,7 +26994,7 @@
         <v>31</v>
       </c>
       <c r="C319">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D319" t="s">
         <v>32</v>
@@ -27008,7 +27008,7 @@
         <v>31</v>
       </c>
       <c r="C320">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D320" t="s">
         <v>32</v>
@@ -27022,7 +27022,7 @@
         <v>31</v>
       </c>
       <c r="C321">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="D321" t="s">
         <v>32</v>
@@ -27036,7 +27036,7 @@
         <v>31</v>
       </c>
       <c r="C322">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D322" t="s">
         <v>32</v>
@@ -27050,7 +27050,7 @@
         <v>31</v>
       </c>
       <c r="C323">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="D323" t="s">
         <v>32</v>
@@ -27064,7 +27064,7 @@
         <v>31</v>
       </c>
       <c r="C324">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D324" t="s">
         <v>32</v>
@@ -27078,7 +27078,7 @@
         <v>31</v>
       </c>
       <c r="C325">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D325" t="s">
         <v>32</v>
@@ -27092,7 +27092,7 @@
         <v>31</v>
       </c>
       <c r="C326">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D326" t="s">
         <v>32</v>
@@ -27106,7 +27106,7 @@
         <v>31</v>
       </c>
       <c r="C327">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D327" t="s">
         <v>32</v>
@@ -27120,7 +27120,7 @@
         <v>31</v>
       </c>
       <c r="C328">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D328" t="s">
         <v>32</v>
@@ -27134,7 +27134,7 @@
         <v>31</v>
       </c>
       <c r="C329">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D329" t="s">
         <v>32</v>
@@ -27148,7 +27148,7 @@
         <v>31</v>
       </c>
       <c r="C330">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D330" t="s">
         <v>32</v>
@@ -27162,7 +27162,7 @@
         <v>31</v>
       </c>
       <c r="C331">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="D331" t="s">
         <v>32</v>
@@ -27176,7 +27176,7 @@
         <v>31</v>
       </c>
       <c r="C332">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D332" t="s">
         <v>32</v>
@@ -27190,7 +27190,7 @@
         <v>31</v>
       </c>
       <c r="C333">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D333" t="s">
         <v>32</v>
@@ -27204,7 +27204,7 @@
         <v>31</v>
       </c>
       <c r="C334">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D334" t="s">
         <v>32</v>
@@ -27218,7 +27218,7 @@
         <v>31</v>
       </c>
       <c r="C335">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D335" t="s">
         <v>32</v>
@@ -27232,7 +27232,7 @@
         <v>31</v>
       </c>
       <c r="C336">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D336" t="s">
         <v>32</v>
@@ -27246,7 +27246,7 @@
         <v>31</v>
       </c>
       <c r="C337">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D337" t="s">
         <v>32</v>
@@ -27260,7 +27260,7 @@
         <v>31</v>
       </c>
       <c r="C338">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D338" t="s">
         <v>32</v>
@@ -27274,7 +27274,7 @@
         <v>31</v>
       </c>
       <c r="C339">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D339" t="s">
         <v>32</v>
@@ -27288,7 +27288,7 @@
         <v>31</v>
       </c>
       <c r="C340">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D340" t="s">
         <v>32</v>
@@ -27302,7 +27302,7 @@
         <v>31</v>
       </c>
       <c r="C341">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D341" t="s">
         <v>32</v>
@@ -27316,7 +27316,7 @@
         <v>31</v>
       </c>
       <c r="C342">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D342" t="s">
         <v>32</v>
@@ -27330,7 +27330,7 @@
         <v>31</v>
       </c>
       <c r="C343">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D343" t="s">
         <v>32</v>
@@ -27344,7 +27344,7 @@
         <v>31</v>
       </c>
       <c r="C344">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D344" t="s">
         <v>32</v>
@@ -27358,7 +27358,7 @@
         <v>31</v>
       </c>
       <c r="C345">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D345" t="s">
         <v>32</v>
@@ -27372,7 +27372,7 @@
         <v>31</v>
       </c>
       <c r="C346">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D346" t="s">
         <v>32</v>
@@ -27386,7 +27386,7 @@
         <v>31</v>
       </c>
       <c r="C347">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D347" t="s">
         <v>32</v>
@@ -27400,7 +27400,7 @@
         <v>31</v>
       </c>
       <c r="C348">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D348" t="s">
         <v>32</v>
@@ -27414,7 +27414,7 @@
         <v>31</v>
       </c>
       <c r="C349">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D349" t="s">
         <v>32</v>
@@ -27428,7 +27428,7 @@
         <v>31</v>
       </c>
       <c r="C350">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D350" t="s">
         <v>32</v>
@@ -27442,7 +27442,7 @@
         <v>31</v>
       </c>
       <c r="C351">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D351" t="s">
         <v>32</v>
@@ -27456,7 +27456,7 @@
         <v>31</v>
       </c>
       <c r="C352">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D352" t="s">
         <v>32</v>
@@ -27470,7 +27470,7 @@
         <v>31</v>
       </c>
       <c r="C353">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D353" t="s">
         <v>32</v>
@@ -27484,7 +27484,7 @@
         <v>31</v>
       </c>
       <c r="C354">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D354" t="s">
         <v>32</v>
@@ -27498,7 +27498,7 @@
         <v>31</v>
       </c>
       <c r="C355">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D355" t="s">
         <v>32</v>
@@ -27512,7 +27512,7 @@
         <v>31</v>
       </c>
       <c r="C356">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D356" t="s">
         <v>32</v>
@@ -27526,7 +27526,7 @@
         <v>31</v>
       </c>
       <c r="C357">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="D357" t="s">
         <v>32</v>
@@ -27540,7 +27540,7 @@
         <v>31</v>
       </c>
       <c r="C358">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D358" t="s">
         <v>32</v>
@@ -27554,7 +27554,7 @@
         <v>31</v>
       </c>
       <c r="C359">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D359" t="s">
         <v>32</v>
@@ -27582,7 +27582,7 @@
         <v>31</v>
       </c>
       <c r="C361">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D361" t="s">
         <v>32</v>
@@ -27596,7 +27596,7 @@
         <v>31</v>
       </c>
       <c r="C362">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D362" t="s">
         <v>32</v>
@@ -27610,7 +27610,7 @@
         <v>31</v>
       </c>
       <c r="C363">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D363" t="s">
         <v>32</v>
@@ -27624,7 +27624,7 @@
         <v>31</v>
       </c>
       <c r="C364">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D364" t="s">
         <v>32</v>
@@ -27638,7 +27638,7 @@
         <v>31</v>
       </c>
       <c r="C365">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D365" t="s">
         <v>32</v>
@@ -27652,7 +27652,7 @@
         <v>31</v>
       </c>
       <c r="C366">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D366" t="s">
         <v>32</v>
@@ -27666,7 +27666,7 @@
         <v>31</v>
       </c>
       <c r="C367">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D367" t="s">
         <v>32</v>
@@ -27680,7 +27680,7 @@
         <v>31</v>
       </c>
       <c r="C368">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D368" t="s">
         <v>32</v>
@@ -27694,7 +27694,7 @@
         <v>31</v>
       </c>
       <c r="C369">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D369" t="s">
         <v>32</v>
@@ -27708,7 +27708,7 @@
         <v>31</v>
       </c>
       <c r="C370">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="D370" t="s">
         <v>32</v>
@@ -27722,7 +27722,7 @@
         <v>31</v>
       </c>
       <c r="C371">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D371" t="s">
         <v>32</v>
@@ -27736,7 +27736,7 @@
         <v>31</v>
       </c>
       <c r="C372">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D372" t="s">
         <v>32</v>
@@ -27750,7 +27750,7 @@
         <v>31</v>
       </c>
       <c r="C373">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="D373" t="s">
         <v>32</v>
@@ -27764,7 +27764,7 @@
         <v>31</v>
       </c>
       <c r="C374">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D374" t="s">
         <v>32</v>
@@ -27778,7 +27778,7 @@
         <v>31</v>
       </c>
       <c r="C375">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="D375" t="s">
         <v>32</v>
@@ -27806,7 +27806,7 @@
         <v>31</v>
       </c>
       <c r="C377">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D377" t="s">
         <v>32</v>
@@ -27820,7 +27820,7 @@
         <v>31</v>
       </c>
       <c r="C378">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D378" t="s">
         <v>32</v>
@@ -27834,7 +27834,7 @@
         <v>31</v>
       </c>
       <c r="C379">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D379" t="s">
         <v>32</v>
@@ -27848,7 +27848,7 @@
         <v>31</v>
       </c>
       <c r="C380">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D380" t="s">
         <v>32</v>
@@ -27862,7 +27862,7 @@
         <v>31</v>
       </c>
       <c r="C381">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D381" t="s">
         <v>32</v>
@@ -27876,7 +27876,7 @@
         <v>31</v>
       </c>
       <c r="C382">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D382" t="s">
         <v>32</v>
@@ -27890,7 +27890,7 @@
         <v>31</v>
       </c>
       <c r="C383">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D383" t="s">
         <v>32</v>
@@ -27904,7 +27904,7 @@
         <v>31</v>
       </c>
       <c r="C384">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D384" t="s">
         <v>32</v>
@@ -27918,7 +27918,7 @@
         <v>31</v>
       </c>
       <c r="C385">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D385" t="s">
         <v>32</v>
@@ -27932,7 +27932,7 @@
         <v>31</v>
       </c>
       <c r="C386">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D386" t="s">
         <v>32</v>
@@ -27946,7 +27946,7 @@
         <v>31</v>
       </c>
       <c r="C387">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="D387" t="s">
         <v>32</v>
@@ -27960,7 +27960,7 @@
         <v>31</v>
       </c>
       <c r="C388">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D388" t="s">
         <v>32</v>
@@ -27974,7 +27974,7 @@
         <v>31</v>
       </c>
       <c r="C389">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D389" t="s">
         <v>32</v>
@@ -27988,7 +27988,7 @@
         <v>31</v>
       </c>
       <c r="C390">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D390" t="s">
         <v>32</v>
@@ -28002,7 +28002,7 @@
         <v>31</v>
       </c>
       <c r="C391">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D391" t="s">
         <v>32</v>
@@ -28016,7 +28016,7 @@
         <v>31</v>
       </c>
       <c r="C392">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D392" t="s">
         <v>32</v>
@@ -28030,7 +28030,7 @@
         <v>31</v>
       </c>
       <c r="C393">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D393" t="s">
         <v>32</v>
@@ -28044,7 +28044,7 @@
         <v>31</v>
       </c>
       <c r="C394">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="D394" t="s">
         <v>32</v>
@@ -28058,7 +28058,7 @@
         <v>31</v>
       </c>
       <c r="C395">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D395" t="s">
         <v>32</v>
@@ -28072,7 +28072,7 @@
         <v>31</v>
       </c>
       <c r="C396">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D396" t="s">
         <v>32</v>
@@ -28086,7 +28086,7 @@
         <v>31</v>
       </c>
       <c r="C397">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="D397" t="s">
         <v>32</v>
@@ -28114,7 +28114,7 @@
         <v>31</v>
       </c>
       <c r="C399">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D399" t="s">
         <v>32</v>
@@ -28128,7 +28128,7 @@
         <v>31</v>
       </c>
       <c r="C400">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="D400" t="s">
         <v>32</v>
@@ -28142,7 +28142,7 @@
         <v>31</v>
       </c>
       <c r="C401">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="D401" t="s">
         <v>32</v>

--- a/unified-summary.xlsx
+++ b/unified-summary.xlsx
@@ -23,13 +23,13 @@
     <t>Build Number:</t>
   </si>
   <si>
-    <t>#2</t>
+    <t>#3</t>
   </si>
   <si>
     <t>Execution Date:</t>
   </si>
   <si>
-    <t>2026-07-19 18:21:02 UTC</t>
+    <t>2026-07-19 18:39:36 UTC</t>
   </si>
   <si>
     <t>Branch:</t>
@@ -6075,7 +6075,7 @@
         <v>31</v>
       </c>
       <c r="C2">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
         <v>32</v>
@@ -6089,7 +6089,7 @@
         <v>31</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
         <v>32</v>
@@ -6103,7 +6103,7 @@
         <v>31</v>
       </c>
       <c r="C4">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
@@ -6117,7 +6117,7 @@
         <v>31</v>
       </c>
       <c r="C5">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
         <v>32</v>
@@ -6131,7 +6131,7 @@
         <v>31</v>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
         <v>32</v>
@@ -6145,7 +6145,7 @@
         <v>31</v>
       </c>
       <c r="C7">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
@@ -6159,7 +6159,7 @@
         <v>31</v>
       </c>
       <c r="C8">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D8" t="s">
         <v>32</v>
@@ -6173,7 +6173,7 @@
         <v>31</v>
       </c>
       <c r="C9">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
         <v>32</v>
@@ -6187,7 +6187,7 @@
         <v>31</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
         <v>32</v>
@@ -6201,7 +6201,7 @@
         <v>31</v>
       </c>
       <c r="C11">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
@@ -6215,7 +6215,7 @@
         <v>31</v>
       </c>
       <c r="C12">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
         <v>32</v>
@@ -6229,7 +6229,7 @@
         <v>31</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
         <v>32</v>
@@ -6243,7 +6243,7 @@
         <v>31</v>
       </c>
       <c r="C14">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D14" t="s">
         <v>32</v>
@@ -6257,7 +6257,7 @@
         <v>31</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="D15" t="s">
         <v>32</v>
@@ -6271,7 +6271,7 @@
         <v>31</v>
       </c>
       <c r="C16">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D16" t="s">
         <v>32</v>
@@ -6285,7 +6285,7 @@
         <v>31</v>
       </c>
       <c r="C17">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D17" t="s">
         <v>32</v>
@@ -6299,7 +6299,7 @@
         <v>31</v>
       </c>
       <c r="C18">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D18" t="s">
         <v>32</v>
@@ -6313,7 +6313,7 @@
         <v>31</v>
       </c>
       <c r="C19">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D19" t="s">
         <v>32</v>
@@ -6327,7 +6327,7 @@
         <v>31</v>
       </c>
       <c r="C20">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D20" t="s">
         <v>32</v>
@@ -6341,7 +6341,7 @@
         <v>31</v>
       </c>
       <c r="C21">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D21" t="s">
         <v>32</v>
@@ -6355,7 +6355,7 @@
         <v>31</v>
       </c>
       <c r="C22">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D22" t="s">
         <v>32</v>
@@ -6369,7 +6369,7 @@
         <v>31</v>
       </c>
       <c r="C23">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D23" t="s">
         <v>32</v>
@@ -6383,7 +6383,7 @@
         <v>31</v>
       </c>
       <c r="C24">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D24" t="s">
         <v>32</v>
@@ -6397,7 +6397,7 @@
         <v>31</v>
       </c>
       <c r="C25">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s">
         <v>32</v>
@@ -6411,7 +6411,7 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D26" t="s">
         <v>32</v>
@@ -6425,7 +6425,7 @@
         <v>31</v>
       </c>
       <c r="C27">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="D27" t="s">
         <v>32</v>
@@ -6439,7 +6439,7 @@
         <v>31</v>
       </c>
       <c r="C28">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D28" t="s">
         <v>32</v>
@@ -6453,7 +6453,7 @@
         <v>31</v>
       </c>
       <c r="C29">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="D29" t="s">
         <v>32</v>
@@ -6467,7 +6467,7 @@
         <v>31</v>
       </c>
       <c r="C30">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D30" t="s">
         <v>32</v>
@@ -6481,7 +6481,7 @@
         <v>31</v>
       </c>
       <c r="C31">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D31" t="s">
         <v>32</v>
@@ -6495,7 +6495,7 @@
         <v>31</v>
       </c>
       <c r="C32">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D32" t="s">
         <v>32</v>
@@ -6509,7 +6509,7 @@
         <v>31</v>
       </c>
       <c r="C33">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D33" t="s">
         <v>32</v>
@@ -6523,7 +6523,7 @@
         <v>31</v>
       </c>
       <c r="C34">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D34" t="s">
         <v>32</v>
@@ -6537,7 +6537,7 @@
         <v>31</v>
       </c>
       <c r="C35">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D35" t="s">
         <v>32</v>
@@ -6551,7 +6551,7 @@
         <v>31</v>
       </c>
       <c r="C36">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D36" t="s">
         <v>32</v>
@@ -6565,7 +6565,7 @@
         <v>31</v>
       </c>
       <c r="C37">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D37" t="s">
         <v>32</v>
@@ -6579,7 +6579,7 @@
         <v>31</v>
       </c>
       <c r="C38">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D38" t="s">
         <v>32</v>
@@ -6593,7 +6593,7 @@
         <v>31</v>
       </c>
       <c r="C39">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D39" t="s">
         <v>32</v>
@@ -6607,7 +6607,7 @@
         <v>31</v>
       </c>
       <c r="C40">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D40" t="s">
         <v>32</v>
@@ -6621,7 +6621,7 @@
         <v>31</v>
       </c>
       <c r="C41">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D41" t="s">
         <v>32</v>
@@ -6635,7 +6635,7 @@
         <v>31</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D42" t="s">
         <v>32</v>
@@ -6649,7 +6649,7 @@
         <v>31</v>
       </c>
       <c r="C43">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="D43" t="s">
         <v>32</v>
@@ -6663,7 +6663,7 @@
         <v>31</v>
       </c>
       <c r="C44">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="D44" t="s">
         <v>32</v>
@@ -6677,7 +6677,7 @@
         <v>31</v>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D45" t="s">
         <v>32</v>
@@ -6691,7 +6691,7 @@
         <v>31</v>
       </c>
       <c r="C46">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D46" t="s">
         <v>32</v>
@@ -6705,7 +6705,7 @@
         <v>31</v>
       </c>
       <c r="C47">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D47" t="s">
         <v>32</v>
@@ -6719,7 +6719,7 @@
         <v>31</v>
       </c>
       <c r="C48">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D48" t="s">
         <v>32</v>
@@ -6733,7 +6733,7 @@
         <v>31</v>
       </c>
       <c r="C49">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="D49" t="s">
         <v>32</v>
@@ -6747,7 +6747,7 @@
         <v>31</v>
       </c>
       <c r="C50">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="D50" t="s">
         <v>32</v>
@@ -6761,7 +6761,7 @@
         <v>31</v>
       </c>
       <c r="C51">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D51" t="s">
         <v>32</v>
@@ -6775,7 +6775,7 @@
         <v>31</v>
       </c>
       <c r="C52">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D52" t="s">
         <v>32</v>
@@ -6789,7 +6789,7 @@
         <v>31</v>
       </c>
       <c r="C53">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D53" t="s">
         <v>32</v>
@@ -6803,7 +6803,7 @@
         <v>31</v>
       </c>
       <c r="C54">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D54" t="s">
         <v>32</v>
@@ -6817,7 +6817,7 @@
         <v>31</v>
       </c>
       <c r="C55">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="D55" t="s">
         <v>32</v>
@@ -6831,7 +6831,7 @@
         <v>31</v>
       </c>
       <c r="C56">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D56" t="s">
         <v>32</v>
@@ -6845,7 +6845,7 @@
         <v>31</v>
       </c>
       <c r="C57">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D57" t="s">
         <v>32</v>
@@ -6859,7 +6859,7 @@
         <v>31</v>
       </c>
       <c r="C58">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D58" t="s">
         <v>32</v>
@@ -6873,7 +6873,7 @@
         <v>31</v>
       </c>
       <c r="C59">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D59" t="s">
         <v>32</v>
@@ -6887,7 +6887,7 @@
         <v>31</v>
       </c>
       <c r="C60">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D60" t="s">
         <v>32</v>
@@ -6901,7 +6901,7 @@
         <v>31</v>
       </c>
       <c r="C61">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D61" t="s">
         <v>32</v>
@@ -6915,7 +6915,7 @@
         <v>31</v>
       </c>
       <c r="C62">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D62" t="s">
         <v>32</v>
@@ -6929,7 +6929,7 @@
         <v>31</v>
       </c>
       <c r="C63">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="D63" t="s">
         <v>32</v>
@@ -6943,7 +6943,7 @@
         <v>31</v>
       </c>
       <c r="C64">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D64" t="s">
         <v>32</v>
@@ -6957,7 +6957,7 @@
         <v>31</v>
       </c>
       <c r="C65">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D65" t="s">
         <v>32</v>
@@ -6971,7 +6971,7 @@
         <v>31</v>
       </c>
       <c r="C66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D66" t="s">
         <v>32</v>
@@ -6985,7 +6985,7 @@
         <v>31</v>
       </c>
       <c r="C67">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="D67" t="s">
         <v>32</v>
@@ -6999,7 +6999,7 @@
         <v>31</v>
       </c>
       <c r="C68">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D68" t="s">
         <v>32</v>
@@ -7013,7 +7013,7 @@
         <v>31</v>
       </c>
       <c r="C69">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D69" t="s">
         <v>32</v>
@@ -7041,7 +7041,7 @@
         <v>31</v>
       </c>
       <c r="C71">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D71" t="s">
         <v>32</v>
@@ -7055,7 +7055,7 @@
         <v>31</v>
       </c>
       <c r="C72">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D72" t="s">
         <v>32</v>
@@ -7069,7 +7069,7 @@
         <v>31</v>
       </c>
       <c r="C73">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="D73" t="s">
         <v>32</v>
@@ -7083,7 +7083,7 @@
         <v>31</v>
       </c>
       <c r="C74">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="D74" t="s">
         <v>32</v>
@@ -7097,7 +7097,7 @@
         <v>31</v>
       </c>
       <c r="C75">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D75" t="s">
         <v>32</v>
@@ -7111,7 +7111,7 @@
         <v>31</v>
       </c>
       <c r="C76">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D76" t="s">
         <v>32</v>
@@ -7125,7 +7125,7 @@
         <v>31</v>
       </c>
       <c r="C77">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D77" t="s">
         <v>32</v>
@@ -7139,7 +7139,7 @@
         <v>31</v>
       </c>
       <c r="C78">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D78" t="s">
         <v>32</v>
@@ -7153,7 +7153,7 @@
         <v>31</v>
       </c>
       <c r="C79">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D79" t="s">
         <v>32</v>
@@ -7167,7 +7167,7 @@
         <v>31</v>
       </c>
       <c r="C80">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="D80" t="s">
         <v>32</v>
@@ -7181,7 +7181,7 @@
         <v>31</v>
       </c>
       <c r="C81">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D81" t="s">
         <v>32</v>
@@ -7195,7 +7195,7 @@
         <v>31</v>
       </c>
       <c r="C82">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="D82" t="s">
         <v>32</v>
@@ -7209,7 +7209,7 @@
         <v>31</v>
       </c>
       <c r="C83">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="D83" t="s">
         <v>32</v>
@@ -7223,7 +7223,7 @@
         <v>31</v>
       </c>
       <c r="C84">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D84" t="s">
         <v>32</v>
@@ -7237,7 +7237,7 @@
         <v>31</v>
       </c>
       <c r="C85">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D85" t="s">
         <v>32</v>
@@ -7251,7 +7251,7 @@
         <v>31</v>
       </c>
       <c r="C86">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="D86" t="s">
         <v>32</v>
@@ -7265,7 +7265,7 @@
         <v>31</v>
       </c>
       <c r="C87">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D87" t="s">
         <v>32</v>
@@ -7279,7 +7279,7 @@
         <v>31</v>
       </c>
       <c r="C88">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D88" t="s">
         <v>32</v>
@@ -7293,7 +7293,7 @@
         <v>31</v>
       </c>
       <c r="C89">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="D89" t="s">
         <v>32</v>
@@ -7307,7 +7307,7 @@
         <v>31</v>
       </c>
       <c r="C90">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D90" t="s">
         <v>32</v>
@@ -7321,7 +7321,7 @@
         <v>31</v>
       </c>
       <c r="C91">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D91" t="s">
         <v>32</v>
@@ -7335,7 +7335,7 @@
         <v>31</v>
       </c>
       <c r="C92">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D92" t="s">
         <v>32</v>
@@ -7349,7 +7349,7 @@
         <v>31</v>
       </c>
       <c r="C93">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="D93" t="s">
         <v>32</v>
@@ -7363,7 +7363,7 @@
         <v>31</v>
       </c>
       <c r="C94">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D94" t="s">
         <v>32</v>
@@ -7377,7 +7377,7 @@
         <v>31</v>
       </c>
       <c r="C95">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D95" t="s">
         <v>32</v>
@@ -7391,7 +7391,7 @@
         <v>31</v>
       </c>
       <c r="C96">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D96" t="s">
         <v>32</v>
@@ -7405,7 +7405,7 @@
         <v>31</v>
       </c>
       <c r="C97">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D97" t="s">
         <v>32</v>
@@ -7419,7 +7419,7 @@
         <v>31</v>
       </c>
       <c r="C98">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D98" t="s">
         <v>32</v>
@@ -7433,7 +7433,7 @@
         <v>31</v>
       </c>
       <c r="C99">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="D99" t="s">
         <v>32</v>
@@ -7447,7 +7447,7 @@
         <v>31</v>
       </c>
       <c r="C100">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D100" t="s">
         <v>32</v>
@@ -7461,7 +7461,7 @@
         <v>31</v>
       </c>
       <c r="C101">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D101" t="s">
         <v>32</v>
@@ -7475,7 +7475,7 @@
         <v>31</v>
       </c>
       <c r="C102">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="D102" t="s">
         <v>32</v>
@@ -7489,7 +7489,7 @@
         <v>31</v>
       </c>
       <c r="C103">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="D103" t="s">
         <v>32</v>
@@ -7503,7 +7503,7 @@
         <v>31</v>
       </c>
       <c r="C104">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D104" t="s">
         <v>32</v>
@@ -7517,7 +7517,7 @@
         <v>31</v>
       </c>
       <c r="C105">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D105" t="s">
         <v>32</v>
@@ -7531,7 +7531,7 @@
         <v>31</v>
       </c>
       <c r="C106">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="D106" t="s">
         <v>32</v>
@@ -7545,7 +7545,7 @@
         <v>31</v>
       </c>
       <c r="C107">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D107" t="s">
         <v>32</v>
@@ -7559,7 +7559,7 @@
         <v>31</v>
       </c>
       <c r="C108">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D108" t="s">
         <v>32</v>
@@ -7573,7 +7573,7 @@
         <v>31</v>
       </c>
       <c r="C109">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D109" t="s">
         <v>32</v>
@@ -7587,7 +7587,7 @@
         <v>31</v>
       </c>
       <c r="C110">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="D110" t="s">
         <v>32</v>
@@ -7601,7 +7601,7 @@
         <v>31</v>
       </c>
       <c r="C111">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D111" t="s">
         <v>32</v>
@@ -7615,7 +7615,7 @@
         <v>31</v>
       </c>
       <c r="C112">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="D112" t="s">
         <v>32</v>
@@ -7629,7 +7629,7 @@
         <v>31</v>
       </c>
       <c r="C113">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D113" t="s">
         <v>32</v>
@@ -7643,7 +7643,7 @@
         <v>31</v>
       </c>
       <c r="C114">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D114" t="s">
         <v>32</v>
@@ -7657,7 +7657,7 @@
         <v>31</v>
       </c>
       <c r="C115">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D115" t="s">
         <v>32</v>
@@ -7671,7 +7671,7 @@
         <v>31</v>
       </c>
       <c r="C116">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="D116" t="s">
         <v>32</v>
@@ -7685,7 +7685,7 @@
         <v>31</v>
       </c>
       <c r="C117">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="D117" t="s">
         <v>32</v>
@@ -7699,7 +7699,7 @@
         <v>31</v>
       </c>
       <c r="C118">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="D118" t="s">
         <v>32</v>
@@ -7713,7 +7713,7 @@
         <v>31</v>
       </c>
       <c r="C119">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="D119" t="s">
         <v>32</v>
@@ -7727,7 +7727,7 @@
         <v>31</v>
       </c>
       <c r="C120">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D120" t="s">
         <v>32</v>
@@ -7741,7 +7741,7 @@
         <v>31</v>
       </c>
       <c r="C121">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="D121" t="s">
         <v>32</v>
@@ -7755,7 +7755,7 @@
         <v>31</v>
       </c>
       <c r="C122">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="D122" t="s">
         <v>32</v>
@@ -7769,7 +7769,7 @@
         <v>31</v>
       </c>
       <c r="C123">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D123" t="s">
         <v>32</v>
@@ -7783,7 +7783,7 @@
         <v>31</v>
       </c>
       <c r="C124">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D124" t="s">
         <v>32</v>
@@ -7797,7 +7797,7 @@
         <v>31</v>
       </c>
       <c r="C125">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D125" t="s">
         <v>32</v>
@@ -7811,7 +7811,7 @@
         <v>31</v>
       </c>
       <c r="C126">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="D126" t="s">
         <v>32</v>
@@ -7825,7 +7825,7 @@
         <v>31</v>
       </c>
       <c r="C127">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D127" t="s">
         <v>32</v>
@@ -7839,7 +7839,7 @@
         <v>31</v>
       </c>
       <c r="C128">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D128" t="s">
         <v>32</v>
@@ -7853,7 +7853,7 @@
         <v>31</v>
       </c>
       <c r="C129">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="D129" t="s">
         <v>32</v>
@@ -7867,7 +7867,7 @@
         <v>31</v>
       </c>
       <c r="C130">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="D130" t="s">
         <v>32</v>
@@ -7881,7 +7881,7 @@
         <v>31</v>
       </c>
       <c r="C131">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D131" t="s">
         <v>32</v>
@@ -7895,7 +7895,7 @@
         <v>31</v>
       </c>
       <c r="C132">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="D132" t="s">
         <v>32</v>
@@ -7909,7 +7909,7 @@
         <v>31</v>
       </c>
       <c r="C133">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D133" t="s">
         <v>32</v>
@@ -7923,7 +7923,7 @@
         <v>31</v>
       </c>
       <c r="C134">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="D134" t="s">
         <v>32</v>
@@ -7937,7 +7937,7 @@
         <v>31</v>
       </c>
       <c r="C135">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D135" t="s">
         <v>32</v>
@@ -7951,7 +7951,7 @@
         <v>31</v>
       </c>
       <c r="C136">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D136" t="s">
         <v>32</v>
@@ -7965,7 +7965,7 @@
         <v>31</v>
       </c>
       <c r="C137">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D137" t="s">
         <v>32</v>
@@ -7979,7 +7979,7 @@
         <v>31</v>
       </c>
       <c r="C138">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="D138" t="s">
         <v>32</v>
@@ -7993,7 +7993,7 @@
         <v>31</v>
       </c>
       <c r="C139">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D139" t="s">
         <v>32</v>
@@ -8007,7 +8007,7 @@
         <v>31</v>
       </c>
       <c r="C140">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D140" t="s">
         <v>32</v>
@@ -8021,7 +8021,7 @@
         <v>31</v>
       </c>
       <c r="C141">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D141" t="s">
         <v>32</v>
@@ -8035,7 +8035,7 @@
         <v>31</v>
       </c>
       <c r="C142">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D142" t="s">
         <v>32</v>
@@ -8049,7 +8049,7 @@
         <v>31</v>
       </c>
       <c r="C143">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D143" t="s">
         <v>32</v>
@@ -8063,7 +8063,7 @@
         <v>31</v>
       </c>
       <c r="C144">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="D144" t="s">
         <v>32</v>
@@ -8077,7 +8077,7 @@
         <v>31</v>
       </c>
       <c r="C145">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="D145" t="s">
         <v>32</v>
@@ -8091,7 +8091,7 @@
         <v>31</v>
       </c>
       <c r="C146">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D146" t="s">
         <v>32</v>
@@ -8105,7 +8105,7 @@
         <v>31</v>
       </c>
       <c r="C147">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="D147" t="s">
         <v>32</v>
@@ -8119,7 +8119,7 @@
         <v>31</v>
       </c>
       <c r="C148">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="D148" t="s">
         <v>32</v>
@@ -8133,7 +8133,7 @@
         <v>31</v>
       </c>
       <c r="C149">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D149" t="s">
         <v>32</v>
@@ -8147,7 +8147,7 @@
         <v>31</v>
       </c>
       <c r="C150">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D150" t="s">
         <v>32</v>
@@ -8161,7 +8161,7 @@
         <v>31</v>
       </c>
       <c r="C151">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D151" t="s">
         <v>32</v>
@@ -8175,7 +8175,7 @@
         <v>31</v>
       </c>
       <c r="C152">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D152" t="s">
         <v>32</v>
@@ -8189,7 +8189,7 @@
         <v>31</v>
       </c>
       <c r="C153">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D153" t="s">
         <v>32</v>
@@ -8217,7 +8217,7 @@
         <v>31</v>
       </c>
       <c r="C155">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D155" t="s">
         <v>32</v>
@@ -8231,7 +8231,7 @@
         <v>31</v>
       </c>
       <c r="C156">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D156" t="s">
         <v>32</v>
@@ -8245,7 +8245,7 @@
         <v>31</v>
       </c>
       <c r="C157">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="D157" t="s">
         <v>32</v>
@@ -8259,7 +8259,7 @@
         <v>31</v>
       </c>
       <c r="C158">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D158" t="s">
         <v>32</v>
@@ -8273,7 +8273,7 @@
         <v>31</v>
       </c>
       <c r="C159">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="D159" t="s">
         <v>32</v>
@@ -8287,7 +8287,7 @@
         <v>31</v>
       </c>
       <c r="C160">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="D160" t="s">
         <v>32</v>
@@ -8301,7 +8301,7 @@
         <v>31</v>
       </c>
       <c r="C161">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D161" t="s">
         <v>32</v>
@@ -8315,7 +8315,7 @@
         <v>31</v>
       </c>
       <c r="C162">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="D162" t="s">
         <v>32</v>
@@ -8329,7 +8329,7 @@
         <v>31</v>
       </c>
       <c r="C163">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D163" t="s">
         <v>32</v>
@@ -8343,7 +8343,7 @@
         <v>31</v>
       </c>
       <c r="C164">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="D164" t="s">
         <v>32</v>
@@ -8357,7 +8357,7 @@
         <v>31</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="D165" t="s">
         <v>32</v>
@@ -8371,7 +8371,7 @@
         <v>31</v>
       </c>
       <c r="C166">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="D166" t="s">
         <v>32</v>
@@ -8385,7 +8385,7 @@
         <v>31</v>
       </c>
       <c r="C167">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D167" t="s">
         <v>32</v>
@@ -8399,7 +8399,7 @@
         <v>31</v>
       </c>
       <c r="C168">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D168" t="s">
         <v>32</v>
@@ -8413,7 +8413,7 @@
         <v>31</v>
       </c>
       <c r="C169">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D169" t="s">
         <v>32</v>
@@ -8427,7 +8427,7 @@
         <v>31</v>
       </c>
       <c r="C170">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D170" t="s">
         <v>32</v>
@@ -8441,7 +8441,7 @@
         <v>31</v>
       </c>
       <c r="C171">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D171" t="s">
         <v>32</v>
@@ -8455,7 +8455,7 @@
         <v>31</v>
       </c>
       <c r="C172">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D172" t="s">
         <v>32</v>
@@ -8469,7 +8469,7 @@
         <v>31</v>
       </c>
       <c r="C173">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D173" t="s">
         <v>32</v>
@@ -8483,7 +8483,7 @@
         <v>31</v>
       </c>
       <c r="C174">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D174" t="s">
         <v>32</v>
@@ -8497,7 +8497,7 @@
         <v>31</v>
       </c>
       <c r="C175">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="D175" t="s">
         <v>32</v>
@@ -8511,7 +8511,7 @@
         <v>31</v>
       </c>
       <c r="C176">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D176" t="s">
         <v>32</v>
@@ -8525,7 +8525,7 @@
         <v>31</v>
       </c>
       <c r="C177">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D177" t="s">
         <v>32</v>
@@ -8539,7 +8539,7 @@
         <v>31</v>
       </c>
       <c r="C178">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="D178" t="s">
         <v>32</v>
@@ -8553,7 +8553,7 @@
         <v>31</v>
       </c>
       <c r="C179">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="D179" t="s">
         <v>32</v>
@@ -8567,7 +8567,7 @@
         <v>31</v>
       </c>
       <c r="C180">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D180" t="s">
         <v>32</v>
@@ -8581,7 +8581,7 @@
         <v>31</v>
       </c>
       <c r="C181">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D181" t="s">
         <v>32</v>
@@ -8595,7 +8595,7 @@
         <v>31</v>
       </c>
       <c r="C182">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D182" t="s">
         <v>32</v>
@@ -8609,7 +8609,7 @@
         <v>31</v>
       </c>
       <c r="C183">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="D183" t="s">
         <v>32</v>
@@ -8623,7 +8623,7 @@
         <v>31</v>
       </c>
       <c r="C184">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="D184" t="s">
         <v>32</v>
@@ -8637,7 +8637,7 @@
         <v>31</v>
       </c>
       <c r="C185">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D185" t="s">
         <v>32</v>
@@ -8651,7 +8651,7 @@
         <v>31</v>
       </c>
       <c r="C186">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="D186" t="s">
         <v>32</v>
@@ -8665,7 +8665,7 @@
         <v>31</v>
       </c>
       <c r="C187">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D187" t="s">
         <v>32</v>
@@ -8679,7 +8679,7 @@
         <v>31</v>
       </c>
       <c r="C188">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D188" t="s">
         <v>32</v>
@@ -8693,7 +8693,7 @@
         <v>31</v>
       </c>
       <c r="C189">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D189" t="s">
         <v>32</v>
@@ -8707,7 +8707,7 @@
         <v>31</v>
       </c>
       <c r="C190">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="D190" t="s">
         <v>32</v>
@@ -8721,7 +8721,7 @@
         <v>31</v>
       </c>
       <c r="C191">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D191" t="s">
         <v>32</v>
@@ -8735,7 +8735,7 @@
         <v>31</v>
       </c>
       <c r="C192">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D192" t="s">
         <v>32</v>
@@ -8749,7 +8749,7 @@
         <v>31</v>
       </c>
       <c r="C193">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D193" t="s">
         <v>32</v>
@@ -8763,7 +8763,7 @@
         <v>31</v>
       </c>
       <c r="C194">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D194" t="s">
         <v>32</v>
@@ -8777,7 +8777,7 @@
         <v>31</v>
       </c>
       <c r="C195">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D195" t="s">
         <v>32</v>
@@ -8791,7 +8791,7 @@
         <v>31</v>
       </c>
       <c r="C196">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D196" t="s">
         <v>32</v>
@@ -8805,7 +8805,7 @@
         <v>31</v>
       </c>
       <c r="C197">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="D197" t="s">
         <v>32</v>
@@ -8819,7 +8819,7 @@
         <v>31</v>
       </c>
       <c r="C198">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="D198" t="s">
         <v>32</v>
@@ -8833,7 +8833,7 @@
         <v>31</v>
       </c>
       <c r="C199">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D199" t="s">
         <v>32</v>
@@ -8847,7 +8847,7 @@
         <v>31</v>
       </c>
       <c r="C200">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D200" t="s">
         <v>32</v>
@@ -8861,7 +8861,7 @@
         <v>31</v>
       </c>
       <c r="C201">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D201" t="s">
         <v>32</v>
@@ -8875,7 +8875,7 @@
         <v>31</v>
       </c>
       <c r="C202">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D202" t="s">
         <v>32</v>
@@ -8889,7 +8889,7 @@
         <v>31</v>
       </c>
       <c r="C203">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D203" t="s">
         <v>32</v>
@@ -8903,7 +8903,7 @@
         <v>31</v>
       </c>
       <c r="C204">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="D204" t="s">
         <v>32</v>
@@ -8917,7 +8917,7 @@
         <v>31</v>
       </c>
       <c r="C205">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D205" t="s">
         <v>32</v>
@@ -8931,7 +8931,7 @@
         <v>31</v>
       </c>
       <c r="C206">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D206" t="s">
         <v>32</v>
@@ -8945,7 +8945,7 @@
         <v>31</v>
       </c>
       <c r="C207">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D207" t="s">
         <v>32</v>
@@ -8959,7 +8959,7 @@
         <v>31</v>
       </c>
       <c r="C208">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D208" t="s">
         <v>32</v>
@@ -8973,7 +8973,7 @@
         <v>31</v>
       </c>
       <c r="C209">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D209" t="s">
         <v>32</v>
@@ -8987,7 +8987,7 @@
         <v>31</v>
       </c>
       <c r="C210">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="D210" t="s">
         <v>32</v>
@@ -9001,7 +9001,7 @@
         <v>31</v>
       </c>
       <c r="C211">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="D211" t="s">
         <v>32</v>
@@ -9015,7 +9015,7 @@
         <v>31</v>
       </c>
       <c r="C212">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="D212" t="s">
         <v>32</v>
@@ -9029,7 +9029,7 @@
         <v>31</v>
       </c>
       <c r="C213">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="D213" t="s">
         <v>32</v>
@@ -9043,7 +9043,7 @@
         <v>31</v>
       </c>
       <c r="C214">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D214" t="s">
         <v>32</v>
@@ -9057,7 +9057,7 @@
         <v>31</v>
       </c>
       <c r="C215">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D215" t="s">
         <v>32</v>
@@ -9071,7 +9071,7 @@
         <v>31</v>
       </c>
       <c r="C216">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D216" t="s">
         <v>32</v>
@@ -9099,7 +9099,7 @@
         <v>31</v>
       </c>
       <c r="C218">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D218" t="s">
         <v>32</v>
@@ -9113,7 +9113,7 @@
         <v>31</v>
       </c>
       <c r="C219">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D219" t="s">
         <v>32</v>
@@ -9127,7 +9127,7 @@
         <v>31</v>
       </c>
       <c r="C220">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="D220" t="s">
         <v>32</v>
@@ -9141,7 +9141,7 @@
         <v>31</v>
       </c>
       <c r="C221">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D221" t="s">
         <v>32</v>
@@ -9155,7 +9155,7 @@
         <v>31</v>
       </c>
       <c r="C222">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="D222" t="s">
         <v>32</v>
@@ -9169,7 +9169,7 @@
         <v>31</v>
       </c>
       <c r="C223">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D223" t="s">
         <v>32</v>
@@ -9183,7 +9183,7 @@
         <v>31</v>
       </c>
       <c r="C224">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D224" t="s">
         <v>32</v>
@@ -9197,7 +9197,7 @@
         <v>31</v>
       </c>
       <c r="C225">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D225" t="s">
         <v>32</v>
@@ -9211,7 +9211,7 @@
         <v>31</v>
       </c>
       <c r="C226">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="D226" t="s">
         <v>32</v>
@@ -9225,7 +9225,7 @@
         <v>31</v>
       </c>
       <c r="C227">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D227" t="s">
         <v>32</v>
@@ -9239,7 +9239,7 @@
         <v>31</v>
       </c>
       <c r="C228">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D228" t="s">
         <v>32</v>
@@ -9253,7 +9253,7 @@
         <v>31</v>
       </c>
       <c r="C229">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D229" t="s">
         <v>32</v>
@@ -9267,7 +9267,7 @@
         <v>31</v>
       </c>
       <c r="C230">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D230" t="s">
         <v>32</v>
@@ -9281,7 +9281,7 @@
         <v>31</v>
       </c>
       <c r="C231">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="D231" t="s">
         <v>32</v>
@@ -9295,7 +9295,7 @@
         <v>31</v>
       </c>
       <c r="C232">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="D232" t="s">
         <v>32</v>
@@ -9309,7 +9309,7 @@
         <v>31</v>
       </c>
       <c r="C233">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D233" t="s">
         <v>32</v>
@@ -9323,7 +9323,7 @@
         <v>31</v>
       </c>
       <c r="C234">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D234" t="s">
         <v>32</v>
@@ -9337,7 +9337,7 @@
         <v>31</v>
       </c>
       <c r="C235">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D235" t="s">
         <v>32</v>
@@ -9351,7 +9351,7 @@
         <v>31</v>
       </c>
       <c r="C236">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D236" t="s">
         <v>32</v>
@@ -9365,7 +9365,7 @@
         <v>31</v>
       </c>
       <c r="C237">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D237" t="s">
         <v>32</v>
@@ -9379,7 +9379,7 @@
         <v>31</v>
       </c>
       <c r="C238">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D238" t="s">
         <v>32</v>
@@ -9393,7 +9393,7 @@
         <v>31</v>
       </c>
       <c r="C239">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D239" t="s">
         <v>32</v>
@@ -9407,7 +9407,7 @@
         <v>31</v>
       </c>
       <c r="C240">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="D240" t="s">
         <v>32</v>
@@ -9421,7 +9421,7 @@
         <v>31</v>
       </c>
       <c r="C241">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D241" t="s">
         <v>32</v>
@@ -9435,7 +9435,7 @@
         <v>31</v>
       </c>
       <c r="C242">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D242" t="s">
         <v>32</v>
@@ -9449,7 +9449,7 @@
         <v>31</v>
       </c>
       <c r="C243">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="D243" t="s">
         <v>32</v>
@@ -9463,7 +9463,7 @@
         <v>31</v>
       </c>
       <c r="C244">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D244" t="s">
         <v>32</v>
@@ -9477,7 +9477,7 @@
         <v>31</v>
       </c>
       <c r="C245">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D245" t="s">
         <v>32</v>
@@ -9491,7 +9491,7 @@
         <v>31</v>
       </c>
       <c r="C246">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D246" t="s">
         <v>32</v>
@@ -9505,7 +9505,7 @@
         <v>31</v>
       </c>
       <c r="C247">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="D247" t="s">
         <v>32</v>
@@ -9519,7 +9519,7 @@
         <v>31</v>
       </c>
       <c r="C248">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D248" t="s">
         <v>32</v>
@@ -9533,7 +9533,7 @@
         <v>31</v>
       </c>
       <c r="C249">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D249" t="s">
         <v>32</v>
@@ -9547,7 +9547,7 @@
         <v>31</v>
       </c>
       <c r="C250">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="D250" t="s">
         <v>32</v>
@@ -9561,7 +9561,7 @@
         <v>31</v>
       </c>
       <c r="C251">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D251" t="s">
         <v>32</v>
@@ -9575,7 +9575,7 @@
         <v>31</v>
       </c>
       <c r="C252">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D252" t="s">
         <v>32</v>
@@ -9589,7 +9589,7 @@
         <v>31</v>
       </c>
       <c r="C253">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="D253" t="s">
         <v>32</v>
@@ -9603,7 +9603,7 @@
         <v>31</v>
       </c>
       <c r="C254">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D254" t="s">
         <v>32</v>
@@ -9617,7 +9617,7 @@
         <v>31</v>
       </c>
       <c r="C255">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="D255" t="s">
         <v>32</v>
@@ -9631,7 +9631,7 @@
         <v>31</v>
       </c>
       <c r="C256">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D256" t="s">
         <v>32</v>
@@ -9645,7 +9645,7 @@
         <v>31</v>
       </c>
       <c r="C257">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D257" t="s">
         <v>32</v>
@@ -9659,7 +9659,7 @@
         <v>31</v>
       </c>
       <c r="C258">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="D258" t="s">
         <v>32</v>
@@ -9673,7 +9673,7 @@
         <v>31</v>
       </c>
       <c r="C259">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D259" t="s">
         <v>32</v>
@@ -9687,7 +9687,7 @@
         <v>31</v>
       </c>
       <c r="C260">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D260" t="s">
         <v>32</v>
@@ -9701,7 +9701,7 @@
         <v>31</v>
       </c>
       <c r="C261">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D261" t="s">
         <v>32</v>
@@ -9715,7 +9715,7 @@
         <v>31</v>
       </c>
       <c r="C262">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D262" t="s">
         <v>32</v>
@@ -9729,7 +9729,7 @@
         <v>31</v>
       </c>
       <c r="C263">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="D263" t="s">
         <v>32</v>
@@ -9743,7 +9743,7 @@
         <v>31</v>
       </c>
       <c r="C264">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D264" t="s">
         <v>32</v>
@@ -9757,7 +9757,7 @@
         <v>31</v>
       </c>
       <c r="C265">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D265" t="s">
         <v>32</v>
@@ -9771,7 +9771,7 @@
         <v>31</v>
       </c>
       <c r="C266">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="D266" t="s">
         <v>32</v>
@@ -9785,7 +9785,7 @@
         <v>31</v>
       </c>
       <c r="C267">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D267" t="s">
         <v>32</v>
@@ -9799,7 +9799,7 @@
         <v>31</v>
       </c>
       <c r="C268">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D268" t="s">
         <v>32</v>
@@ -9813,7 +9813,7 @@
         <v>31</v>
       </c>
       <c r="C269">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D269" t="s">
         <v>32</v>
@@ -9827,7 +9827,7 @@
         <v>31</v>
       </c>
       <c r="C270">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D270" t="s">
         <v>32</v>
@@ -9841,7 +9841,7 @@
         <v>31</v>
       </c>
       <c r="C271">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D271" t="s">
         <v>32</v>
@@ -9869,7 +9869,7 @@
         <v>31</v>
       </c>
       <c r="C273">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="D273" t="s">
         <v>32</v>
@@ -9883,7 +9883,7 @@
         <v>31</v>
       </c>
       <c r="C274">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="D274" t="s">
         <v>32</v>
@@ -9897,7 +9897,7 @@
         <v>31</v>
       </c>
       <c r="C275">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D275" t="s">
         <v>32</v>
@@ -9911,7 +9911,7 @@
         <v>31</v>
       </c>
       <c r="C276">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D276" t="s">
         <v>32</v>
@@ -9925,7 +9925,7 @@
         <v>31</v>
       </c>
       <c r="C277">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D277" t="s">
         <v>32</v>
@@ -9939,7 +9939,7 @@
         <v>31</v>
       </c>
       <c r="C278">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D278" t="s">
         <v>32</v>
@@ -9953,7 +9953,7 @@
         <v>31</v>
       </c>
       <c r="C279">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D279" t="s">
         <v>32</v>
@@ -9967,7 +9967,7 @@
         <v>31</v>
       </c>
       <c r="C280">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D280" t="s">
         <v>32</v>
@@ -9981,7 +9981,7 @@
         <v>31</v>
       </c>
       <c r="C281">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D281" t="s">
         <v>32</v>
@@ -9995,7 +9995,7 @@
         <v>31</v>
       </c>
       <c r="C282">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="D282" t="s">
         <v>32</v>
@@ -10009,7 +10009,7 @@
         <v>31</v>
       </c>
       <c r="C283">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D283" t="s">
         <v>32</v>
@@ -10023,7 +10023,7 @@
         <v>31</v>
       </c>
       <c r="C284">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D284" t="s">
         <v>32</v>
@@ -10037,7 +10037,7 @@
         <v>31</v>
       </c>
       <c r="C285">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D285" t="s">
         <v>32</v>
@@ -10051,7 +10051,7 @@
         <v>31</v>
       </c>
       <c r="C286">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D286" t="s">
         <v>32</v>
@@ -10065,7 +10065,7 @@
         <v>31</v>
       </c>
       <c r="C287">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="D287" t="s">
         <v>32</v>
@@ -10079,7 +10079,7 @@
         <v>31</v>
       </c>
       <c r="C288">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D288" t="s">
         <v>32</v>
@@ -10093,7 +10093,7 @@
         <v>31</v>
       </c>
       <c r="C289">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D289" t="s">
         <v>32</v>
@@ -10107,7 +10107,7 @@
         <v>31</v>
       </c>
       <c r="C290">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D290" t="s">
         <v>32</v>
@@ -10121,7 +10121,7 @@
         <v>31</v>
       </c>
       <c r="C291">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D291" t="s">
         <v>32</v>
@@ -10135,7 +10135,7 @@
         <v>31</v>
       </c>
       <c r="C292">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D292" t="s">
         <v>32</v>
@@ -10149,7 +10149,7 @@
         <v>31</v>
       </c>
       <c r="C293">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="D293" t="s">
         <v>32</v>
@@ -10163,7 +10163,7 @@
         <v>31</v>
       </c>
       <c r="C294">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="D294" t="s">
         <v>32</v>
@@ -10177,7 +10177,7 @@
         <v>31</v>
       </c>
       <c r="C295">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="D295" t="s">
         <v>32</v>
@@ -10191,7 +10191,7 @@
         <v>31</v>
       </c>
       <c r="C296">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D296" t="s">
         <v>32</v>
@@ -10205,7 +10205,7 @@
         <v>31</v>
       </c>
       <c r="C297">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D297" t="s">
         <v>32</v>
@@ -10219,7 +10219,7 @@
         <v>31</v>
       </c>
       <c r="C298">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D298" t="s">
         <v>32</v>
@@ -10233,7 +10233,7 @@
         <v>31</v>
       </c>
       <c r="C299">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D299" t="s">
         <v>32</v>
@@ -10247,7 +10247,7 @@
         <v>31</v>
       </c>
       <c r="C300">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D300" t="s">
         <v>32</v>
@@ -10261,7 +10261,7 @@
         <v>31</v>
       </c>
       <c r="C301">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D301" t="s">
         <v>32</v>
@@ -10275,7 +10275,7 @@
         <v>31</v>
       </c>
       <c r="C302">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D302" t="s">
         <v>32</v>
@@ -10289,7 +10289,7 @@
         <v>31</v>
       </c>
       <c r="C303">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D303" t="s">
         <v>32</v>
@@ -10303,7 +10303,7 @@
         <v>31</v>
       </c>
       <c r="C304">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D304" t="s">
         <v>32</v>
@@ -10317,7 +10317,7 @@
         <v>31</v>
       </c>
       <c r="C305">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="D305" t="s">
         <v>32</v>
@@ -10345,7 +10345,7 @@
         <v>31</v>
       </c>
       <c r="C307">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D307" t="s">
         <v>32</v>
@@ -10359,7 +10359,7 @@
         <v>31</v>
       </c>
       <c r="C308">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D308" t="s">
         <v>32</v>
@@ -10373,7 +10373,7 @@
         <v>31</v>
       </c>
       <c r="C309">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D309" t="s">
         <v>32</v>
@@ -10387,7 +10387,7 @@
         <v>31</v>
       </c>
       <c r="C310">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D310" t="s">
         <v>32</v>
@@ -10401,7 +10401,7 @@
         <v>31</v>
       </c>
       <c r="C311">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D311" t="s">
         <v>32</v>
@@ -10415,7 +10415,7 @@
         <v>31</v>
       </c>
       <c r="C312">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="D312" t="s">
         <v>32</v>
@@ -10429,7 +10429,7 @@
         <v>31</v>
       </c>
       <c r="C313">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D313" t="s">
         <v>32</v>
@@ -10443,7 +10443,7 @@
         <v>31</v>
       </c>
       <c r="C314">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D314" t="s">
         <v>32</v>
@@ -10457,7 +10457,7 @@
         <v>31</v>
       </c>
       <c r="C315">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="D315" t="s">
         <v>32</v>
@@ -10471,7 +10471,7 @@
         <v>31</v>
       </c>
       <c r="C316">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D316" t="s">
         <v>32</v>
@@ -10485,7 +10485,7 @@
         <v>31</v>
       </c>
       <c r="C317">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D317" t="s">
         <v>32</v>
@@ -10499,7 +10499,7 @@
         <v>31</v>
       </c>
       <c r="C318">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D318" t="s">
         <v>32</v>
@@ -10513,7 +10513,7 @@
         <v>31</v>
       </c>
       <c r="C319">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="D319" t="s">
         <v>32</v>
@@ -10527,7 +10527,7 @@
         <v>31</v>
       </c>
       <c r="C320">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D320" t="s">
         <v>32</v>
@@ -10541,7 +10541,7 @@
         <v>31</v>
       </c>
       <c r="C321">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="D321" t="s">
         <v>32</v>
@@ -10555,7 +10555,7 @@
         <v>31</v>
       </c>
       <c r="C322">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="D322" t="s">
         <v>32</v>
@@ -10569,7 +10569,7 @@
         <v>31</v>
       </c>
       <c r="C323">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D323" t="s">
         <v>32</v>
@@ -10583,7 +10583,7 @@
         <v>31</v>
       </c>
       <c r="C324">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D324" t="s">
         <v>32</v>
@@ -10597,7 +10597,7 @@
         <v>31</v>
       </c>
       <c r="C325">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D325" t="s">
         <v>32</v>
@@ -10611,7 +10611,7 @@
         <v>31</v>
       </c>
       <c r="C326">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="D326" t="s">
         <v>32</v>
@@ -10625,7 +10625,7 @@
         <v>31</v>
       </c>
       <c r="C327">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D327" t="s">
         <v>32</v>
@@ -10639,7 +10639,7 @@
         <v>31</v>
       </c>
       <c r="C328">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D328" t="s">
         <v>32</v>
@@ -10653,7 +10653,7 @@
         <v>31</v>
       </c>
       <c r="C329">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D329" t="s">
         <v>32</v>
@@ -10667,7 +10667,7 @@
         <v>31</v>
       </c>
       <c r="C330">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D330" t="s">
         <v>32</v>
@@ -10681,7 +10681,7 @@
         <v>31</v>
       </c>
       <c r="C331">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D331" t="s">
         <v>32</v>
@@ -10695,7 +10695,7 @@
         <v>31</v>
       </c>
       <c r="C332">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D332" t="s">
         <v>32</v>
@@ -10709,7 +10709,7 @@
         <v>31</v>
       </c>
       <c r="C333">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D333" t="s">
         <v>32</v>
@@ -10723,7 +10723,7 @@
         <v>31</v>
       </c>
       <c r="C334">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D334" t="s">
         <v>32</v>
@@ -10737,7 +10737,7 @@
         <v>31</v>
       </c>
       <c r="C335">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D335" t="s">
         <v>32</v>
@@ -10751,7 +10751,7 @@
         <v>31</v>
       </c>
       <c r="C336">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D336" t="s">
         <v>32</v>
@@ -10765,7 +10765,7 @@
         <v>31</v>
       </c>
       <c r="C337">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D337" t="s">
         <v>32</v>
@@ -10779,7 +10779,7 @@
         <v>31</v>
       </c>
       <c r="C338">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D338" t="s">
         <v>32</v>
@@ -10793,7 +10793,7 @@
         <v>31</v>
       </c>
       <c r="C339">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D339" t="s">
         <v>32</v>
@@ -10807,7 +10807,7 @@
         <v>31</v>
       </c>
       <c r="C340">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D340" t="s">
         <v>32</v>
@@ -10821,7 +10821,7 @@
         <v>31</v>
       </c>
       <c r="C341">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D341" t="s">
         <v>32</v>
@@ -10835,7 +10835,7 @@
         <v>31</v>
       </c>
       <c r="C342">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D342" t="s">
         <v>32</v>
@@ -10849,7 +10849,7 @@
         <v>31</v>
       </c>
       <c r="C343">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="D343" t="s">
         <v>32</v>
@@ -10863,7 +10863,7 @@
         <v>31</v>
       </c>
       <c r="C344">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D344" t="s">
         <v>32</v>
@@ -10877,7 +10877,7 @@
         <v>31</v>
       </c>
       <c r="C345">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="D345" t="s">
         <v>32</v>
@@ -10891,7 +10891,7 @@
         <v>31</v>
       </c>
       <c r="C346">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="D346" t="s">
         <v>32</v>
@@ -10919,7 +10919,7 @@
         <v>31</v>
       </c>
       <c r="C348">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="D348" t="s">
         <v>32</v>
@@ -10933,7 +10933,7 @@
         <v>31</v>
       </c>
       <c r="C349">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D349" t="s">
         <v>32</v>
@@ -10947,7 +10947,7 @@
         <v>31</v>
       </c>
       <c r="C350">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="D350" t="s">
         <v>32</v>
@@ -10961,7 +10961,7 @@
         <v>31</v>
       </c>
       <c r="C351">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D351" t="s">
         <v>32</v>
@@ -10975,7 +10975,7 @@
         <v>31</v>
       </c>
       <c r="C352">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D352" t="s">
         <v>32</v>
@@ -10989,7 +10989,7 @@
         <v>31</v>
       </c>
       <c r="C353">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D353" t="s">
         <v>32</v>
@@ -11003,7 +11003,7 @@
         <v>31</v>
       </c>
       <c r="C354">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="D354" t="s">
         <v>32</v>
@@ -11017,7 +11017,7 @@
         <v>31</v>
       </c>
       <c r="C355">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="D355" t="s">
         <v>32</v>
@@ -11031,7 +11031,7 @@
         <v>31</v>
       </c>
       <c r="C356">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D356" t="s">
         <v>32</v>
@@ -11045,7 +11045,7 @@
         <v>31</v>
       </c>
       <c r="C357">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="D357" t="s">
         <v>32</v>
@@ -11059,7 +11059,7 @@
         <v>31</v>
       </c>
       <c r="C358">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D358" t="s">
         <v>32</v>
@@ -11073,7 +11073,7 @@
         <v>31</v>
       </c>
       <c r="C359">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D359" t="s">
         <v>32</v>
@@ -11087,7 +11087,7 @@
         <v>31</v>
       </c>
       <c r="C360">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="D360" t="s">
         <v>32</v>
@@ -11101,7 +11101,7 @@
         <v>31</v>
       </c>
       <c r="C361">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D361" t="s">
         <v>32</v>
@@ -11115,7 +11115,7 @@
         <v>31</v>
       </c>
       <c r="C362">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D362" t="s">
         <v>32</v>
@@ -11129,7 +11129,7 @@
         <v>31</v>
       </c>
       <c r="C363">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D363" t="s">
         <v>32</v>
@@ -11143,7 +11143,7 @@
         <v>31</v>
       </c>
       <c r="C364">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D364" t="s">
         <v>32</v>
@@ -11157,7 +11157,7 @@
         <v>31</v>
       </c>
       <c r="C365">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D365" t="s">
         <v>32</v>
@@ -11171,7 +11171,7 @@
         <v>31</v>
       </c>
       <c r="C366">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D366" t="s">
         <v>32</v>
@@ -11185,7 +11185,7 @@
         <v>31</v>
       </c>
       <c r="C367">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D367" t="s">
         <v>32</v>
@@ -11199,7 +11199,7 @@
         <v>31</v>
       </c>
       <c r="C368">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D368" t="s">
         <v>32</v>
@@ -11213,7 +11213,7 @@
         <v>31</v>
       </c>
       <c r="C369">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D369" t="s">
         <v>32</v>
@@ -11227,7 +11227,7 @@
         <v>31</v>
       </c>
       <c r="C370">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D370" t="s">
         <v>32</v>
@@ -11241,7 +11241,7 @@
         <v>31</v>
       </c>
       <c r="C371">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="D371" t="s">
         <v>32</v>
@@ -11255,7 +11255,7 @@
         <v>31</v>
       </c>
       <c r="C372">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="D372" t="s">
         <v>32</v>
@@ -11269,7 +11269,7 @@
         <v>31</v>
       </c>
       <c r="C373">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D373" t="s">
         <v>32</v>
@@ -11283,7 +11283,7 @@
         <v>31</v>
       </c>
       <c r="C374">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D374" t="s">
         <v>32</v>
@@ -11297,7 +11297,7 @@
         <v>31</v>
       </c>
       <c r="C375">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D375" t="s">
         <v>32</v>
@@ -11311,7 +11311,7 @@
         <v>31</v>
       </c>
       <c r="C376">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D376" t="s">
         <v>32</v>
@@ -11325,7 +11325,7 @@
         <v>31</v>
       </c>
       <c r="C377">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="D377" t="s">
         <v>32</v>
@@ -11339,7 +11339,7 @@
         <v>31</v>
       </c>
       <c r="C378">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D378" t="s">
         <v>32</v>
@@ -11353,7 +11353,7 @@
         <v>31</v>
       </c>
       <c r="C379">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D379" t="s">
         <v>32</v>
@@ -11367,7 +11367,7 @@
         <v>31</v>
       </c>
       <c r="C380">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D380" t="s">
         <v>32</v>
@@ -11381,7 +11381,7 @@
         <v>31</v>
       </c>
       <c r="C381">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="D381" t="s">
         <v>32</v>
@@ -11395,7 +11395,7 @@
         <v>31</v>
       </c>
       <c r="C382">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D382" t="s">
         <v>32</v>
@@ -11409,7 +11409,7 @@
         <v>31</v>
       </c>
       <c r="C383">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D383" t="s">
         <v>32</v>
@@ -11423,7 +11423,7 @@
         <v>31</v>
       </c>
       <c r="C384">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D384" t="s">
         <v>32</v>
@@ -11437,7 +11437,7 @@
         <v>31</v>
       </c>
       <c r="C385">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="D385" t="s">
         <v>32</v>
@@ -11465,7 +11465,7 @@
         <v>31</v>
       </c>
       <c r="C387">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D387" t="s">
         <v>32</v>
@@ -11479,7 +11479,7 @@
         <v>31</v>
       </c>
       <c r="C388">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D388" t="s">
         <v>32</v>
@@ -11493,7 +11493,7 @@
         <v>31</v>
       </c>
       <c r="C389">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D389" t="s">
         <v>32</v>
@@ -11507,7 +11507,7 @@
         <v>31</v>
       </c>
       <c r="C390">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D390" t="s">
         <v>32</v>
@@ -11521,7 +11521,7 @@
         <v>31</v>
       </c>
       <c r="C391">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="D391" t="s">
         <v>32</v>
@@ -11549,7 +11549,7 @@
         <v>31</v>
       </c>
       <c r="C393">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="D393" t="s">
         <v>32</v>
@@ -11563,7 +11563,7 @@
         <v>31</v>
       </c>
       <c r="C394">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="D394" t="s">
         <v>32</v>
@@ -11577,7 +11577,7 @@
         <v>31</v>
       </c>
       <c r="C395">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D395" t="s">
         <v>32</v>
@@ -11591,7 +11591,7 @@
         <v>31</v>
       </c>
       <c r="C396">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D396" t="s">
         <v>32</v>
@@ -11605,7 +11605,7 @@
         <v>31</v>
       </c>
       <c r="C397">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="D397" t="s">
         <v>32</v>
@@ -11619,7 +11619,7 @@
         <v>31</v>
       </c>
       <c r="C398">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="D398" t="s">
         <v>32</v>
@@ -11633,7 +11633,7 @@
         <v>31</v>
       </c>
       <c r="C399">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D399" t="s">
         <v>32</v>
@@ -11647,7 +11647,7 @@
         <v>31</v>
       </c>
       <c r="C400">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D400" t="s">
         <v>32</v>
@@ -11661,7 +11661,7 @@
         <v>31</v>
       </c>
       <c r="C401">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D401" t="s">
         <v>32</v>
@@ -22556,7 +22556,7 @@
         <v>31</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
         <v>32</v>
@@ -22570,7 +22570,7 @@
         <v>31</v>
       </c>
       <c r="C3">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
         <v>32</v>
@@ -22584,7 +22584,7 @@
         <v>31</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
@@ -22598,7 +22598,7 @@
         <v>31</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
         <v>32</v>
@@ -22612,7 +22612,7 @@
         <v>31</v>
       </c>
       <c r="C6">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="D6" t="s">
         <v>32</v>
@@ -22626,7 +22626,7 @@
         <v>31</v>
       </c>
       <c r="C7">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
@@ -22640,7 +22640,7 @@
         <v>31</v>
       </c>
       <c r="C8">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D8" t="s">
         <v>32</v>
@@ -22654,7 +22654,7 @@
         <v>31</v>
       </c>
       <c r="C9">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
         <v>32</v>
@@ -22668,7 +22668,7 @@
         <v>31</v>
       </c>
       <c r="C10">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
         <v>32</v>
@@ -22682,7 +22682,7 @@
         <v>31</v>
       </c>
       <c r="C11">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
@@ -22696,7 +22696,7 @@
         <v>31</v>
       </c>
       <c r="C12">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
         <v>32</v>
@@ -22710,7 +22710,7 @@
         <v>31</v>
       </c>
       <c r="C13">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
         <v>32</v>
@@ -22724,7 +22724,7 @@
         <v>31</v>
       </c>
       <c r="C14">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
         <v>32</v>
@@ -22738,7 +22738,7 @@
         <v>31</v>
       </c>
       <c r="C15">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
         <v>32</v>
@@ -22752,7 +22752,7 @@
         <v>31</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s">
         <v>32</v>
@@ -22766,7 +22766,7 @@
         <v>31</v>
       </c>
       <c r="C17">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D17" t="s">
         <v>32</v>
@@ -22780,7 +22780,7 @@
         <v>31</v>
       </c>
       <c r="C18">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D18" t="s">
         <v>32</v>
@@ -22794,7 +22794,7 @@
         <v>31</v>
       </c>
       <c r="C19">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="D19" t="s">
         <v>32</v>
@@ -22808,7 +22808,7 @@
         <v>31</v>
       </c>
       <c r="C20">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D20" t="s">
         <v>32</v>
@@ -22822,7 +22822,7 @@
         <v>31</v>
       </c>
       <c r="C21">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D21" t="s">
         <v>32</v>
@@ -22836,7 +22836,7 @@
         <v>31</v>
       </c>
       <c r="C22">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D22" t="s">
         <v>32</v>
@@ -22850,7 +22850,7 @@
         <v>31</v>
       </c>
       <c r="C23">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D23" t="s">
         <v>32</v>
@@ -22864,7 +22864,7 @@
         <v>31</v>
       </c>
       <c r="C24">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D24" t="s">
         <v>32</v>
@@ -22878,7 +22878,7 @@
         <v>31</v>
       </c>
       <c r="C25">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D25" t="s">
         <v>32</v>
@@ -22906,7 +22906,7 @@
         <v>31</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D27" t="s">
         <v>32</v>
@@ -22920,7 +22920,7 @@
         <v>31</v>
       </c>
       <c r="C28">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D28" t="s">
         <v>32</v>
@@ -22934,7 +22934,7 @@
         <v>31</v>
       </c>
       <c r="C29">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D29" t="s">
         <v>32</v>
@@ -22948,7 +22948,7 @@
         <v>31</v>
       </c>
       <c r="C30">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D30" t="s">
         <v>32</v>
@@ -22962,7 +22962,7 @@
         <v>31</v>
       </c>
       <c r="C31">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D31" t="s">
         <v>32</v>
@@ -22976,7 +22976,7 @@
         <v>31</v>
       </c>
       <c r="C32">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D32" t="s">
         <v>32</v>
@@ -22990,7 +22990,7 @@
         <v>31</v>
       </c>
       <c r="C33">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D33" t="s">
         <v>32</v>
@@ -23004,7 +23004,7 @@
         <v>31</v>
       </c>
       <c r="C34">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D34" t="s">
         <v>32</v>
@@ -23018,7 +23018,7 @@
         <v>31</v>
       </c>
       <c r="C35">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D35" t="s">
         <v>32</v>
@@ -23032,7 +23032,7 @@
         <v>31</v>
       </c>
       <c r="C36">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D36" t="s">
         <v>32</v>
@@ -23046,7 +23046,7 @@
         <v>31</v>
       </c>
       <c r="C37">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D37" t="s">
         <v>32</v>
@@ -23060,7 +23060,7 @@
         <v>31</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D38" t="s">
         <v>32</v>
@@ -23074,7 +23074,7 @@
         <v>31</v>
       </c>
       <c r="C39">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D39" t="s">
         <v>32</v>
@@ -23088,7 +23088,7 @@
         <v>31</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D40" t="s">
         <v>32</v>
@@ -23102,7 +23102,7 @@
         <v>31</v>
       </c>
       <c r="C41">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D41" t="s">
         <v>32</v>
@@ -23116,7 +23116,7 @@
         <v>31</v>
       </c>
       <c r="C42">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D42" t="s">
         <v>32</v>
@@ -23130,7 +23130,7 @@
         <v>31</v>
       </c>
       <c r="C43">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D43" t="s">
         <v>32</v>
@@ -23144,7 +23144,7 @@
         <v>31</v>
       </c>
       <c r="C44">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D44" t="s">
         <v>32</v>
@@ -23158,7 +23158,7 @@
         <v>31</v>
       </c>
       <c r="C45">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D45" t="s">
         <v>32</v>
@@ -23172,7 +23172,7 @@
         <v>31</v>
       </c>
       <c r="C46">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D46" t="s">
         <v>32</v>
@@ -23186,7 +23186,7 @@
         <v>31</v>
       </c>
       <c r="C47">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D47" t="s">
         <v>32</v>
@@ -23200,7 +23200,7 @@
         <v>31</v>
       </c>
       <c r="C48">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D48" t="s">
         <v>32</v>
@@ -23214,7 +23214,7 @@
         <v>31</v>
       </c>
       <c r="C49">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D49" t="s">
         <v>32</v>
@@ -23228,7 +23228,7 @@
         <v>31</v>
       </c>
       <c r="C50">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D50" t="s">
         <v>32</v>
@@ -23242,7 +23242,7 @@
         <v>31</v>
       </c>
       <c r="C51">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D51" t="s">
         <v>32</v>
@@ -23256,7 +23256,7 @@
         <v>31</v>
       </c>
       <c r="C52">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D52" t="s">
         <v>32</v>
@@ -23270,7 +23270,7 @@
         <v>31</v>
       </c>
       <c r="C53">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D53" t="s">
         <v>32</v>
@@ -23298,7 +23298,7 @@
         <v>31</v>
       </c>
       <c r="C55">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D55" t="s">
         <v>32</v>
@@ -23312,7 +23312,7 @@
         <v>31</v>
       </c>
       <c r="C56">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D56" t="s">
         <v>32</v>
@@ -23326,7 +23326,7 @@
         <v>31</v>
       </c>
       <c r="C57">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D57" t="s">
         <v>32</v>
@@ -23340,7 +23340,7 @@
         <v>31</v>
       </c>
       <c r="C58">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D58" t="s">
         <v>32</v>
@@ -23354,7 +23354,7 @@
         <v>31</v>
       </c>
       <c r="C59">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D59" t="s">
         <v>32</v>
@@ -23368,7 +23368,7 @@
         <v>31</v>
       </c>
       <c r="C60">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D60" t="s">
         <v>32</v>
@@ -23396,7 +23396,7 @@
         <v>31</v>
       </c>
       <c r="C62">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D62" t="s">
         <v>32</v>
@@ -23410,7 +23410,7 @@
         <v>31</v>
       </c>
       <c r="C63">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D63" t="s">
         <v>32</v>
@@ -23424,7 +23424,7 @@
         <v>31</v>
       </c>
       <c r="C64">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D64" t="s">
         <v>32</v>
@@ -23438,7 +23438,7 @@
         <v>31</v>
       </c>
       <c r="C65">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D65" t="s">
         <v>32</v>
@@ -23452,7 +23452,7 @@
         <v>31</v>
       </c>
       <c r="C66">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D66" t="s">
         <v>32</v>
@@ -23466,7 +23466,7 @@
         <v>31</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D67" t="s">
         <v>32</v>
@@ -23480,7 +23480,7 @@
         <v>31</v>
       </c>
       <c r="C68">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D68" t="s">
         <v>32</v>
@@ -23494,7 +23494,7 @@
         <v>31</v>
       </c>
       <c r="C69">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D69" t="s">
         <v>32</v>
@@ -23508,7 +23508,7 @@
         <v>31</v>
       </c>
       <c r="C70">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D70" t="s">
         <v>32</v>
@@ -23536,7 +23536,7 @@
         <v>31</v>
       </c>
       <c r="C72">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D72" t="s">
         <v>32</v>
@@ -23550,7 +23550,7 @@
         <v>31</v>
       </c>
       <c r="C73">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D73" t="s">
         <v>32</v>
@@ -23564,7 +23564,7 @@
         <v>31</v>
       </c>
       <c r="C74">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D74" t="s">
         <v>32</v>
@@ -23578,7 +23578,7 @@
         <v>31</v>
       </c>
       <c r="C75">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D75" t="s">
         <v>32</v>
@@ -23592,7 +23592,7 @@
         <v>31</v>
       </c>
       <c r="C76">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D76" t="s">
         <v>32</v>
@@ -23606,7 +23606,7 @@
         <v>31</v>
       </c>
       <c r="C77">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D77" t="s">
         <v>32</v>
@@ -23620,7 +23620,7 @@
         <v>31</v>
       </c>
       <c r="C78">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D78" t="s">
         <v>32</v>
@@ -23634,7 +23634,7 @@
         <v>31</v>
       </c>
       <c r="C79">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D79" t="s">
         <v>32</v>
@@ -23648,7 +23648,7 @@
         <v>31</v>
       </c>
       <c r="C80">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D80" t="s">
         <v>32</v>
@@ -23662,7 +23662,7 @@
         <v>31</v>
       </c>
       <c r="C81">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D81" t="s">
         <v>32</v>
@@ -23676,7 +23676,7 @@
         <v>31</v>
       </c>
       <c r="C82">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D82" t="s">
         <v>32</v>
@@ -23690,7 +23690,7 @@
         <v>31</v>
       </c>
       <c r="C83">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D83" t="s">
         <v>32</v>
@@ -23704,7 +23704,7 @@
         <v>31</v>
       </c>
       <c r="C84">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D84" t="s">
         <v>32</v>
@@ -23718,7 +23718,7 @@
         <v>31</v>
       </c>
       <c r="C85">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D85" t="s">
         <v>32</v>
@@ -23732,7 +23732,7 @@
         <v>31</v>
       </c>
       <c r="C86">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D86" t="s">
         <v>32</v>
@@ -23746,7 +23746,7 @@
         <v>31</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D87" t="s">
         <v>32</v>
@@ -23760,7 +23760,7 @@
         <v>31</v>
       </c>
       <c r="C88">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D88" t="s">
         <v>32</v>
@@ -23788,7 +23788,7 @@
         <v>31</v>
       </c>
       <c r="C90">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D90" t="s">
         <v>32</v>
@@ -23802,7 +23802,7 @@
         <v>31</v>
       </c>
       <c r="C91">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D91" t="s">
         <v>32</v>
@@ -23816,7 +23816,7 @@
         <v>31</v>
       </c>
       <c r="C92">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D92" t="s">
         <v>32</v>
@@ -23830,7 +23830,7 @@
         <v>31</v>
       </c>
       <c r="C93">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D93" t="s">
         <v>32</v>
@@ -23844,7 +23844,7 @@
         <v>31</v>
       </c>
       <c r="C94">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D94" t="s">
         <v>32</v>
@@ -23858,7 +23858,7 @@
         <v>31</v>
       </c>
       <c r="C95">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D95" t="s">
         <v>32</v>
@@ -23872,7 +23872,7 @@
         <v>31</v>
       </c>
       <c r="C96">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D96" t="s">
         <v>32</v>
@@ -23886,7 +23886,7 @@
         <v>31</v>
       </c>
       <c r="C97">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D97" t="s">
         <v>32</v>
@@ -23900,7 +23900,7 @@
         <v>31</v>
       </c>
       <c r="C98">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D98" t="s">
         <v>32</v>
@@ -23914,7 +23914,7 @@
         <v>31</v>
       </c>
       <c r="C99">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D99" t="s">
         <v>32</v>
@@ -23928,7 +23928,7 @@
         <v>31</v>
       </c>
       <c r="C100">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D100" t="s">
         <v>32</v>
@@ -23942,7 +23942,7 @@
         <v>31</v>
       </c>
       <c r="C101">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D101" t="s">
         <v>32</v>
@@ -23956,7 +23956,7 @@
         <v>31</v>
       </c>
       <c r="C102">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D102" t="s">
         <v>32</v>
@@ -23970,7 +23970,7 @@
         <v>31</v>
       </c>
       <c r="C103">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D103" t="s">
         <v>32</v>
@@ -23984,7 +23984,7 @@
         <v>31</v>
       </c>
       <c r="C104">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D104" t="s">
         <v>32</v>
@@ -23998,7 +23998,7 @@
         <v>31</v>
       </c>
       <c r="C105">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D105" t="s">
         <v>32</v>
@@ -24012,7 +24012,7 @@
         <v>31</v>
       </c>
       <c r="C106">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="D106" t="s">
         <v>32</v>
@@ -24026,7 +24026,7 @@
         <v>31</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D107" t="s">
         <v>32</v>
@@ -24040,7 +24040,7 @@
         <v>31</v>
       </c>
       <c r="C108">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D108" t="s">
         <v>32</v>
@@ -24054,7 +24054,7 @@
         <v>31</v>
       </c>
       <c r="C109">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D109" t="s">
         <v>32</v>
@@ -24068,7 +24068,7 @@
         <v>31</v>
       </c>
       <c r="C110">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D110" t="s">
         <v>32</v>
@@ -24082,7 +24082,7 @@
         <v>31</v>
       </c>
       <c r="C111">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D111" t="s">
         <v>32</v>
@@ -24096,7 +24096,7 @@
         <v>31</v>
       </c>
       <c r="C112">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="D112" t="s">
         <v>32</v>
@@ -24110,7 +24110,7 @@
         <v>31</v>
       </c>
       <c r="C113">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D113" t="s">
         <v>32</v>
@@ -24124,7 +24124,7 @@
         <v>31</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D114" t="s">
         <v>32</v>
@@ -24138,7 +24138,7 @@
         <v>31</v>
       </c>
       <c r="C115">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D115" t="s">
         <v>32</v>
@@ -24152,7 +24152,7 @@
         <v>31</v>
       </c>
       <c r="C116">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D116" t="s">
         <v>32</v>
@@ -24166,7 +24166,7 @@
         <v>31</v>
       </c>
       <c r="C117">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="D117" t="s">
         <v>32</v>
@@ -24180,7 +24180,7 @@
         <v>31</v>
       </c>
       <c r="C118">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D118" t="s">
         <v>32</v>
@@ -24194,7 +24194,7 @@
         <v>31</v>
       </c>
       <c r="C119">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D119" t="s">
         <v>32</v>
@@ -24208,7 +24208,7 @@
         <v>31</v>
       </c>
       <c r="C120">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D120" t="s">
         <v>32</v>
@@ -24222,7 +24222,7 @@
         <v>31</v>
       </c>
       <c r="C121">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D121" t="s">
         <v>32</v>
@@ -24236,7 +24236,7 @@
         <v>31</v>
       </c>
       <c r="C122">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="D122" t="s">
         <v>32</v>
@@ -24250,7 +24250,7 @@
         <v>31</v>
       </c>
       <c r="C123">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D123" t="s">
         <v>32</v>
@@ -24264,7 +24264,7 @@
         <v>31</v>
       </c>
       <c r="C124">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D124" t="s">
         <v>32</v>
@@ -24278,7 +24278,7 @@
         <v>31</v>
       </c>
       <c r="C125">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D125" t="s">
         <v>32</v>
@@ -24292,7 +24292,7 @@
         <v>31</v>
       </c>
       <c r="C126">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="D126" t="s">
         <v>32</v>
@@ -24306,7 +24306,7 @@
         <v>31</v>
       </c>
       <c r="C127">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D127" t="s">
         <v>32</v>
@@ -24320,7 +24320,7 @@
         <v>31</v>
       </c>
       <c r="C128">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D128" t="s">
         <v>32</v>
@@ -24334,7 +24334,7 @@
         <v>31</v>
       </c>
       <c r="C129">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="D129" t="s">
         <v>32</v>
@@ -24348,7 +24348,7 @@
         <v>31</v>
       </c>
       <c r="C130">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D130" t="s">
         <v>32</v>
@@ -24362,7 +24362,7 @@
         <v>31</v>
       </c>
       <c r="C131">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="D131" t="s">
         <v>32</v>
@@ -24376,7 +24376,7 @@
         <v>31</v>
       </c>
       <c r="C132">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D132" t="s">
         <v>32</v>
@@ -24390,7 +24390,7 @@
         <v>31</v>
       </c>
       <c r="C133">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D133" t="s">
         <v>32</v>
@@ -24404,7 +24404,7 @@
         <v>31</v>
       </c>
       <c r="C134">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D134" t="s">
         <v>32</v>
@@ -24418,7 +24418,7 @@
         <v>31</v>
       </c>
       <c r="C135">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D135" t="s">
         <v>32</v>
@@ -24432,7 +24432,7 @@
         <v>31</v>
       </c>
       <c r="C136">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="D136" t="s">
         <v>32</v>
@@ -24446,7 +24446,7 @@
         <v>31</v>
       </c>
       <c r="C137">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D137" t="s">
         <v>32</v>
@@ -24460,7 +24460,7 @@
         <v>31</v>
       </c>
       <c r="C138">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="D138" t="s">
         <v>32</v>
@@ -24474,7 +24474,7 @@
         <v>31</v>
       </c>
       <c r="C139">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D139" t="s">
         <v>32</v>
@@ -24488,7 +24488,7 @@
         <v>31</v>
       </c>
       <c r="C140">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D140" t="s">
         <v>32</v>
@@ -24502,7 +24502,7 @@
         <v>31</v>
       </c>
       <c r="C141">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D141" t="s">
         <v>32</v>
@@ -24516,7 +24516,7 @@
         <v>31</v>
       </c>
       <c r="C142">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D142" t="s">
         <v>32</v>
@@ -24530,7 +24530,7 @@
         <v>31</v>
       </c>
       <c r="C143">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D143" t="s">
         <v>32</v>
@@ -24544,7 +24544,7 @@
         <v>31</v>
       </c>
       <c r="C144">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D144" t="s">
         <v>32</v>
@@ -24558,7 +24558,7 @@
         <v>31</v>
       </c>
       <c r="C145">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D145" t="s">
         <v>32</v>
@@ -24572,7 +24572,7 @@
         <v>31</v>
       </c>
       <c r="C146">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="D146" t="s">
         <v>32</v>
@@ -24586,7 +24586,7 @@
         <v>31</v>
       </c>
       <c r="C147">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D147" t="s">
         <v>32</v>
@@ -24600,7 +24600,7 @@
         <v>31</v>
       </c>
       <c r="C148">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D148" t="s">
         <v>32</v>
@@ -24614,7 +24614,7 @@
         <v>31</v>
       </c>
       <c r="C149">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D149" t="s">
         <v>32</v>
@@ -24628,7 +24628,7 @@
         <v>31</v>
       </c>
       <c r="C150">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D150" t="s">
         <v>32</v>
@@ -24642,7 +24642,7 @@
         <v>31</v>
       </c>
       <c r="C151">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D151" t="s">
         <v>32</v>
@@ -24656,7 +24656,7 @@
         <v>31</v>
       </c>
       <c r="C152">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D152" t="s">
         <v>32</v>
@@ -24670,7 +24670,7 @@
         <v>31</v>
       </c>
       <c r="C153">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D153" t="s">
         <v>32</v>
@@ -24684,7 +24684,7 @@
         <v>31</v>
       </c>
       <c r="C154">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D154" t="s">
         <v>32</v>
@@ -24698,7 +24698,7 @@
         <v>31</v>
       </c>
       <c r="C155">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D155" t="s">
         <v>32</v>
@@ -24712,7 +24712,7 @@
         <v>31</v>
       </c>
       <c r="C156">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D156" t="s">
         <v>32</v>
@@ -24726,7 +24726,7 @@
         <v>31</v>
       </c>
       <c r="C157">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D157" t="s">
         <v>32</v>
@@ -24740,7 +24740,7 @@
         <v>31</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D158" t="s">
         <v>32</v>
@@ -24754,7 +24754,7 @@
         <v>31</v>
       </c>
       <c r="C159">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D159" t="s">
         <v>32</v>
@@ -24768,7 +24768,7 @@
         <v>31</v>
       </c>
       <c r="C160">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D160" t="s">
         <v>32</v>
@@ -24782,7 +24782,7 @@
         <v>31</v>
       </c>
       <c r="C161">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D161" t="s">
         <v>32</v>
@@ -24796,7 +24796,7 @@
         <v>31</v>
       </c>
       <c r="C162">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="D162" t="s">
         <v>32</v>
@@ -24810,7 +24810,7 @@
         <v>31</v>
       </c>
       <c r="C163">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D163" t="s">
         <v>32</v>
@@ -24824,7 +24824,7 @@
         <v>31</v>
       </c>
       <c r="C164">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D164" t="s">
         <v>32</v>
@@ -24852,7 +24852,7 @@
         <v>31</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D166" t="s">
         <v>32</v>
@@ -24866,7 +24866,7 @@
         <v>31</v>
       </c>
       <c r="C167">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D167" t="s">
         <v>32</v>
@@ -24880,7 +24880,7 @@
         <v>31</v>
       </c>
       <c r="C168">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D168" t="s">
         <v>32</v>
@@ -24894,7 +24894,7 @@
         <v>31</v>
       </c>
       <c r="C169">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D169" t="s">
         <v>32</v>
@@ -24908,7 +24908,7 @@
         <v>31</v>
       </c>
       <c r="C170">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="D170" t="s">
         <v>32</v>
@@ -24922,7 +24922,7 @@
         <v>31</v>
       </c>
       <c r="C171">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D171" t="s">
         <v>32</v>
@@ -24936,7 +24936,7 @@
         <v>31</v>
       </c>
       <c r="C172">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D172" t="s">
         <v>32</v>
@@ -24950,7 +24950,7 @@
         <v>31</v>
       </c>
       <c r="C173">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D173" t="s">
         <v>32</v>
@@ -24964,7 +24964,7 @@
         <v>31</v>
       </c>
       <c r="C174">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D174" t="s">
         <v>32</v>
@@ -24978,7 +24978,7 @@
         <v>31</v>
       </c>
       <c r="C175">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D175" t="s">
         <v>32</v>
@@ -25006,7 +25006,7 @@
         <v>31</v>
       </c>
       <c r="C177">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D177" t="s">
         <v>32</v>
@@ -25020,7 +25020,7 @@
         <v>31</v>
       </c>
       <c r="C178">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D178" t="s">
         <v>32</v>
@@ -25048,7 +25048,7 @@
         <v>31</v>
       </c>
       <c r="C180">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="D180" t="s">
         <v>32</v>
@@ -25062,7 +25062,7 @@
         <v>31</v>
       </c>
       <c r="C181">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D181" t="s">
         <v>32</v>
@@ -25076,7 +25076,7 @@
         <v>31</v>
       </c>
       <c r="C182">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D182" t="s">
         <v>32</v>
@@ -25090,7 +25090,7 @@
         <v>31</v>
       </c>
       <c r="C183">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="D183" t="s">
         <v>32</v>
@@ -25104,7 +25104,7 @@
         <v>31</v>
       </c>
       <c r="C184">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="D184" t="s">
         <v>32</v>
@@ -25118,7 +25118,7 @@
         <v>31</v>
       </c>
       <c r="C185">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D185" t="s">
         <v>32</v>
@@ -25132,7 +25132,7 @@
         <v>31</v>
       </c>
       <c r="C186">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D186" t="s">
         <v>32</v>
@@ -25146,7 +25146,7 @@
         <v>31</v>
       </c>
       <c r="C187">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="D187" t="s">
         <v>32</v>
@@ -25160,7 +25160,7 @@
         <v>31</v>
       </c>
       <c r="C188">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D188" t="s">
         <v>32</v>
@@ -25174,7 +25174,7 @@
         <v>31</v>
       </c>
       <c r="C189">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D189" t="s">
         <v>32</v>
@@ -25188,7 +25188,7 @@
         <v>31</v>
       </c>
       <c r="C190">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D190" t="s">
         <v>32</v>
@@ -25202,7 +25202,7 @@
         <v>31</v>
       </c>
       <c r="C191">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D191" t="s">
         <v>32</v>
@@ -25216,7 +25216,7 @@
         <v>31</v>
       </c>
       <c r="C192">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D192" t="s">
         <v>32</v>
@@ -25230,7 +25230,7 @@
         <v>31</v>
       </c>
       <c r="C193">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D193" t="s">
         <v>32</v>
@@ -25244,7 +25244,7 @@
         <v>31</v>
       </c>
       <c r="C194">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="D194" t="s">
         <v>32</v>
@@ -25258,7 +25258,7 @@
         <v>31</v>
       </c>
       <c r="C195">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D195" t="s">
         <v>32</v>
@@ -25272,7 +25272,7 @@
         <v>31</v>
       </c>
       <c r="C196">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D196" t="s">
         <v>32</v>
@@ -25286,7 +25286,7 @@
         <v>31</v>
       </c>
       <c r="C197">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D197" t="s">
         <v>32</v>
@@ -25300,7 +25300,7 @@
         <v>31</v>
       </c>
       <c r="C198">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="D198" t="s">
         <v>32</v>
@@ -25314,7 +25314,7 @@
         <v>31</v>
       </c>
       <c r="C199">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D199" t="s">
         <v>32</v>
@@ -25328,7 +25328,7 @@
         <v>31</v>
       </c>
       <c r="C200">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D200" t="s">
         <v>32</v>
@@ -25342,7 +25342,7 @@
         <v>31</v>
       </c>
       <c r="C201">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D201" t="s">
         <v>32</v>
@@ -25356,7 +25356,7 @@
         <v>31</v>
       </c>
       <c r="C202">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D202" t="s">
         <v>32</v>
@@ -25370,7 +25370,7 @@
         <v>31</v>
       </c>
       <c r="C203">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D203" t="s">
         <v>32</v>
@@ -25398,7 +25398,7 @@
         <v>31</v>
       </c>
       <c r="C205">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D205" t="s">
         <v>32</v>
@@ -25412,7 +25412,7 @@
         <v>31</v>
       </c>
       <c r="C206">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="D206" t="s">
         <v>32</v>
@@ -25426,7 +25426,7 @@
         <v>31</v>
       </c>
       <c r="C207">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D207" t="s">
         <v>32</v>
@@ -25440,7 +25440,7 @@
         <v>31</v>
       </c>
       <c r="C208">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D208" t="s">
         <v>32</v>
@@ -25454,7 +25454,7 @@
         <v>31</v>
       </c>
       <c r="C209">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="D209" t="s">
         <v>32</v>
@@ -25468,7 +25468,7 @@
         <v>31</v>
       </c>
       <c r="C210">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="D210" t="s">
         <v>32</v>
@@ -25482,7 +25482,7 @@
         <v>31</v>
       </c>
       <c r="C211">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D211" t="s">
         <v>32</v>
@@ -25496,7 +25496,7 @@
         <v>31</v>
       </c>
       <c r="C212">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D212" t="s">
         <v>32</v>
@@ -25510,7 +25510,7 @@
         <v>31</v>
       </c>
       <c r="C213">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D213" t="s">
         <v>32</v>
@@ -25524,7 +25524,7 @@
         <v>31</v>
       </c>
       <c r="C214">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D214" t="s">
         <v>32</v>
@@ -25538,7 +25538,7 @@
         <v>31</v>
       </c>
       <c r="C215">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D215" t="s">
         <v>32</v>
@@ -25552,7 +25552,7 @@
         <v>31</v>
       </c>
       <c r="C216">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D216" t="s">
         <v>32</v>
@@ -25566,7 +25566,7 @@
         <v>31</v>
       </c>
       <c r="C217">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="D217" t="s">
         <v>32</v>
@@ -25580,7 +25580,7 @@
         <v>31</v>
       </c>
       <c r="C218">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D218" t="s">
         <v>32</v>
@@ -25594,7 +25594,7 @@
         <v>31</v>
       </c>
       <c r="C219">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D219" t="s">
         <v>32</v>
@@ -25622,7 +25622,7 @@
         <v>31</v>
       </c>
       <c r="C221">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="D221" t="s">
         <v>32</v>
@@ -25636,7 +25636,7 @@
         <v>31</v>
       </c>
       <c r="C222">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D222" t="s">
         <v>32</v>
@@ -25650,7 +25650,7 @@
         <v>31</v>
       </c>
       <c r="C223">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D223" t="s">
         <v>32</v>
@@ -25664,7 +25664,7 @@
         <v>31</v>
       </c>
       <c r="C224">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D224" t="s">
         <v>32</v>
@@ -25678,7 +25678,7 @@
         <v>31</v>
       </c>
       <c r="C225">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D225" t="s">
         <v>32</v>
@@ -25692,7 +25692,7 @@
         <v>31</v>
       </c>
       <c r="C226">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D226" t="s">
         <v>32</v>
@@ -25706,7 +25706,7 @@
         <v>31</v>
       </c>
       <c r="C227">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="D227" t="s">
         <v>32</v>
@@ -25720,7 +25720,7 @@
         <v>31</v>
       </c>
       <c r="C228">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D228" t="s">
         <v>32</v>
@@ -25734,7 +25734,7 @@
         <v>31</v>
       </c>
       <c r="C229">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="D229" t="s">
         <v>32</v>
@@ -25748,7 +25748,7 @@
         <v>31</v>
       </c>
       <c r="C230">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D230" t="s">
         <v>32</v>
@@ -25762,7 +25762,7 @@
         <v>31</v>
       </c>
       <c r="C231">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D231" t="s">
         <v>32</v>
@@ -25776,7 +25776,7 @@
         <v>31</v>
       </c>
       <c r="C232">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D232" t="s">
         <v>32</v>
@@ -25790,7 +25790,7 @@
         <v>31</v>
       </c>
       <c r="C233">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D233" t="s">
         <v>32</v>
@@ -25804,7 +25804,7 @@
         <v>31</v>
       </c>
       <c r="C234">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D234" t="s">
         <v>32</v>
@@ -25818,7 +25818,7 @@
         <v>31</v>
       </c>
       <c r="C235">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D235" t="s">
         <v>32</v>
@@ -25832,7 +25832,7 @@
         <v>31</v>
       </c>
       <c r="C236">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D236" t="s">
         <v>32</v>
@@ -25846,7 +25846,7 @@
         <v>31</v>
       </c>
       <c r="C237">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D237" t="s">
         <v>32</v>
@@ -25860,7 +25860,7 @@
         <v>31</v>
       </c>
       <c r="C238">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D238" t="s">
         <v>32</v>
@@ -25874,7 +25874,7 @@
         <v>31</v>
       </c>
       <c r="C239">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D239" t="s">
         <v>32</v>
@@ -25888,7 +25888,7 @@
         <v>31</v>
       </c>
       <c r="C240">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D240" t="s">
         <v>32</v>
@@ -25902,7 +25902,7 @@
         <v>31</v>
       </c>
       <c r="C241">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D241" t="s">
         <v>32</v>
@@ -25916,7 +25916,7 @@
         <v>31</v>
       </c>
       <c r="C242">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D242" t="s">
         <v>32</v>
@@ -25930,7 +25930,7 @@
         <v>31</v>
       </c>
       <c r="C243">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D243" t="s">
         <v>32</v>
@@ -25944,7 +25944,7 @@
         <v>31</v>
       </c>
       <c r="C244">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D244" t="s">
         <v>32</v>
@@ -25958,7 +25958,7 @@
         <v>31</v>
       </c>
       <c r="C245">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D245" t="s">
         <v>32</v>
@@ -25972,7 +25972,7 @@
         <v>31</v>
       </c>
       <c r="C246">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D246" t="s">
         <v>32</v>
@@ -25986,7 +25986,7 @@
         <v>31</v>
       </c>
       <c r="C247">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D247" t="s">
         <v>32</v>
@@ -26000,7 +26000,7 @@
         <v>31</v>
       </c>
       <c r="C248">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="D248" t="s">
         <v>32</v>
@@ -26014,7 +26014,7 @@
         <v>31</v>
       </c>
       <c r="C249">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D249" t="s">
         <v>32</v>
@@ -26028,7 +26028,7 @@
         <v>31</v>
       </c>
       <c r="C250">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D250" t="s">
         <v>32</v>
@@ -26042,7 +26042,7 @@
         <v>31</v>
       </c>
       <c r="C251">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D251" t="s">
         <v>32</v>
@@ -26056,7 +26056,7 @@
         <v>31</v>
       </c>
       <c r="C252">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D252" t="s">
         <v>32</v>
@@ -26070,7 +26070,7 @@
         <v>31</v>
       </c>
       <c r="C253">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D253" t="s">
         <v>32</v>
@@ -26084,7 +26084,7 @@
         <v>31</v>
       </c>
       <c r="C254">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D254" t="s">
         <v>32</v>
@@ -26098,7 +26098,7 @@
         <v>31</v>
       </c>
       <c r="C255">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D255" t="s">
         <v>32</v>
@@ -26112,7 +26112,7 @@
         <v>31</v>
       </c>
       <c r="C256">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D256" t="s">
         <v>32</v>
@@ -26126,7 +26126,7 @@
         <v>31</v>
       </c>
       <c r="C257">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D257" t="s">
         <v>32</v>
@@ -26140,7 +26140,7 @@
         <v>31</v>
       </c>
       <c r="C258">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D258" t="s">
         <v>32</v>
@@ -26154,7 +26154,7 @@
         <v>31</v>
       </c>
       <c r="C259">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D259" t="s">
         <v>32</v>
@@ -26168,7 +26168,7 @@
         <v>31</v>
       </c>
       <c r="C260">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D260" t="s">
         <v>32</v>
@@ -26182,7 +26182,7 @@
         <v>31</v>
       </c>
       <c r="C261">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="D261" t="s">
         <v>32</v>
@@ -26196,7 +26196,7 @@
         <v>31</v>
       </c>
       <c r="C262">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D262" t="s">
         <v>32</v>
@@ -26210,7 +26210,7 @@
         <v>31</v>
       </c>
       <c r="C263">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D263" t="s">
         <v>32</v>
@@ -26224,7 +26224,7 @@
         <v>31</v>
       </c>
       <c r="C264">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D264" t="s">
         <v>32</v>
@@ -26238,7 +26238,7 @@
         <v>31</v>
       </c>
       <c r="C265">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D265" t="s">
         <v>32</v>
@@ -26252,7 +26252,7 @@
         <v>31</v>
       </c>
       <c r="C266">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D266" t="s">
         <v>32</v>
@@ -26266,7 +26266,7 @@
         <v>31</v>
       </c>
       <c r="C267">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="D267" t="s">
         <v>32</v>
@@ -26280,7 +26280,7 @@
         <v>31</v>
       </c>
       <c r="C268">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D268" t="s">
         <v>32</v>
@@ -26294,7 +26294,7 @@
         <v>31</v>
       </c>
       <c r="C269">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="D269" t="s">
         <v>32</v>
@@ -26308,7 +26308,7 @@
         <v>31</v>
       </c>
       <c r="C270">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D270" t="s">
         <v>32</v>
@@ -26322,7 +26322,7 @@
         <v>31</v>
       </c>
       <c r="C271">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D271" t="s">
         <v>32</v>
@@ -26336,7 +26336,7 @@
         <v>31</v>
       </c>
       <c r="C272">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D272" t="s">
         <v>32</v>
@@ -26350,7 +26350,7 @@
         <v>31</v>
       </c>
       <c r="C273">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D273" t="s">
         <v>32</v>
@@ -26364,7 +26364,7 @@
         <v>31</v>
       </c>
       <c r="C274">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D274" t="s">
         <v>32</v>
@@ -26378,7 +26378,7 @@
         <v>31</v>
       </c>
       <c r="C275">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D275" t="s">
         <v>32</v>
@@ -26392,7 +26392,7 @@
         <v>31</v>
       </c>
       <c r="C276">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D276" t="s">
         <v>32</v>
@@ -26406,7 +26406,7 @@
         <v>31</v>
       </c>
       <c r="C277">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D277" t="s">
         <v>32</v>
@@ -26420,7 +26420,7 @@
         <v>31</v>
       </c>
       <c r="C278">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D278" t="s">
         <v>32</v>
@@ -26434,7 +26434,7 @@
         <v>31</v>
       </c>
       <c r="C279">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D279" t="s">
         <v>32</v>
@@ -26462,7 +26462,7 @@
         <v>31</v>
       </c>
       <c r="C281">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D281" t="s">
         <v>32</v>
@@ -26476,7 +26476,7 @@
         <v>31</v>
       </c>
       <c r="C282">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D282" t="s">
         <v>32</v>
@@ -26504,7 +26504,7 @@
         <v>31</v>
       </c>
       <c r="C284">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D284" t="s">
         <v>32</v>
@@ -26518,7 +26518,7 @@
         <v>31</v>
       </c>
       <c r="C285">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D285" t="s">
         <v>32</v>
@@ -26532,7 +26532,7 @@
         <v>31</v>
       </c>
       <c r="C286">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D286" t="s">
         <v>32</v>
@@ -26546,7 +26546,7 @@
         <v>31</v>
       </c>
       <c r="C287">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D287" t="s">
         <v>32</v>
@@ -26560,7 +26560,7 @@
         <v>31</v>
       </c>
       <c r="C288">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D288" t="s">
         <v>32</v>
@@ -26574,7 +26574,7 @@
         <v>31</v>
       </c>
       <c r="C289">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D289" t="s">
         <v>32</v>
@@ -26588,7 +26588,7 @@
         <v>31</v>
       </c>
       <c r="C290">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D290" t="s">
         <v>32</v>
@@ -26602,7 +26602,7 @@
         <v>31</v>
       </c>
       <c r="C291">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D291" t="s">
         <v>32</v>
@@ -26616,7 +26616,7 @@
         <v>31</v>
       </c>
       <c r="C292">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D292" t="s">
         <v>32</v>
@@ -26630,7 +26630,7 @@
         <v>31</v>
       </c>
       <c r="C293">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D293" t="s">
         <v>32</v>
@@ -26644,7 +26644,7 @@
         <v>31</v>
       </c>
       <c r="C294">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D294" t="s">
         <v>32</v>
@@ -26658,7 +26658,7 @@
         <v>31</v>
       </c>
       <c r="C295">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="D295" t="s">
         <v>32</v>
@@ -26672,7 +26672,7 @@
         <v>31</v>
       </c>
       <c r="C296">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D296" t="s">
         <v>32</v>
@@ -26686,7 +26686,7 @@
         <v>31</v>
       </c>
       <c r="C297">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D297" t="s">
         <v>32</v>
@@ -26700,7 +26700,7 @@
         <v>31</v>
       </c>
       <c r="C298">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D298" t="s">
         <v>32</v>
@@ -26714,7 +26714,7 @@
         <v>31</v>
       </c>
       <c r="C299">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D299" t="s">
         <v>32</v>
@@ -26728,7 +26728,7 @@
         <v>31</v>
       </c>
       <c r="C300">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D300" t="s">
         <v>32</v>
@@ -26742,7 +26742,7 @@
         <v>31</v>
       </c>
       <c r="C301">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D301" t="s">
         <v>32</v>
@@ -26756,7 +26756,7 @@
         <v>31</v>
       </c>
       <c r="C302">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D302" t="s">
         <v>32</v>
@@ -26770,7 +26770,7 @@
         <v>31</v>
       </c>
       <c r="C303">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D303" t="s">
         <v>32</v>
@@ -26784,7 +26784,7 @@
         <v>31</v>
       </c>
       <c r="C304">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D304" t="s">
         <v>32</v>
@@ -26798,7 +26798,7 @@
         <v>31</v>
       </c>
       <c r="C305">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D305" t="s">
         <v>32</v>
@@ -26812,7 +26812,7 @@
         <v>31</v>
       </c>
       <c r="C306">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D306" t="s">
         <v>32</v>
@@ -26826,7 +26826,7 @@
         <v>31</v>
       </c>
       <c r="C307">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D307" t="s">
         <v>32</v>
@@ -26840,7 +26840,7 @@
         <v>31</v>
       </c>
       <c r="C308">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D308" t="s">
         <v>32</v>
@@ -26854,7 +26854,7 @@
         <v>31</v>
       </c>
       <c r="C309">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D309" t="s">
         <v>32</v>
@@ -26868,7 +26868,7 @@
         <v>31</v>
       </c>
       <c r="C310">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="D310" t="s">
         <v>32</v>
@@ -26882,7 +26882,7 @@
         <v>31</v>
       </c>
       <c r="C311">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D311" t="s">
         <v>32</v>
@@ -26896,7 +26896,7 @@
         <v>31</v>
       </c>
       <c r="C312">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D312" t="s">
         <v>32</v>
@@ -26910,7 +26910,7 @@
         <v>31</v>
       </c>
       <c r="C313">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D313" t="s">
         <v>32</v>
@@ -26924,7 +26924,7 @@
         <v>31</v>
       </c>
       <c r="C314">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="D314" t="s">
         <v>32</v>
@@ -26938,7 +26938,7 @@
         <v>31</v>
       </c>
       <c r="C315">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="D315" t="s">
         <v>32</v>
@@ -26952,7 +26952,7 @@
         <v>31</v>
       </c>
       <c r="C316">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D316" t="s">
         <v>32</v>
@@ -26966,7 +26966,7 @@
         <v>31</v>
       </c>
       <c r="C317">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D317" t="s">
         <v>32</v>
@@ -26980,7 +26980,7 @@
         <v>31</v>
       </c>
       <c r="C318">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="D318" t="s">
         <v>32</v>
@@ -26994,7 +26994,7 @@
         <v>31</v>
       </c>
       <c r="C319">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D319" t="s">
         <v>32</v>
@@ -27008,7 +27008,7 @@
         <v>31</v>
       </c>
       <c r="C320">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D320" t="s">
         <v>32</v>
@@ -27022,7 +27022,7 @@
         <v>31</v>
       </c>
       <c r="C321">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D321" t="s">
         <v>32</v>
@@ -27036,7 +27036,7 @@
         <v>31</v>
       </c>
       <c r="C322">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D322" t="s">
         <v>32</v>
@@ -27050,7 +27050,7 @@
         <v>31</v>
       </c>
       <c r="C323">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D323" t="s">
         <v>32</v>
@@ -27064,7 +27064,7 @@
         <v>31</v>
       </c>
       <c r="C324">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D324" t="s">
         <v>32</v>
@@ -27078,7 +27078,7 @@
         <v>31</v>
       </c>
       <c r="C325">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D325" t="s">
         <v>32</v>
@@ -27092,7 +27092,7 @@
         <v>31</v>
       </c>
       <c r="C326">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="D326" t="s">
         <v>32</v>
@@ -27106,7 +27106,7 @@
         <v>31</v>
       </c>
       <c r="C327">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D327" t="s">
         <v>32</v>
@@ -27120,7 +27120,7 @@
         <v>31</v>
       </c>
       <c r="C328">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D328" t="s">
         <v>32</v>
@@ -27134,7 +27134,7 @@
         <v>31</v>
       </c>
       <c r="C329">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D329" t="s">
         <v>32</v>
@@ -27148,7 +27148,7 @@
         <v>31</v>
       </c>
       <c r="C330">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D330" t="s">
         <v>32</v>
@@ -27162,7 +27162,7 @@
         <v>31</v>
       </c>
       <c r="C331">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D331" t="s">
         <v>32</v>
@@ -27176,7 +27176,7 @@
         <v>31</v>
       </c>
       <c r="C332">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D332" t="s">
         <v>32</v>
@@ -27190,7 +27190,7 @@
         <v>31</v>
       </c>
       <c r="C333">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D333" t="s">
         <v>32</v>
@@ -27204,7 +27204,7 @@
         <v>31</v>
       </c>
       <c r="C334">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D334" t="s">
         <v>32</v>
@@ -27218,7 +27218,7 @@
         <v>31</v>
       </c>
       <c r="C335">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D335" t="s">
         <v>32</v>
@@ -27232,7 +27232,7 @@
         <v>31</v>
       </c>
       <c r="C336">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D336" t="s">
         <v>32</v>
@@ -27246,7 +27246,7 @@
         <v>31</v>
       </c>
       <c r="C337">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D337" t="s">
         <v>32</v>
@@ -27260,7 +27260,7 @@
         <v>31</v>
       </c>
       <c r="C338">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="D338" t="s">
         <v>32</v>
@@ -27274,7 +27274,7 @@
         <v>31</v>
       </c>
       <c r="C339">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D339" t="s">
         <v>32</v>
@@ -27302,7 +27302,7 @@
         <v>31</v>
       </c>
       <c r="C341">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D341" t="s">
         <v>32</v>
@@ -27316,7 +27316,7 @@
         <v>31</v>
       </c>
       <c r="C342">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D342" t="s">
         <v>32</v>
@@ -27330,7 +27330,7 @@
         <v>31</v>
       </c>
       <c r="C343">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D343" t="s">
         <v>32</v>
@@ -27344,7 +27344,7 @@
         <v>31</v>
       </c>
       <c r="C344">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D344" t="s">
         <v>32</v>
@@ -27358,7 +27358,7 @@
         <v>31</v>
       </c>
       <c r="C345">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D345" t="s">
         <v>32</v>
@@ -27372,7 +27372,7 @@
         <v>31</v>
       </c>
       <c r="C346">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D346" t="s">
         <v>32</v>
@@ -27386,7 +27386,7 @@
         <v>31</v>
       </c>
       <c r="C347">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D347" t="s">
         <v>32</v>
@@ -27400,7 +27400,7 @@
         <v>31</v>
       </c>
       <c r="C348">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D348" t="s">
         <v>32</v>
@@ -27414,7 +27414,7 @@
         <v>31</v>
       </c>
       <c r="C349">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D349" t="s">
         <v>32</v>
@@ -27428,7 +27428,7 @@
         <v>31</v>
       </c>
       <c r="C350">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D350" t="s">
         <v>32</v>
@@ -27442,7 +27442,7 @@
         <v>31</v>
       </c>
       <c r="C351">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="D351" t="s">
         <v>32</v>
@@ -27456,7 +27456,7 @@
         <v>31</v>
       </c>
       <c r="C352">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D352" t="s">
         <v>32</v>
@@ -27470,7 +27470,7 @@
         <v>31</v>
       </c>
       <c r="C353">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D353" t="s">
         <v>32</v>
@@ -27484,7 +27484,7 @@
         <v>31</v>
       </c>
       <c r="C354">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="D354" t="s">
         <v>32</v>
@@ -27498,7 +27498,7 @@
         <v>31</v>
       </c>
       <c r="C355">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D355" t="s">
         <v>32</v>
@@ -27512,7 +27512,7 @@
         <v>31</v>
       </c>
       <c r="C356">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D356" t="s">
         <v>32</v>
@@ -27526,7 +27526,7 @@
         <v>31</v>
       </c>
       <c r="C357">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="D357" t="s">
         <v>32</v>
@@ -27540,7 +27540,7 @@
         <v>31</v>
       </c>
       <c r="C358">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D358" t="s">
         <v>32</v>
@@ -27554,7 +27554,7 @@
         <v>31</v>
       </c>
       <c r="C359">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D359" t="s">
         <v>32</v>
@@ -27568,7 +27568,7 @@
         <v>31</v>
       </c>
       <c r="C360">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="D360" t="s">
         <v>32</v>
@@ -27582,7 +27582,7 @@
         <v>31</v>
       </c>
       <c r="C361">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D361" t="s">
         <v>32</v>
@@ -27596,7 +27596,7 @@
         <v>31</v>
       </c>
       <c r="C362">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="D362" t="s">
         <v>32</v>
@@ -27610,7 +27610,7 @@
         <v>31</v>
       </c>
       <c r="C363">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="D363" t="s">
         <v>32</v>
@@ -27624,7 +27624,7 @@
         <v>31</v>
       </c>
       <c r="C364">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D364" t="s">
         <v>32</v>
@@ -27638,7 +27638,7 @@
         <v>31</v>
       </c>
       <c r="C365">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="D365" t="s">
         <v>32</v>
@@ -27652,7 +27652,7 @@
         <v>31</v>
       </c>
       <c r="C366">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D366" t="s">
         <v>32</v>
@@ -27666,7 +27666,7 @@
         <v>31</v>
       </c>
       <c r="C367">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D367" t="s">
         <v>32</v>
@@ -27680,7 +27680,7 @@
         <v>31</v>
       </c>
       <c r="C368">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D368" t="s">
         <v>32</v>
@@ -27694,7 +27694,7 @@
         <v>31</v>
       </c>
       <c r="C369">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D369" t="s">
         <v>32</v>
@@ -27708,7 +27708,7 @@
         <v>31</v>
       </c>
       <c r="C370">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D370" t="s">
         <v>32</v>
@@ -27722,7 +27722,7 @@
         <v>31</v>
       </c>
       <c r="C371">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D371" t="s">
         <v>32</v>
@@ -27736,7 +27736,7 @@
         <v>31</v>
       </c>
       <c r="C372">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="D372" t="s">
         <v>32</v>
@@ -27750,7 +27750,7 @@
         <v>31</v>
       </c>
       <c r="C373">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D373" t="s">
         <v>32</v>
@@ -27764,7 +27764,7 @@
         <v>31</v>
       </c>
       <c r="C374">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D374" t="s">
         <v>32</v>
@@ -27792,7 +27792,7 @@
         <v>31</v>
       </c>
       <c r="C376">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D376" t="s">
         <v>32</v>
@@ -27806,7 +27806,7 @@
         <v>31</v>
       </c>
       <c r="C377">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D377" t="s">
         <v>32</v>
@@ -27820,7 +27820,7 @@
         <v>31</v>
       </c>
       <c r="C378">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D378" t="s">
         <v>32</v>
@@ -27834,7 +27834,7 @@
         <v>31</v>
       </c>
       <c r="C379">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D379" t="s">
         <v>32</v>
@@ -27848,7 +27848,7 @@
         <v>31</v>
       </c>
       <c r="C380">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D380" t="s">
         <v>32</v>
@@ -27862,7 +27862,7 @@
         <v>31</v>
       </c>
       <c r="C381">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D381" t="s">
         <v>32</v>
@@ -27876,7 +27876,7 @@
         <v>31</v>
       </c>
       <c r="C382">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D382" t="s">
         <v>32</v>
@@ -27890,7 +27890,7 @@
         <v>31</v>
       </c>
       <c r="C383">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="D383" t="s">
         <v>32</v>
@@ -27904,7 +27904,7 @@
         <v>31</v>
       </c>
       <c r="C384">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D384" t="s">
         <v>32</v>
@@ -27918,7 +27918,7 @@
         <v>31</v>
       </c>
       <c r="C385">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D385" t="s">
         <v>32</v>
@@ -27932,7 +27932,7 @@
         <v>31</v>
       </c>
       <c r="C386">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D386" t="s">
         <v>32</v>
@@ -27946,7 +27946,7 @@
         <v>31</v>
       </c>
       <c r="C387">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="D387" t="s">
         <v>32</v>
@@ -27960,7 +27960,7 @@
         <v>31</v>
       </c>
       <c r="C388">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="D388" t="s">
         <v>32</v>
@@ -27974,7 +27974,7 @@
         <v>31</v>
       </c>
       <c r="C389">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D389" t="s">
         <v>32</v>
@@ -27988,7 +27988,7 @@
         <v>31</v>
       </c>
       <c r="C390">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D390" t="s">
         <v>32</v>
@@ -28002,7 +28002,7 @@
         <v>31</v>
       </c>
       <c r="C391">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D391" t="s">
         <v>32</v>
@@ -28030,7 +28030,7 @@
         <v>31</v>
       </c>
       <c r="C393">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D393" t="s">
         <v>32</v>
@@ -28044,7 +28044,7 @@
         <v>31</v>
       </c>
       <c r="C394">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="D394" t="s">
         <v>32</v>
@@ -28058,7 +28058,7 @@
         <v>31</v>
       </c>
       <c r="C395">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="D395" t="s">
         <v>32</v>
@@ -28072,7 +28072,7 @@
         <v>31</v>
       </c>
       <c r="C396">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D396" t="s">
         <v>32</v>
@@ -28086,7 +28086,7 @@
         <v>31</v>
       </c>
       <c r="C397">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D397" t="s">
         <v>32</v>
@@ -28100,7 +28100,7 @@
         <v>31</v>
       </c>
       <c r="C398">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D398" t="s">
         <v>32</v>
@@ -28114,7 +28114,7 @@
         <v>31</v>
       </c>
       <c r="C399">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D399" t="s">
         <v>32</v>
@@ -28128,7 +28128,7 @@
         <v>31</v>
       </c>
       <c r="C400">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D400" t="s">
         <v>32</v>
@@ -28142,7 +28142,7 @@
         <v>31</v>
       </c>
       <c r="C401">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D401" t="s">
         <v>32</v>
